--- a/filer/35663908_kompan.xlsx
+++ b/filer/35663908_kompan.xlsx
@@ -615,7 +615,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/35663908_kompan.xlsx
+++ b/filer/35663908_kompan.xlsx
@@ -10,7 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik_35663908" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw_35663908" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw_35663908" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_funktion" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw_35663908" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,6 +72,17 @@
       <i val="1"/>
       <color rgb="00595959"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00444444"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="8">
@@ -170,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -184,17 +197,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -230,6 +243,27 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -595,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L83"/>
+  <dimension ref="A1:L106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -615,7 +649,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Independent Auditor’s Report</t>
         </is>
       </c>
     </row>
@@ -629,7 +663,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -644,35 +678,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -726,7 +760,7 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Produktionsomkostninger</t>
+          <t>Andre driftsindtægter</t>
         </is>
       </c>
       <c r="B5" s="8">
@@ -772,49 +806,49 @@
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Bruttoresultat</t>
-        </is>
-      </c>
-      <c r="B6" s="8">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Vareforbrug</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
         <f>'res_raw_35663908'!$B$4</f>
         <v/>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="5">
         <f>'res_raw_35663908'!$C$4</f>
         <v/>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="5">
         <f>'res_raw_35663908'!$D$4</f>
         <v/>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="5">
         <f>'res_raw_35663908'!$E$4</f>
         <v/>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="5">
         <f>'res_raw_35663908'!$F$4</f>
         <v/>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" s="9">
+      <c r="H6" s="6">
         <f>IFERROR(B6/$B$6*100,"")</f>
         <v/>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="6">
         <f>IFERROR(C6/$B$6*100,"")</f>
         <v/>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="6">
         <f>IFERROR(D6/$B$6*100,"")</f>
         <v/>
       </c>
-      <c r="K6" s="9">
+      <c r="K6" s="6">
         <f>IFERROR(E6/$B$6*100,"")</f>
         <v/>
       </c>
-      <c r="L6" s="9">
+      <c r="L6" s="6">
         <f>IFERROR(F6/$B$6*100,"")</f>
         <v/>
       </c>
@@ -822,7 +856,7 @@
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Salgs- og distributionsomkostninger</t>
+          <t>Andre eksterne omkostninger</t>
         </is>
       </c>
       <c r="B7" s="8">
@@ -868,145 +902,145 @@
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Administrationsomkostninger</t>
-        </is>
-      </c>
-      <c r="B8" s="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Bruttoresultat</t>
+        </is>
+      </c>
+      <c r="B8" s="11">
         <f>'res_raw_35663908'!$B$6</f>
         <v/>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="11">
         <f>'res_raw_35663908'!$C$6</f>
         <v/>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="11">
         <f>'res_raw_35663908'!$D$6</f>
         <v/>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="11">
         <f>'res_raw_35663908'!$E$6</f>
         <v/>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="11">
         <f>'res_raw_35663908'!$F$6</f>
         <v/>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" s="9">
+      <c r="H8" s="12">
         <f>IFERROR(B8/$B$8*100,"")</f>
         <v/>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="12">
         <f>IFERROR(C8/$B$8*100,"")</f>
         <v/>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="12">
         <f>IFERROR(D8/$B$8*100,"")</f>
         <v/>
       </c>
-      <c r="K8" s="9">
+      <c r="K8" s="12">
         <f>IFERROR(E8/$B$8*100,"")</f>
         <v/>
       </c>
-      <c r="L8" s="9">
+      <c r="L8" s="12">
         <f>IFERROR(F8/$B$8*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Andre driftsindtægter</t>
-        </is>
-      </c>
-      <c r="B9" s="11">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Personaleomkostninger</t>
+        </is>
+      </c>
+      <c r="B9" s="8">
         <f>'res_raw_35663908'!$B$7</f>
         <v/>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="8">
         <f>'res_raw_35663908'!$C$7</f>
         <v/>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="8">
         <f>'res_raw_35663908'!$D$7</f>
         <v/>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="8">
         <f>'res_raw_35663908'!$E$7</f>
         <v/>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="8">
         <f>'res_raw_35663908'!$F$7</f>
         <v/>
       </c>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" s="12">
+      <c r="H9" s="9">
         <f>IFERROR(B9/$B$9*100,"")</f>
         <v/>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="9">
         <f>IFERROR(C9/$B$9*100,"")</f>
         <v/>
       </c>
-      <c r="J9" s="12">
+      <c r="J9" s="9">
         <f>IFERROR(D9/$B$9*100,"")</f>
         <v/>
       </c>
-      <c r="K9" s="12">
+      <c r="K9" s="9">
         <f>IFERROR(E9/$B$9*100,"")</f>
         <v/>
       </c>
-      <c r="L9" s="12">
+      <c r="L9" s="9">
         <f>IFERROR(F9/$B$9*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Andre driftsomkostninger</t>
-        </is>
-      </c>
-      <c r="B10" s="5">
-        <f>'res_raw_35663908'!$B$8</f>
-        <v/>
-      </c>
-      <c r="C10" s="5">
-        <f>'res_raw_35663908'!$C$8</f>
-        <v/>
-      </c>
-      <c r="D10" s="5">
-        <f>'res_raw_35663908'!$D$8</f>
-        <v/>
-      </c>
-      <c r="E10" s="5">
-        <f>'res_raw_35663908'!$E$8</f>
-        <v/>
-      </c>
-      <c r="F10" s="5">
-        <f>'res_raw_35663908'!$F$8</f>
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Resultat før afskrivninger</t>
+        </is>
+      </c>
+      <c r="B10" s="11">
+        <f>IFERROR($B$8-ABS($B$9),"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="11">
+        <f>IFERROR($C$8-ABS($C$9),"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="11">
+        <f>IFERROR($D$8-ABS($D$9),"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="11">
+        <f>IFERROR($E$8-ABS($E$9),"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="11">
+        <f>IFERROR($F$8-ABS($F$9),"")</f>
         <v/>
       </c>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="6">
+      <c r="H10" s="12">
         <f>IFERROR(B10/$B$10*100,"")</f>
         <v/>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="12">
         <f>IFERROR(C10/$B$10*100,"")</f>
         <v/>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="12">
         <f>IFERROR(D10/$B$10*100,"")</f>
         <v/>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="12">
         <f>IFERROR(E10/$B$10*100,"")</f>
         <v/>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="12">
         <f>IFERROR(F10/$B$10*100,"")</f>
         <v/>
       </c>
@@ -1014,7 +1048,7 @@
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Resultat af primær drift</t>
+          <t>Af- og nedskrivninger</t>
         </is>
       </c>
       <c r="B11" s="8">
@@ -1062,7 +1096,7 @@
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Indtægter af kapitalandele, dattervirksomheder</t>
+          <t>Andre driftsomkostninger</t>
         </is>
       </c>
       <c r="B12" s="5">
@@ -1110,7 +1144,7 @@
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Finansielle indtægter</t>
+          <t>Resultat af primær drift</t>
         </is>
       </c>
       <c r="B13" s="11">
@@ -1158,7 +1192,7 @@
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Finansielle omkostninger</t>
+          <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
       <c r="B14" s="5">
@@ -1206,7 +1240,7 @@
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Finansielle poster, netto</t>
+          <t>Finansielle indtægter</t>
         </is>
       </c>
       <c r="B15" s="8">
@@ -1252,49 +1286,49 @@
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Resultat før skat</t>
-        </is>
-      </c>
-      <c r="B16" s="8">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Finansielle omkostninger</t>
+        </is>
+      </c>
+      <c r="B16" s="5">
         <f>'res_raw_35663908'!$B$14</f>
         <v/>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="5">
         <f>'res_raw_35663908'!$C$14</f>
         <v/>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="5">
         <f>'res_raw_35663908'!$D$14</f>
         <v/>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="5">
         <f>'res_raw_35663908'!$E$14</f>
         <v/>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="5">
         <f>'res_raw_35663908'!$F$14</f>
         <v/>
       </c>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" s="9">
+      <c r="H16" s="6">
         <f>IFERROR(B16/$B$16*100,"")</f>
         <v/>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="6">
         <f>IFERROR(C16/$B$16*100,"")</f>
         <v/>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="6">
         <f>IFERROR(D16/$B$16*100,"")</f>
         <v/>
       </c>
-      <c r="K16" s="9">
+      <c r="K16" s="6">
         <f>IFERROR(E16/$B$16*100,"")</f>
         <v/>
       </c>
-      <c r="L16" s="9">
+      <c r="L16" s="6">
         <f>IFERROR(F16/$B$16*100,"")</f>
         <v/>
       </c>
@@ -1302,7 +1336,7 @@
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Skat af årets resultat</t>
+          <t>Finansielle poster, netto</t>
         </is>
       </c>
       <c r="B17" s="11">
@@ -1348,211 +1382,211 @@
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Resultat før skat</t>
+        </is>
+      </c>
+      <c r="B18" s="11">
+        <f>'res_raw_35663908'!$B$16</f>
+        <v/>
+      </c>
+      <c r="C18" s="11">
+        <f>'res_raw_35663908'!$C$16</f>
+        <v/>
+      </c>
+      <c r="D18" s="11">
+        <f>'res_raw_35663908'!$D$16</f>
+        <v/>
+      </c>
+      <c r="E18" s="11">
+        <f>'res_raw_35663908'!$E$16</f>
+        <v/>
+      </c>
+      <c r="F18" s="11">
+        <f>'res_raw_35663908'!$F$16</f>
+        <v/>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" s="12">
+        <f>IFERROR(B18/$B$18*100,"")</f>
+        <v/>
+      </c>
+      <c r="I18" s="12">
+        <f>IFERROR(C18/$B$18*100,"")</f>
+        <v/>
+      </c>
+      <c r="J18" s="12">
+        <f>IFERROR(D18/$B$18*100,"")</f>
+        <v/>
+      </c>
+      <c r="K18" s="12">
+        <f>IFERROR(E18/$B$18*100,"")</f>
+        <v/>
+      </c>
+      <c r="L18" s="12">
+        <f>IFERROR(F18/$B$18*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Skat af årets resultat</t>
+        </is>
+      </c>
+      <c r="B19" s="8">
+        <f>'res_raw_35663908'!$B$17</f>
+        <v/>
+      </c>
+      <c r="C19" s="8">
+        <f>'res_raw_35663908'!$C$17</f>
+        <v/>
+      </c>
+      <c r="D19" s="8">
+        <f>'res_raw_35663908'!$D$17</f>
+        <v/>
+      </c>
+      <c r="E19" s="8">
+        <f>'res_raw_35663908'!$E$17</f>
+        <v/>
+      </c>
+      <c r="F19" s="8">
+        <f>'res_raw_35663908'!$F$17</f>
+        <v/>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" s="9">
+        <f>IFERROR(B19/$B$19*100,"")</f>
+        <v/>
+      </c>
+      <c r="I19" s="9">
+        <f>IFERROR(C19/$B$19*100,"")</f>
+        <v/>
+      </c>
+      <c r="J19" s="9">
+        <f>IFERROR(D19/$B$19*100,"")</f>
+        <v/>
+      </c>
+      <c r="K19" s="9">
+        <f>IFERROR(E19/$B$19*100,"")</f>
+        <v/>
+      </c>
+      <c r="L19" s="9">
+        <f>IFERROR(F19/$B$19*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B18" s="8">
-        <f>'res_raw_35663908'!$B$16</f>
-        <v/>
-      </c>
-      <c r="C18" s="8">
-        <f>'res_raw_35663908'!$C$16</f>
-        <v/>
-      </c>
-      <c r="D18" s="8">
-        <f>'res_raw_35663908'!$D$16</f>
-        <v/>
-      </c>
-      <c r="E18" s="8">
-        <f>'res_raw_35663908'!$E$16</f>
-        <v/>
-      </c>
-      <c r="F18" s="8">
-        <f>'res_raw_35663908'!$F$16</f>
-        <v/>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" s="9">
-        <f>IFERROR(B18/$B$18*100,"")</f>
-        <v/>
-      </c>
-      <c r="I18" s="9">
-        <f>IFERROR(C18/$B$18*100,"")</f>
-        <v/>
-      </c>
-      <c r="J18" s="9">
-        <f>IFERROR(D18/$B$18*100,"")</f>
-        <v/>
-      </c>
-      <c r="K18" s="9">
-        <f>IFERROR(E18/$B$18*100,"")</f>
-        <v/>
-      </c>
-      <c r="L18" s="9">
-        <f>IFERROR(F18/$B$18*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="B20" s="11">
+        <f>'res_raw_35663908'!$B$18</f>
+        <v/>
+      </c>
+      <c r="C20" s="11">
+        <f>'res_raw_35663908'!$C$18</f>
+        <v/>
+      </c>
+      <c r="D20" s="11">
+        <f>'res_raw_35663908'!$D$18</f>
+        <v/>
+      </c>
+      <c r="E20" s="11">
+        <f>'res_raw_35663908'!$E$18</f>
+        <v/>
+      </c>
+      <c r="F20" s="11">
+        <f>'res_raw_35663908'!$F$18</f>
+        <v/>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" s="12">
+        <f>IFERROR(B20/$B$20*100,"")</f>
+        <v/>
+      </c>
+      <c r="I20" s="12">
+        <f>IFERROR(C20/$B$20*100,"")</f>
+        <v/>
+      </c>
+      <c r="J20" s="12">
+        <f>IFERROR(D20/$B$20*100,"")</f>
+        <v/>
+      </c>
+      <c r="K20" s="12">
+        <f>IFERROR(E20/$B$20*100,"")</f>
+        <v/>
+      </c>
+      <c r="L20" s="12">
+        <f>IFERROR(F20/$B$20*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>AKTIVER t.kr.</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C20" s="3" t="n">
+      <c r="B22" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="C22" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>2024</v>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="I20" s="3" t="n">
+      <c r="F22" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="J20" s="3" t="n">
+      <c r="I22" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="J22" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="K22" s="3" t="n">
         <v>2024</v>
       </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Immaterielle anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B21" s="8">
-        <f>'balance_raw_35663908'!$B$2</f>
-        <v/>
-      </c>
-      <c r="C21" s="8">
-        <f>'balance_raw_35663908'!$C$2</f>
-        <v/>
-      </c>
-      <c r="D21" s="8">
-        <f>'balance_raw_35663908'!$D$2</f>
-        <v/>
-      </c>
-      <c r="E21" s="8">
-        <f>'balance_raw_35663908'!$E$2</f>
-        <v/>
-      </c>
-      <c r="F21" s="8">
-        <f>'balance_raw_35663908'!$F$2</f>
-        <v/>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" s="9">
-        <f>IFERROR(B21/$B$21*100,"")</f>
-        <v/>
-      </c>
-      <c r="I21" s="9">
-        <f>IFERROR(C21/$B$21*100,"")</f>
-        <v/>
-      </c>
-      <c r="J21" s="9">
-        <f>IFERROR(D21/$B$21*100,"")</f>
-        <v/>
-      </c>
-      <c r="K21" s="9">
-        <f>IFERROR(E21/$B$21*100,"")</f>
-        <v/>
-      </c>
-      <c r="L21" s="9">
-        <f>IFERROR(F21/$B$21*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Materielle anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B22" s="8">
-        <f>'balance_raw_35663908'!$B$3</f>
-        <v/>
-      </c>
-      <c r="C22" s="8">
-        <f>'balance_raw_35663908'!$C$3</f>
-        <v/>
-      </c>
-      <c r="D22" s="8">
-        <f>'balance_raw_35663908'!$D$3</f>
-        <v/>
-      </c>
-      <c r="E22" s="8">
-        <f>'balance_raw_35663908'!$E$3</f>
-        <v/>
-      </c>
-      <c r="F22" s="8">
-        <f>'balance_raw_35663908'!$F$3</f>
-        <v/>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" s="9">
-        <f>IFERROR(B22/$B$22*100,"")</f>
-        <v/>
-      </c>
-      <c r="I22" s="9">
-        <f>IFERROR(C22/$B$22*100,"")</f>
-        <v/>
-      </c>
-      <c r="J22" s="9">
-        <f>IFERROR(D22/$B$22*100,"")</f>
-        <v/>
-      </c>
-      <c r="K22" s="9">
-        <f>IFERROR(E22/$B$22*100,"")</f>
-        <v/>
-      </c>
-      <c r="L22" s="9">
-        <f>IFERROR(F22/$B$22*100,"")</f>
-        <v/>
+      <c r="L22" s="3" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Anlægsaktiver</t>
+          <t>Udviklingsprojekter</t>
         </is>
       </c>
       <c r="B23" s="8">
-        <f>'balance_raw_35663908'!$B$4</f>
+        <f>'balance_raw_35663908'!$B$2</f>
         <v/>
       </c>
       <c r="C23" s="8">
-        <f>'balance_raw_35663908'!$C$4</f>
+        <f>'balance_raw_35663908'!$C$2</f>
         <v/>
       </c>
       <c r="D23" s="8">
-        <f>'balance_raw_35663908'!$D$4</f>
+        <f>'balance_raw_35663908'!$D$2</f>
         <v/>
       </c>
       <c r="E23" s="8">
-        <f>'balance_raw_35663908'!$E$4</f>
+        <f>'balance_raw_35663908'!$E$2</f>
         <v/>
       </c>
       <c r="F23" s="8">
-        <f>'balance_raw_35663908'!$F$4</f>
+        <f>'balance_raw_35663908'!$F$2</f>
         <v/>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1578,193 +1612,193 @@
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Varebeholdninger</t>
-        </is>
-      </c>
-      <c r="B24" s="8">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Patenter, varemærker mv.</t>
+        </is>
+      </c>
+      <c r="B24" s="5">
+        <f>'balance_raw_35663908'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C24" s="5">
+        <f>'balance_raw_35663908'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D24" s="5">
+        <f>'balance_raw_35663908'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E24" s="5">
+        <f>'balance_raw_35663908'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F24" s="5">
+        <f>'balance_raw_35663908'!$F$3</f>
+        <v/>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" s="6">
+        <f>IFERROR(B24/$B$24*100,"")</f>
+        <v/>
+      </c>
+      <c r="I24" s="6">
+        <f>IFERROR(C24/$B$24*100,"")</f>
+        <v/>
+      </c>
+      <c r="J24" s="6">
+        <f>IFERROR(D24/$B$24*100,"")</f>
+        <v/>
+      </c>
+      <c r="K24" s="6">
+        <f>IFERROR(E24/$B$24*100,"")</f>
+        <v/>
+      </c>
+      <c r="L24" s="6">
+        <f>IFERROR(F24/$B$24*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B25" s="8">
+        <f>'balance_raw_35663908'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C25" s="8">
+        <f>'balance_raw_35663908'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D25" s="8">
+        <f>'balance_raw_35663908'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E25" s="8">
+        <f>'balance_raw_35663908'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F25" s="8">
+        <f>'balance_raw_35663908'!$F$4</f>
+        <v/>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" s="9">
+        <f>IFERROR(B25/$B$25*100,"")</f>
+        <v/>
+      </c>
+      <c r="I25" s="9">
+        <f>IFERROR(C25/$B$25*100,"")</f>
+        <v/>
+      </c>
+      <c r="J25" s="9">
+        <f>IFERROR(D25/$B$25*100,"")</f>
+        <v/>
+      </c>
+      <c r="K25" s="9">
+        <f>IFERROR(E25/$B$25*100,"")</f>
+        <v/>
+      </c>
+      <c r="L25" s="9">
+        <f>IFERROR(F25/$B$25*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Immaterielle anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B26" s="11">
         <f>'balance_raw_35663908'!$B$5</f>
         <v/>
       </c>
-      <c r="C24" s="8">
+      <c r="C26" s="11">
         <f>'balance_raw_35663908'!$C$5</f>
         <v/>
       </c>
-      <c r="D24" s="8">
+      <c r="D26" s="11">
         <f>'balance_raw_35663908'!$D$5</f>
         <v/>
       </c>
-      <c r="E24" s="8">
+      <c r="E26" s="11">
         <f>'balance_raw_35663908'!$E$5</f>
         <v/>
       </c>
-      <c r="F24" s="8">
+      <c r="F26" s="11">
         <f>'balance_raw_35663908'!$F$5</f>
         <v/>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" s="9">
-        <f>IFERROR(B24/$B$24*100,"")</f>
-        <v/>
-      </c>
-      <c r="I24" s="9">
-        <f>IFERROR(C24/$B$24*100,"")</f>
-        <v/>
-      </c>
-      <c r="J24" s="9">
-        <f>IFERROR(D24/$B$24*100,"")</f>
-        <v/>
-      </c>
-      <c r="K24" s="9">
-        <f>IFERROR(E24/$B$24*100,"")</f>
-        <v/>
-      </c>
-      <c r="L24" s="9">
-        <f>IFERROR(F24/$B$24*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>Tilgodehavender fra salg og tjenesteydelser</t>
-        </is>
-      </c>
-      <c r="B25" s="11">
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" s="12">
+        <f>IFERROR(B26/$B$26*100,"")</f>
+        <v/>
+      </c>
+      <c r="I26" s="12">
+        <f>IFERROR(C26/$B$26*100,"")</f>
+        <v/>
+      </c>
+      <c r="J26" s="12">
+        <f>IFERROR(D26/$B$26*100,"")</f>
+        <v/>
+      </c>
+      <c r="K26" s="12">
+        <f>IFERROR(E26/$B$26*100,"")</f>
+        <v/>
+      </c>
+      <c r="L26" s="12">
+        <f>IFERROR(F26/$B$26*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Grunde og bygninger</t>
+        </is>
+      </c>
+      <c r="B27" s="8">
         <f>'balance_raw_35663908'!$B$6</f>
         <v/>
       </c>
-      <c r="C25" s="11">
+      <c r="C27" s="8">
         <f>'balance_raw_35663908'!$C$6</f>
         <v/>
       </c>
-      <c r="D25" s="11">
+      <c r="D27" s="8">
         <f>'balance_raw_35663908'!$D$6</f>
         <v/>
       </c>
-      <c r="E25" s="11">
+      <c r="E27" s="8">
         <f>'balance_raw_35663908'!$E$6</f>
         <v/>
       </c>
-      <c r="F25" s="11">
+      <c r="F27" s="8">
         <f>'balance_raw_35663908'!$F$6</f>
         <v/>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" s="12">
-        <f>IFERROR(B25/$B$25*100,"")</f>
-        <v/>
-      </c>
-      <c r="I25" s="12">
-        <f>IFERROR(C25/$B$25*100,"")</f>
-        <v/>
-      </c>
-      <c r="J25" s="12">
-        <f>IFERROR(D25/$B$25*100,"")</f>
-        <v/>
-      </c>
-      <c r="K25" s="12">
-        <f>IFERROR(E25/$B$25*100,"")</f>
-        <v/>
-      </c>
-      <c r="L25" s="12">
-        <f>IFERROR(F25/$B$25*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Tilgodehavender hos tilknyttede virksomheder</t>
-        </is>
-      </c>
-      <c r="B26" s="5">
-        <f>'balance_raw_35663908'!$B$7</f>
-        <v/>
-      </c>
-      <c r="C26" s="5">
-        <f>'balance_raw_35663908'!$C$7</f>
-        <v/>
-      </c>
-      <c r="D26" s="5">
-        <f>'balance_raw_35663908'!$D$7</f>
-        <v/>
-      </c>
-      <c r="E26" s="5">
-        <f>'balance_raw_35663908'!$E$7</f>
-        <v/>
-      </c>
-      <c r="F26" s="5">
-        <f>'balance_raw_35663908'!$F$7</f>
-        <v/>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" s="6">
-        <f>IFERROR(B26/$B$26*100,"")</f>
-        <v/>
-      </c>
-      <c r="I26" s="6">
-        <f>IFERROR(C26/$B$26*100,"")</f>
-        <v/>
-      </c>
-      <c r="J26" s="6">
-        <f>IFERROR(D26/$B$26*100,"")</f>
-        <v/>
-      </c>
-      <c r="K26" s="6">
-        <f>IFERROR(E26/$B$26*100,"")</f>
-        <v/>
-      </c>
-      <c r="L26" s="6">
-        <f>IFERROR(F26/$B$26*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>Andre tilgodehavender</t>
-        </is>
-      </c>
-      <c r="B27" s="11">
-        <f>'balance_raw_35663908'!$B$8</f>
-        <v/>
-      </c>
-      <c r="C27" s="11">
-        <f>'balance_raw_35663908'!$C$8</f>
-        <v/>
-      </c>
-      <c r="D27" s="11">
-        <f>'balance_raw_35663908'!$D$8</f>
-        <v/>
-      </c>
-      <c r="E27" s="11">
-        <f>'balance_raw_35663908'!$E$8</f>
-        <v/>
-      </c>
-      <c r="F27" s="11">
-        <f>'balance_raw_35663908'!$F$8</f>
-        <v/>
-      </c>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" s="12">
+      <c r="H27" s="9">
         <f>IFERROR(B27/$B$27*100,"")</f>
         <v/>
       </c>
-      <c r="I27" s="12">
+      <c r="I27" s="9">
         <f>IFERROR(C27/$B$27*100,"")</f>
         <v/>
       </c>
-      <c r="J27" s="12">
+      <c r="J27" s="9">
         <f>IFERROR(D27/$B$27*100,"")</f>
         <v/>
       </c>
-      <c r="K27" s="12">
+      <c r="K27" s="9">
         <f>IFERROR(E27/$B$27*100,"")</f>
         <v/>
       </c>
-      <c r="L27" s="12">
+      <c r="L27" s="9">
         <f>IFERROR(F27/$B$27*100,"")</f>
         <v/>
       </c>
@@ -1772,27 +1806,27 @@
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Periodeafgrænsningsposter (aktiver)</t>
+          <t>Produktionsanlæg og maskiner</t>
         </is>
       </c>
       <c r="B28" s="5">
-        <f>'balance_raw_35663908'!$B$9</f>
+        <f>'balance_raw_35663908'!$B$7</f>
         <v/>
       </c>
       <c r="C28" s="5">
-        <f>'balance_raw_35663908'!$C$9</f>
+        <f>'balance_raw_35663908'!$C$7</f>
         <v/>
       </c>
       <c r="D28" s="5">
-        <f>'balance_raw_35663908'!$D$9</f>
+        <f>'balance_raw_35663908'!$D$7</f>
         <v/>
       </c>
       <c r="E28" s="5">
-        <f>'balance_raw_35663908'!$E$9</f>
+        <f>'balance_raw_35663908'!$E$7</f>
         <v/>
       </c>
       <c r="F28" s="5">
-        <f>'balance_raw_35663908'!$F$9</f>
+        <f>'balance_raw_35663908'!$F$7</f>
         <v/>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -1818,49 +1852,49 @@
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>Udskudt skatteaktiv</t>
-        </is>
-      </c>
-      <c r="B29" s="11">
-        <f>'balance_raw_35663908'!$B$10</f>
-        <v/>
-      </c>
-      <c r="C29" s="11">
-        <f>'balance_raw_35663908'!$C$10</f>
-        <v/>
-      </c>
-      <c r="D29" s="11">
-        <f>'balance_raw_35663908'!$D$10</f>
-        <v/>
-      </c>
-      <c r="E29" s="11">
-        <f>'balance_raw_35663908'!$E$10</f>
-        <v/>
-      </c>
-      <c r="F29" s="11">
-        <f>'balance_raw_35663908'!$F$10</f>
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Driftsmateriel og inventar</t>
+        </is>
+      </c>
+      <c r="B29" s="8">
+        <f>'balance_raw_35663908'!$B$8</f>
+        <v/>
+      </c>
+      <c r="C29" s="8">
+        <f>'balance_raw_35663908'!$C$8</f>
+        <v/>
+      </c>
+      <c r="D29" s="8">
+        <f>'balance_raw_35663908'!$D$8</f>
+        <v/>
+      </c>
+      <c r="E29" s="8">
+        <f>'balance_raw_35663908'!$E$8</f>
+        <v/>
+      </c>
+      <c r="F29" s="8">
+        <f>'balance_raw_35663908'!$F$8</f>
         <v/>
       </c>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" s="12">
+      <c r="H29" s="9">
         <f>IFERROR(B29/$B$29*100,"")</f>
         <v/>
       </c>
-      <c r="I29" s="12">
+      <c r="I29" s="9">
         <f>IFERROR(C29/$B$29*100,"")</f>
         <v/>
       </c>
-      <c r="J29" s="12">
+      <c r="J29" s="9">
         <f>IFERROR(D29/$B$29*100,"")</f>
         <v/>
       </c>
-      <c r="K29" s="12">
+      <c r="K29" s="9">
         <f>IFERROR(E29/$B$29*100,"")</f>
         <v/>
       </c>
-      <c r="L29" s="12">
+      <c r="L29" s="9">
         <f>IFERROR(F29/$B$29*100,"")</f>
         <v/>
       </c>
@@ -1868,27 +1902,27 @@
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
+          <t>Indretning af lejede lokaler</t>
         </is>
       </c>
       <c r="B30" s="5">
-        <f>'balance_raw_35663908'!$B$11</f>
+        <f>'balance_raw_35663908'!$B$9</f>
         <v/>
       </c>
       <c r="C30" s="5">
-        <f>'balance_raw_35663908'!$C$11</f>
+        <f>'balance_raw_35663908'!$C$9</f>
         <v/>
       </c>
       <c r="D30" s="5">
-        <f>'balance_raw_35663908'!$D$11</f>
+        <f>'balance_raw_35663908'!$D$9</f>
         <v/>
       </c>
       <c r="E30" s="5">
-        <f>'balance_raw_35663908'!$E$11</f>
+        <f>'balance_raw_35663908'!$E$9</f>
         <v/>
       </c>
       <c r="F30" s="5">
-        <f>'balance_raw_35663908'!$F$11</f>
+        <f>'balance_raw_35663908'!$F$9</f>
         <v/>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -1914,145 +1948,145 @@
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>Kortfristede skattetilgodehavender</t>
-        </is>
-      </c>
-      <c r="B31" s="11">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Forudbetaling og anlægsaktiver under opførelse</t>
+        </is>
+      </c>
+      <c r="B31" s="8">
+        <f>'balance_raw_35663908'!$B$10</f>
+        <v/>
+      </c>
+      <c r="C31" s="8">
+        <f>'balance_raw_35663908'!$C$10</f>
+        <v/>
+      </c>
+      <c r="D31" s="8">
+        <f>'balance_raw_35663908'!$D$10</f>
+        <v/>
+      </c>
+      <c r="E31" s="8">
+        <f>'balance_raw_35663908'!$E$10</f>
+        <v/>
+      </c>
+      <c r="F31" s="8">
+        <f>'balance_raw_35663908'!$F$10</f>
+        <v/>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" s="9">
+        <f>IFERROR(B31/$B$31*100,"")</f>
+        <v/>
+      </c>
+      <c r="I31" s="9">
+        <f>IFERROR(C31/$B$31*100,"")</f>
+        <v/>
+      </c>
+      <c r="J31" s="9">
+        <f>IFERROR(D31/$B$31*100,"")</f>
+        <v/>
+      </c>
+      <c r="K31" s="9">
+        <f>IFERROR(E31/$B$31*100,"")</f>
+        <v/>
+      </c>
+      <c r="L31" s="9">
+        <f>IFERROR(F31/$B$31*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>Materielle anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B32" s="11">
+        <f>'balance_raw_35663908'!$B$11</f>
+        <v/>
+      </c>
+      <c r="C32" s="11">
+        <f>'balance_raw_35663908'!$C$11</f>
+        <v/>
+      </c>
+      <c r="D32" s="11">
+        <f>'balance_raw_35663908'!$D$11</f>
+        <v/>
+      </c>
+      <c r="E32" s="11">
+        <f>'balance_raw_35663908'!$E$11</f>
+        <v/>
+      </c>
+      <c r="F32" s="11">
+        <f>'balance_raw_35663908'!$F$11</f>
+        <v/>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" s="12">
+        <f>IFERROR(B32/$B$32*100,"")</f>
+        <v/>
+      </c>
+      <c r="I32" s="12">
+        <f>IFERROR(C32/$B$32*100,"")</f>
+        <v/>
+      </c>
+      <c r="J32" s="12">
+        <f>IFERROR(D32/$B$32*100,"")</f>
+        <v/>
+      </c>
+      <c r="K32" s="12">
+        <f>IFERROR(E32/$B$32*100,"")</f>
+        <v/>
+      </c>
+      <c r="L32" s="12">
+        <f>IFERROR(F32/$B$32*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Kapitalandele, dattervirksomheder</t>
+        </is>
+      </c>
+      <c r="B33" s="8">
         <f>'balance_raw_35663908'!$B$12</f>
         <v/>
       </c>
-      <c r="C31" s="11">
+      <c r="C33" s="8">
         <f>'balance_raw_35663908'!$C$12</f>
         <v/>
       </c>
-      <c r="D31" s="11">
+      <c r="D33" s="8">
         <f>'balance_raw_35663908'!$D$12</f>
         <v/>
       </c>
-      <c r="E31" s="11">
+      <c r="E33" s="8">
         <f>'balance_raw_35663908'!$E$12</f>
         <v/>
       </c>
-      <c r="F31" s="11">
+      <c r="F33" s="8">
         <f>'balance_raw_35663908'!$F$12</f>
         <v/>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" s="12">
-        <f>IFERROR(B31/$B$31*100,"")</f>
-        <v/>
-      </c>
-      <c r="I31" s="12">
-        <f>IFERROR(C31/$B$31*100,"")</f>
-        <v/>
-      </c>
-      <c r="J31" s="12">
-        <f>IFERROR(D31/$B$31*100,"")</f>
-        <v/>
-      </c>
-      <c r="K31" s="12">
-        <f>IFERROR(E31/$B$31*100,"")</f>
-        <v/>
-      </c>
-      <c r="L31" s="12">
-        <f>IFERROR(F31/$B$31*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>Tilgodehavender</t>
-        </is>
-      </c>
-      <c r="B32" s="8">
-        <f>'balance_raw_35663908'!$B$13</f>
-        <v/>
-      </c>
-      <c r="C32" s="8">
-        <f>'balance_raw_35663908'!$C$13</f>
-        <v/>
-      </c>
-      <c r="D32" s="8">
-        <f>'balance_raw_35663908'!$D$13</f>
-        <v/>
-      </c>
-      <c r="E32" s="8">
-        <f>'balance_raw_35663908'!$E$13</f>
-        <v/>
-      </c>
-      <c r="F32" s="8">
-        <f>'balance_raw_35663908'!$F$13</f>
-        <v/>
-      </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" s="9">
-        <f>IFERROR(B32/$B$32*100,"")</f>
-        <v/>
-      </c>
-      <c r="I32" s="9">
-        <f>IFERROR(C32/$B$32*100,"")</f>
-        <v/>
-      </c>
-      <c r="J32" s="9">
-        <f>IFERROR(D32/$B$32*100,"")</f>
-        <v/>
-      </c>
-      <c r="K32" s="9">
-        <f>IFERROR(E32/$B$32*100,"")</f>
-        <v/>
-      </c>
-      <c r="L32" s="9">
-        <f>IFERROR(F32/$B$32*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>Værdipapirer</t>
-        </is>
-      </c>
-      <c r="B33" s="11">
-        <f>'balance_raw_35663908'!$B$14</f>
-        <v/>
-      </c>
-      <c r="C33" s="11">
-        <f>'balance_raw_35663908'!$C$14</f>
-        <v/>
-      </c>
-      <c r="D33" s="11">
-        <f>'balance_raw_35663908'!$D$14</f>
-        <v/>
-      </c>
-      <c r="E33" s="11">
-        <f>'balance_raw_35663908'!$E$14</f>
-        <v/>
-      </c>
-      <c r="F33" s="11">
-        <f>'balance_raw_35663908'!$F$14</f>
-        <v/>
-      </c>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" s="12">
+      <c r="H33" s="9">
         <f>IFERROR(B33/$B$33*100,"")</f>
         <v/>
       </c>
-      <c r="I33" s="12">
+      <c r="I33" s="9">
         <f>IFERROR(C33/$B$33*100,"")</f>
         <v/>
       </c>
-      <c r="J33" s="12">
+      <c r="J33" s="9">
         <f>IFERROR(D33/$B$33*100,"")</f>
         <v/>
       </c>
-      <c r="K33" s="12">
+      <c r="K33" s="9">
         <f>IFERROR(E33/$B$33*100,"")</f>
         <v/>
       </c>
-      <c r="L33" s="12">
+      <c r="L33" s="9">
         <f>IFERROR(F33/$B$33*100,"")</f>
         <v/>
       </c>
@@ -2060,27 +2094,27 @@
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Likvide beholdninger</t>
+          <t>Deposita</t>
         </is>
       </c>
       <c r="B34" s="5">
-        <f>'balance_raw_35663908'!$B$15</f>
+        <f>'balance_raw_35663908'!$B$13</f>
         <v/>
       </c>
       <c r="C34" s="5">
-        <f>'balance_raw_35663908'!$C$15</f>
+        <f>'balance_raw_35663908'!$C$13</f>
         <v/>
       </c>
       <c r="D34" s="5">
-        <f>'balance_raw_35663908'!$D$15</f>
+        <f>'balance_raw_35663908'!$D$13</f>
         <v/>
       </c>
       <c r="E34" s="5">
-        <f>'balance_raw_35663908'!$E$15</f>
+        <f>'balance_raw_35663908'!$E$13</f>
         <v/>
       </c>
       <c r="F34" s="5">
-        <f>'balance_raw_35663908'!$F$15</f>
+        <f>'balance_raw_35663908'!$F$13</f>
         <v/>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -2106,279 +2140,337 @@
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>Omsætningsaktiver</t>
-        </is>
-      </c>
-      <c r="B35" s="8">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>Finansielle anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B35" s="11">
+        <f>'balance_raw_35663908'!$B$14</f>
+        <v/>
+      </c>
+      <c r="C35" s="11">
+        <f>'balance_raw_35663908'!$C$14</f>
+        <v/>
+      </c>
+      <c r="D35" s="11">
+        <f>'balance_raw_35663908'!$D$14</f>
+        <v/>
+      </c>
+      <c r="E35" s="11">
+        <f>'balance_raw_35663908'!$E$14</f>
+        <v/>
+      </c>
+      <c r="F35" s="11">
+        <f>'balance_raw_35663908'!$F$14</f>
+        <v/>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" s="12">
+        <f>IFERROR(B35/$B$35*100,"")</f>
+        <v/>
+      </c>
+      <c r="I35" s="12">
+        <f>IFERROR(C35/$B$35*100,"")</f>
+        <v/>
+      </c>
+      <c r="J35" s="12">
+        <f>IFERROR(D35/$B$35*100,"")</f>
+        <v/>
+      </c>
+      <c r="K35" s="12">
+        <f>IFERROR(E35/$B$35*100,"")</f>
+        <v/>
+      </c>
+      <c r="L35" s="12">
+        <f>IFERROR(F35/$B$35*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>Anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B36" s="11">
+        <f>'balance_raw_35663908'!$B$15</f>
+        <v/>
+      </c>
+      <c r="C36" s="11">
+        <f>'balance_raw_35663908'!$C$15</f>
+        <v/>
+      </c>
+      <c r="D36" s="11">
+        <f>'balance_raw_35663908'!$D$15</f>
+        <v/>
+      </c>
+      <c r="E36" s="11">
+        <f>'balance_raw_35663908'!$E$15</f>
+        <v/>
+      </c>
+      <c r="F36" s="11">
+        <f>'balance_raw_35663908'!$F$15</f>
+        <v/>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" s="12">
+        <f>IFERROR(B36/$B$36*100,"")</f>
+        <v/>
+      </c>
+      <c r="I36" s="12">
+        <f>IFERROR(C36/$B$36*100,"")</f>
+        <v/>
+      </c>
+      <c r="J36" s="12">
+        <f>IFERROR(D36/$B$36*100,"")</f>
+        <v/>
+      </c>
+      <c r="K36" s="12">
+        <f>IFERROR(E36/$B$36*100,"")</f>
+        <v/>
+      </c>
+      <c r="L36" s="12">
+        <f>IFERROR(F36/$B$36*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Råvarer og hjælpematerialer</t>
+        </is>
+      </c>
+      <c r="B37" s="8">
         <f>'balance_raw_35663908'!$B$16</f>
         <v/>
       </c>
-      <c r="C35" s="8">
+      <c r="C37" s="8">
         <f>'balance_raw_35663908'!$C$16</f>
         <v/>
       </c>
-      <c r="D35" s="8">
+      <c r="D37" s="8">
         <f>'balance_raw_35663908'!$D$16</f>
         <v/>
       </c>
-      <c r="E35" s="8">
+      <c r="E37" s="8">
         <f>'balance_raw_35663908'!$E$16</f>
         <v/>
       </c>
-      <c r="F35" s="8">
+      <c r="F37" s="8">
         <f>'balance_raw_35663908'!$F$16</f>
         <v/>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" s="9">
-        <f>IFERROR(B35/$B$35*100,"")</f>
-        <v/>
-      </c>
-      <c r="I35" s="9">
-        <f>IFERROR(C35/$B$35*100,"")</f>
-        <v/>
-      </c>
-      <c r="J35" s="9">
-        <f>IFERROR(D35/$B$35*100,"")</f>
-        <v/>
-      </c>
-      <c r="K35" s="9">
-        <f>IFERROR(E35/$B$35*100,"")</f>
-        <v/>
-      </c>
-      <c r="L35" s="9">
-        <f>IFERROR(F35/$B$35*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>Aktiver</t>
-        </is>
-      </c>
-      <c r="B36" s="8">
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" s="9">
+        <f>IFERROR(B37/$B$37*100,"")</f>
+        <v/>
+      </c>
+      <c r="I37" s="9">
+        <f>IFERROR(C37/$B$37*100,"")</f>
+        <v/>
+      </c>
+      <c r="J37" s="9">
+        <f>IFERROR(D37/$B$37*100,"")</f>
+        <v/>
+      </c>
+      <c r="K37" s="9">
+        <f>IFERROR(E37/$B$37*100,"")</f>
+        <v/>
+      </c>
+      <c r="L37" s="9">
+        <f>IFERROR(F37/$B$37*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Varer under fremstilling</t>
+        </is>
+      </c>
+      <c r="B38" s="5">
         <f>'balance_raw_35663908'!$B$17</f>
         <v/>
       </c>
-      <c r="C36" s="8">
+      <c r="C38" s="5">
         <f>'balance_raw_35663908'!$C$17</f>
         <v/>
       </c>
-      <c r="D36" s="8">
+      <c r="D38" s="5">
         <f>'balance_raw_35663908'!$D$17</f>
         <v/>
       </c>
-      <c r="E36" s="8">
+      <c r="E38" s="5">
         <f>'balance_raw_35663908'!$E$17</f>
         <v/>
       </c>
-      <c r="F36" s="8">
+      <c r="F38" s="5">
         <f>'balance_raw_35663908'!$F$17</f>
         <v/>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" s="9">
-        <f>IFERROR(B36/$B$36*100,"")</f>
-        <v/>
-      </c>
-      <c r="I36" s="9">
-        <f>IFERROR(C36/$B$36*100,"")</f>
-        <v/>
-      </c>
-      <c r="J36" s="9">
-        <f>IFERROR(D36/$B$36*100,"")</f>
-        <v/>
-      </c>
-      <c r="K36" s="9">
-        <f>IFERROR(E36/$B$36*100,"")</f>
-        <v/>
-      </c>
-      <c r="L36" s="9">
-        <f>IFERROR(F36/$B$36*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>PASSIVER t.kr.</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C38" s="3" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>2024</v>
-      </c>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="I38" s="3" t="n">
-        <v>2021</v>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>2022</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>2023</v>
-      </c>
-      <c r="L38" s="3" t="n">
-        <v>2024</v>
+      <c r="H38" s="6">
+        <f>IFERROR(B38/$B$38*100,"")</f>
+        <v/>
+      </c>
+      <c r="I38" s="6">
+        <f>IFERROR(C38/$B$38*100,"")</f>
+        <v/>
+      </c>
+      <c r="J38" s="6">
+        <f>IFERROR(D38/$B$38*100,"")</f>
+        <v/>
+      </c>
+      <c r="K38" s="6">
+        <f>IFERROR(E38/$B$38*100,"")</f>
+        <v/>
+      </c>
+      <c r="L38" s="6">
+        <f>IFERROR(F38/$B$38*100,"")</f>
+        <v/>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>Selskabskapital</t>
-        </is>
-      </c>
-      <c r="B39" s="11">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Færdigvarer og handelsvarer</t>
+        </is>
+      </c>
+      <c r="B39" s="8">
         <f>'balance_raw_35663908'!$B$18</f>
         <v/>
       </c>
-      <c r="C39" s="11">
+      <c r="C39" s="8">
         <f>'balance_raw_35663908'!$C$18</f>
         <v/>
       </c>
-      <c r="D39" s="11">
+      <c r="D39" s="8">
         <f>'balance_raw_35663908'!$D$18</f>
         <v/>
       </c>
-      <c r="E39" s="11">
+      <c r="E39" s="8">
         <f>'balance_raw_35663908'!$E$18</f>
         <v/>
       </c>
-      <c r="F39" s="11">
+      <c r="F39" s="8">
         <f>'balance_raw_35663908'!$F$18</f>
         <v/>
       </c>
       <c r="G39" t="inlineStr"/>
-      <c r="H39" s="12">
+      <c r="H39" s="9">
         <f>IFERROR(B39/$B$39*100,"")</f>
         <v/>
       </c>
-      <c r="I39" s="12">
+      <c r="I39" s="9">
         <f>IFERROR(C39/$B$39*100,"")</f>
         <v/>
       </c>
-      <c r="J39" s="12">
+      <c r="J39" s="9">
         <f>IFERROR(D39/$B$39*100,"")</f>
         <v/>
       </c>
-      <c r="K39" s="12">
+      <c r="K39" s="9">
         <f>IFERROR(E39/$B$39*100,"")</f>
         <v/>
       </c>
-      <c r="L39" s="12">
+      <c r="L39" s="9">
         <f>IFERROR(F39/$B$39*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
-        </is>
-      </c>
-      <c r="B40" s="5">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>Varebeholdninger</t>
+        </is>
+      </c>
+      <c r="B40" s="11">
         <f>'balance_raw_35663908'!$B$19</f>
         <v/>
       </c>
-      <c r="C40" s="5">
+      <c r="C40" s="11">
         <f>'balance_raw_35663908'!$C$19</f>
         <v/>
       </c>
-      <c r="D40" s="5">
+      <c r="D40" s="11">
         <f>'balance_raw_35663908'!$D$19</f>
         <v/>
       </c>
-      <c r="E40" s="5">
+      <c r="E40" s="11">
         <f>'balance_raw_35663908'!$E$19</f>
         <v/>
       </c>
-      <c r="F40" s="5">
+      <c r="F40" s="11">
         <f>'balance_raw_35663908'!$F$19</f>
         <v/>
       </c>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" s="6">
+      <c r="H40" s="12">
         <f>IFERROR(B40/$B$40*100,"")</f>
         <v/>
       </c>
-      <c r="I40" s="6">
+      <c r="I40" s="12">
         <f>IFERROR(C40/$B$40*100,"")</f>
         <v/>
       </c>
-      <c r="J40" s="6">
+      <c r="J40" s="12">
         <f>IFERROR(D40/$B$40*100,"")</f>
         <v/>
       </c>
-      <c r="K40" s="6">
+      <c r="K40" s="12">
         <f>IFERROR(E40/$B$40*100,"")</f>
         <v/>
       </c>
-      <c r="L40" s="6">
+      <c r="L40" s="12">
         <f>IFERROR(F40/$B$40*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>Reserve for udviklingsomkostninger</t>
-        </is>
-      </c>
-      <c r="B41" s="11">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Tilgodehavender fra salg og tjenesteydelser</t>
+        </is>
+      </c>
+      <c r="B41" s="8">
         <f>'balance_raw_35663908'!$B$20</f>
         <v/>
       </c>
-      <c r="C41" s="11">
+      <c r="C41" s="8">
         <f>'balance_raw_35663908'!$C$20</f>
         <v/>
       </c>
-      <c r="D41" s="11">
+      <c r="D41" s="8">
         <f>'balance_raw_35663908'!$D$20</f>
         <v/>
       </c>
-      <c r="E41" s="11">
+      <c r="E41" s="8">
         <f>'balance_raw_35663908'!$E$20</f>
         <v/>
       </c>
-      <c r="F41" s="11">
+      <c r="F41" s="8">
         <f>'balance_raw_35663908'!$F$20</f>
         <v/>
       </c>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" s="12">
+      <c r="H41" s="9">
         <f>IFERROR(B41/$B$41*100,"")</f>
         <v/>
       </c>
-      <c r="I41" s="12">
+      <c r="I41" s="9">
         <f>IFERROR(C41/$B$41*100,"")</f>
         <v/>
       </c>
-      <c r="J41" s="12">
+      <c r="J41" s="9">
         <f>IFERROR(D41/$B$41*100,"")</f>
         <v/>
       </c>
-      <c r="K41" s="12">
+      <c r="K41" s="9">
         <f>IFERROR(E41/$B$41*100,"")</f>
         <v/>
       </c>
-      <c r="L41" s="12">
+      <c r="L41" s="9">
         <f>IFERROR(F41/$B$41*100,"")</f>
         <v/>
       </c>
@@ -2386,7 +2478,7 @@
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Reserve for sikringstransaktioner</t>
+          <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B42" s="5">
@@ -2432,49 +2524,49 @@
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>Andre reserver</t>
-        </is>
-      </c>
-      <c r="B43" s="11">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>Andre tilgodehavender</t>
+        </is>
+      </c>
+      <c r="B43" s="8">
         <f>'balance_raw_35663908'!$B$22</f>
         <v/>
       </c>
-      <c r="C43" s="11">
+      <c r="C43" s="8">
         <f>'balance_raw_35663908'!$C$22</f>
         <v/>
       </c>
-      <c r="D43" s="11">
+      <c r="D43" s="8">
         <f>'balance_raw_35663908'!$D$22</f>
         <v/>
       </c>
-      <c r="E43" s="11">
+      <c r="E43" s="8">
         <f>'balance_raw_35663908'!$E$22</f>
         <v/>
       </c>
-      <c r="F43" s="11">
+      <c r="F43" s="8">
         <f>'balance_raw_35663908'!$F$22</f>
         <v/>
       </c>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" s="12">
+      <c r="H43" s="9">
         <f>IFERROR(B43/$B$43*100,"")</f>
         <v/>
       </c>
-      <c r="I43" s="12">
+      <c r="I43" s="9">
         <f>IFERROR(C43/$B$43*100,"")</f>
         <v/>
       </c>
-      <c r="J43" s="12">
+      <c r="J43" s="9">
         <f>IFERROR(D43/$B$43*100,"")</f>
         <v/>
       </c>
-      <c r="K43" s="12">
+      <c r="K43" s="9">
         <f>IFERROR(E43/$B$43*100,"")</f>
         <v/>
       </c>
-      <c r="L43" s="12">
+      <c r="L43" s="9">
         <f>IFERROR(F43/$B$43*100,"")</f>
         <v/>
       </c>
@@ -2482,7 +2574,7 @@
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Overført resultat</t>
+          <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
       <c r="B44" s="5">
@@ -2530,7 +2622,7 @@
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>Egenkapital i alt</t>
+          <t>Udskudt skatteaktiv</t>
         </is>
       </c>
       <c r="B45" s="8">
@@ -2578,7 +2670,7 @@
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Hensættelse til udskudt skat</t>
+          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B46" s="5">
@@ -2626,7 +2718,7 @@
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>Hensatte forpligtelser</t>
+          <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
       <c r="B47" s="8">
@@ -2672,97 +2764,97 @@
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>Ansvarlig lånekapital (langfristet)</t>
-        </is>
-      </c>
-      <c r="B48" s="5">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>Tilgodehavender</t>
+        </is>
+      </c>
+      <c r="B48" s="11">
         <f>'balance_raw_35663908'!$B$27</f>
         <v/>
       </c>
-      <c r="C48" s="5">
+      <c r="C48" s="11">
         <f>'balance_raw_35663908'!$C$27</f>
         <v/>
       </c>
-      <c r="D48" s="5">
+      <c r="D48" s="11">
         <f>'balance_raw_35663908'!$D$27</f>
         <v/>
       </c>
-      <c r="E48" s="5">
+      <c r="E48" s="11">
         <f>'balance_raw_35663908'!$E$27</f>
         <v/>
       </c>
-      <c r="F48" s="5">
+      <c r="F48" s="11">
         <f>'balance_raw_35663908'!$F$27</f>
         <v/>
       </c>
       <c r="G48" t="inlineStr"/>
-      <c r="H48" s="6">
+      <c r="H48" s="12">
         <f>IFERROR(B48/$B$48*100,"")</f>
         <v/>
       </c>
-      <c r="I48" s="6">
+      <c r="I48" s="12">
         <f>IFERROR(C48/$B$48*100,"")</f>
         <v/>
       </c>
-      <c r="J48" s="6">
+      <c r="J48" s="12">
         <f>IFERROR(D48/$B$48*100,"")</f>
         <v/>
       </c>
-      <c r="K48" s="6">
+      <c r="K48" s="12">
         <f>IFERROR(E48/$B$48*100,"")</f>
         <v/>
       </c>
-      <c r="L48" s="6">
+      <c r="L48" s="12">
         <f>IFERROR(F48/$B$48*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>Langfristede lån</t>
-        </is>
-      </c>
-      <c r="B49" s="11">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>Værdipapirer</t>
+        </is>
+      </c>
+      <c r="B49" s="8">
         <f>'balance_raw_35663908'!$B$28</f>
         <v/>
       </c>
-      <c r="C49" s="11">
+      <c r="C49" s="8">
         <f>'balance_raw_35663908'!$C$28</f>
         <v/>
       </c>
-      <c r="D49" s="11">
+      <c r="D49" s="8">
         <f>'balance_raw_35663908'!$D$28</f>
         <v/>
       </c>
-      <c r="E49" s="11">
+      <c r="E49" s="8">
         <f>'balance_raw_35663908'!$E$28</f>
         <v/>
       </c>
-      <c r="F49" s="11">
+      <c r="F49" s="8">
         <f>'balance_raw_35663908'!$F$28</f>
         <v/>
       </c>
       <c r="G49" t="inlineStr"/>
-      <c r="H49" s="12">
+      <c r="H49" s="9">
         <f>IFERROR(B49/$B$49*100,"")</f>
         <v/>
       </c>
-      <c r="I49" s="12">
+      <c r="I49" s="9">
         <f>IFERROR(C49/$B$49*100,"")</f>
         <v/>
       </c>
-      <c r="J49" s="12">
+      <c r="J49" s="9">
         <f>IFERROR(D49/$B$49*100,"")</f>
         <v/>
       </c>
-      <c r="K49" s="12">
+      <c r="K49" s="9">
         <f>IFERROR(E49/$B$49*100,"")</f>
         <v/>
       </c>
-      <c r="L49" s="12">
+      <c r="L49" s="9">
         <f>IFERROR(F49/$B$49*100,"")</f>
         <v/>
       </c>
@@ -2770,7 +2862,7 @@
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Leasingforpligtelser (langfristet)</t>
+          <t>Likvide beholdninger</t>
         </is>
       </c>
       <c r="B50" s="5">
@@ -2818,7 +2910,7 @@
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>Anden gæld (langfristet)</t>
+          <t>Omsætningsaktiver</t>
         </is>
       </c>
       <c r="B51" s="11">
@@ -2864,193 +2956,135 @@
       </c>
     </row>
     <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>Langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B52" s="8">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>Aktiver</t>
+        </is>
+      </c>
+      <c r="B52" s="11">
         <f>'balance_raw_35663908'!$B$31</f>
         <v/>
       </c>
-      <c r="C52" s="8">
+      <c r="C52" s="11">
         <f>'balance_raw_35663908'!$C$31</f>
         <v/>
       </c>
-      <c r="D52" s="8">
+      <c r="D52" s="11">
         <f>'balance_raw_35663908'!$D$31</f>
         <v/>
       </c>
-      <c r="E52" s="8">
+      <c r="E52" s="11">
         <f>'balance_raw_35663908'!$E$31</f>
         <v/>
       </c>
-      <c r="F52" s="8">
+      <c r="F52" s="11">
         <f>'balance_raw_35663908'!$F$31</f>
         <v/>
       </c>
       <c r="G52" t="inlineStr"/>
-      <c r="H52" s="9">
+      <c r="H52" s="12">
         <f>IFERROR(B52/$B$52*100,"")</f>
         <v/>
       </c>
-      <c r="I52" s="9">
+      <c r="I52" s="12">
         <f>IFERROR(C52/$B$52*100,"")</f>
         <v/>
       </c>
-      <c r="J52" s="9">
+      <c r="J52" s="12">
         <f>IFERROR(D52/$B$52*100,"")</f>
         <v/>
       </c>
-      <c r="K52" s="9">
+      <c r="K52" s="12">
         <f>IFERROR(E52/$B$52*100,"")</f>
         <v/>
       </c>
-      <c r="L52" s="9">
+      <c r="L52" s="12">
         <f>IFERROR(F52/$B$52*100,"")</f>
         <v/>
       </c>
     </row>
-    <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>Ansvarlig lånekapital (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B53" s="11">
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>PASSIVER t.kr.</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J54" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>Selskabskapital</t>
+        </is>
+      </c>
+      <c r="B55" s="8">
         <f>'balance_raw_35663908'!$B$32</f>
         <v/>
       </c>
-      <c r="C53" s="11">
+      <c r="C55" s="8">
         <f>'balance_raw_35663908'!$C$32</f>
         <v/>
       </c>
-      <c r="D53" s="11">
+      <c r="D55" s="8">
         <f>'balance_raw_35663908'!$D$32</f>
         <v/>
       </c>
-      <c r="E53" s="11">
+      <c r="E55" s="8">
         <f>'balance_raw_35663908'!$E$32</f>
         <v/>
       </c>
-      <c r="F53" s="11">
+      <c r="F55" s="8">
         <f>'balance_raw_35663908'!$F$32</f>
         <v/>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" s="12">
-        <f>IFERROR(B53/$B$53*100,"")</f>
-        <v/>
-      </c>
-      <c r="I53" s="12">
-        <f>IFERROR(C53/$B$53*100,"")</f>
-        <v/>
-      </c>
-      <c r="J53" s="12">
-        <f>IFERROR(D53/$B$53*100,"")</f>
-        <v/>
-      </c>
-      <c r="K53" s="12">
-        <f>IFERROR(E53/$B$53*100,"")</f>
-        <v/>
-      </c>
-      <c r="L53" s="12">
-        <f>IFERROR(F53/$B$53*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>Kortfristet del af langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B54" s="5">
-        <f>'balance_raw_35663908'!$B$33</f>
-        <v/>
-      </c>
-      <c r="C54" s="5">
-        <f>'balance_raw_35663908'!$C$33</f>
-        <v/>
-      </c>
-      <c r="D54" s="5">
-        <f>'balance_raw_35663908'!$D$33</f>
-        <v/>
-      </c>
-      <c r="E54" s="5">
-        <f>'balance_raw_35663908'!$E$33</f>
-        <v/>
-      </c>
-      <c r="F54" s="5">
-        <f>'balance_raw_35663908'!$F$33</f>
-        <v/>
-      </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" s="6">
-        <f>IFERROR(B54/$B$54*100,"")</f>
-        <v/>
-      </c>
-      <c r="I54" s="6">
-        <f>IFERROR(C54/$B$54*100,"")</f>
-        <v/>
-      </c>
-      <c r="J54" s="6">
-        <f>IFERROR(D54/$B$54*100,"")</f>
-        <v/>
-      </c>
-      <c r="K54" s="6">
-        <f>IFERROR(E54/$B$54*100,"")</f>
-        <v/>
-      </c>
-      <c r="L54" s="6">
-        <f>IFERROR(F54/$B$54*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="10" t="inlineStr">
-        <is>
-          <t>Kreditinstitutter</t>
-        </is>
-      </c>
-      <c r="B55" s="11">
-        <f>'balance_raw_35663908'!$B$34</f>
-        <v/>
-      </c>
-      <c r="C55" s="11">
-        <f>'balance_raw_35663908'!$C$34</f>
-        <v/>
-      </c>
-      <c r="D55" s="11">
-        <f>'balance_raw_35663908'!$D$34</f>
-        <v/>
-      </c>
-      <c r="E55" s="11">
-        <f>'balance_raw_35663908'!$E$34</f>
-        <v/>
-      </c>
-      <c r="F55" s="11">
-        <f>'balance_raw_35663908'!$F$34</f>
-        <v/>
-      </c>
       <c r="G55" t="inlineStr"/>
-      <c r="H55" s="12">
+      <c r="H55" s="9">
         <f>IFERROR(B55/$B$55*100,"")</f>
         <v/>
       </c>
-      <c r="I55" s="12">
+      <c r="I55" s="9">
         <f>IFERROR(C55/$B$55*100,"")</f>
         <v/>
       </c>
-      <c r="J55" s="12">
+      <c r="J55" s="9">
         <f>IFERROR(D55/$B$55*100,"")</f>
         <v/>
       </c>
-      <c r="K55" s="12">
+      <c r="K55" s="9">
         <f>IFERROR(E55/$B$55*100,"")</f>
         <v/>
       </c>
-      <c r="L55" s="12">
+      <c r="L55" s="9">
         <f>IFERROR(F55/$B$55*100,"")</f>
         <v/>
       </c>
@@ -3058,27 +3092,27 @@
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Leasingforpligtelser (kortfristet)</t>
+          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
       <c r="B56" s="5">
-        <f>'balance_raw_35663908'!$B$35</f>
+        <f>'balance_raw_35663908'!$B$33</f>
         <v/>
       </c>
       <c r="C56" s="5">
-        <f>'balance_raw_35663908'!$C$35</f>
+        <f>'balance_raw_35663908'!$C$33</f>
         <v/>
       </c>
       <c r="D56" s="5">
-        <f>'balance_raw_35663908'!$D$35</f>
+        <f>'balance_raw_35663908'!$D$33</f>
         <v/>
       </c>
       <c r="E56" s="5">
-        <f>'balance_raw_35663908'!$E$35</f>
+        <f>'balance_raw_35663908'!$E$33</f>
         <v/>
       </c>
       <c r="F56" s="5">
-        <f>'balance_raw_35663908'!$F$35</f>
+        <f>'balance_raw_35663908'!$F$33</f>
         <v/>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -3104,49 +3138,49 @@
       </c>
     </row>
     <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="10" t="inlineStr">
-        <is>
-          <t>Leverandører af varer og tjenesteydelser</t>
-        </is>
-      </c>
-      <c r="B57" s="11">
-        <f>'balance_raw_35663908'!$B$36</f>
-        <v/>
-      </c>
-      <c r="C57" s="11">
-        <f>'balance_raw_35663908'!$C$36</f>
-        <v/>
-      </c>
-      <c r="D57" s="11">
-        <f>'balance_raw_35663908'!$D$36</f>
-        <v/>
-      </c>
-      <c r="E57" s="11">
-        <f>'balance_raw_35663908'!$E$36</f>
-        <v/>
-      </c>
-      <c r="F57" s="11">
-        <f>'balance_raw_35663908'!$F$36</f>
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>Reserve for udviklingsomkostninger</t>
+        </is>
+      </c>
+      <c r="B57" s="8">
+        <f>'balance_raw_35663908'!$B$34</f>
+        <v/>
+      </c>
+      <c r="C57" s="8">
+        <f>'balance_raw_35663908'!$C$34</f>
+        <v/>
+      </c>
+      <c r="D57" s="8">
+        <f>'balance_raw_35663908'!$D$34</f>
+        <v/>
+      </c>
+      <c r="E57" s="8">
+        <f>'balance_raw_35663908'!$E$34</f>
+        <v/>
+      </c>
+      <c r="F57" s="8">
+        <f>'balance_raw_35663908'!$F$34</f>
         <v/>
       </c>
       <c r="G57" t="inlineStr"/>
-      <c r="H57" s="12">
+      <c r="H57" s="9">
         <f>IFERROR(B57/$B$57*100,"")</f>
         <v/>
       </c>
-      <c r="I57" s="12">
+      <c r="I57" s="9">
         <f>IFERROR(C57/$B$57*100,"")</f>
         <v/>
       </c>
-      <c r="J57" s="12">
+      <c r="J57" s="9">
         <f>IFERROR(D57/$B$57*100,"")</f>
         <v/>
       </c>
-      <c r="K57" s="12">
+      <c r="K57" s="9">
         <f>IFERROR(E57/$B$57*100,"")</f>
         <v/>
       </c>
-      <c r="L57" s="12">
+      <c r="L57" s="9">
         <f>IFERROR(F57/$B$57*100,"")</f>
         <v/>
       </c>
@@ -3154,27 +3188,27 @@
     <row r="58" ht="16" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder</t>
+          <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
       <c r="B58" s="5">
-        <f>'balance_raw_35663908'!$B$37</f>
+        <f>'balance_raw_35663908'!$B$35</f>
         <v/>
       </c>
       <c r="C58" s="5">
-        <f>'balance_raw_35663908'!$C$37</f>
+        <f>'balance_raw_35663908'!$C$35</f>
         <v/>
       </c>
       <c r="D58" s="5">
-        <f>'balance_raw_35663908'!$D$37</f>
+        <f>'balance_raw_35663908'!$D$35</f>
         <v/>
       </c>
       <c r="E58" s="5">
-        <f>'balance_raw_35663908'!$E$37</f>
+        <f>'balance_raw_35663908'!$E$35</f>
         <v/>
       </c>
       <c r="F58" s="5">
-        <f>'balance_raw_35663908'!$F$37</f>
+        <f>'balance_raw_35663908'!$F$35</f>
         <v/>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -3200,49 +3234,49 @@
       </c>
     </row>
     <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="10" t="inlineStr">
-        <is>
-          <t>Gæld til selskabsdeltagere og ledelse</t>
-        </is>
-      </c>
-      <c r="B59" s="11">
-        <f>'balance_raw_35663908'!$B$38</f>
-        <v/>
-      </c>
-      <c r="C59" s="11">
-        <f>'balance_raw_35663908'!$C$38</f>
-        <v/>
-      </c>
-      <c r="D59" s="11">
-        <f>'balance_raw_35663908'!$D$38</f>
-        <v/>
-      </c>
-      <c r="E59" s="11">
-        <f>'balance_raw_35663908'!$E$38</f>
-        <v/>
-      </c>
-      <c r="F59" s="11">
-        <f>'balance_raw_35663908'!$F$38</f>
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>Andre reserver</t>
+        </is>
+      </c>
+      <c r="B59" s="8">
+        <f>'balance_raw_35663908'!$B$36</f>
+        <v/>
+      </c>
+      <c r="C59" s="8">
+        <f>'balance_raw_35663908'!$C$36</f>
+        <v/>
+      </c>
+      <c r="D59" s="8">
+        <f>'balance_raw_35663908'!$D$36</f>
+        <v/>
+      </c>
+      <c r="E59" s="8">
+        <f>'balance_raw_35663908'!$E$36</f>
+        <v/>
+      </c>
+      <c r="F59" s="8">
+        <f>'balance_raw_35663908'!$F$36</f>
         <v/>
       </c>
       <c r="G59" t="inlineStr"/>
-      <c r="H59" s="12">
+      <c r="H59" s="9">
         <f>IFERROR(B59/$B$59*100,"")</f>
         <v/>
       </c>
-      <c r="I59" s="12">
+      <c r="I59" s="9">
         <f>IFERROR(C59/$B$59*100,"")</f>
         <v/>
       </c>
-      <c r="J59" s="12">
+      <c r="J59" s="9">
         <f>IFERROR(D59/$B$59*100,"")</f>
         <v/>
       </c>
-      <c r="K59" s="12">
+      <c r="K59" s="9">
         <f>IFERROR(E59/$B$59*100,"")</f>
         <v/>
       </c>
-      <c r="L59" s="12">
+      <c r="L59" s="9">
         <f>IFERROR(F59/$B$59*100,"")</f>
         <v/>
       </c>
@@ -3250,27 +3284,27 @@
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Selskabsskat</t>
+          <t>Overført resultat</t>
         </is>
       </c>
       <c r="B60" s="5">
-        <f>'balance_raw_35663908'!$B$39</f>
+        <f>'balance_raw_35663908'!$B$37</f>
         <v/>
       </c>
       <c r="C60" s="5">
-        <f>'balance_raw_35663908'!$C$39</f>
+        <f>'balance_raw_35663908'!$C$37</f>
         <v/>
       </c>
       <c r="D60" s="5">
-        <f>'balance_raw_35663908'!$D$39</f>
+        <f>'balance_raw_35663908'!$D$37</f>
         <v/>
       </c>
       <c r="E60" s="5">
-        <f>'balance_raw_35663908'!$E$39</f>
+        <f>'balance_raw_35663908'!$E$37</f>
         <v/>
       </c>
       <c r="F60" s="5">
-        <f>'balance_raw_35663908'!$F$39</f>
+        <f>'balance_raw_35663908'!$F$37</f>
         <v/>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -3298,27 +3332,27 @@
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
+          <t>Egenkapital i alt</t>
         </is>
       </c>
       <c r="B61" s="11">
-        <f>'balance_raw_35663908'!$B$40</f>
+        <f>'balance_raw_35663908'!$B$38</f>
         <v/>
       </c>
       <c r="C61" s="11">
-        <f>'balance_raw_35663908'!$C$40</f>
+        <f>'balance_raw_35663908'!$C$38</f>
         <v/>
       </c>
       <c r="D61" s="11">
-        <f>'balance_raw_35663908'!$D$40</f>
+        <f>'balance_raw_35663908'!$D$38</f>
         <v/>
       </c>
       <c r="E61" s="11">
-        <f>'balance_raw_35663908'!$E$40</f>
+        <f>'balance_raw_35663908'!$E$38</f>
         <v/>
       </c>
       <c r="F61" s="11">
-        <f>'balance_raw_35663908'!$F$40</f>
+        <f>'balance_raw_35663908'!$F$38</f>
         <v/>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -3346,27 +3380,27 @@
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Anden gæld (kortfristet)</t>
+          <t>Hensættelse til udskudt skat</t>
         </is>
       </c>
       <c r="B62" s="5">
-        <f>'balance_raw_35663908'!$B$41</f>
+        <f>'balance_raw_35663908'!$B$39</f>
         <v/>
       </c>
       <c r="C62" s="5">
-        <f>'balance_raw_35663908'!$C$41</f>
+        <f>'balance_raw_35663908'!$C$39</f>
         <v/>
       </c>
       <c r="D62" s="5">
-        <f>'balance_raw_35663908'!$D$41</f>
+        <f>'balance_raw_35663908'!$D$39</f>
         <v/>
       </c>
       <c r="E62" s="5">
-        <f>'balance_raw_35663908'!$E$41</f>
+        <f>'balance_raw_35663908'!$E$39</f>
         <v/>
       </c>
       <c r="F62" s="5">
-        <f>'balance_raw_35663908'!$F$41</f>
+        <f>'balance_raw_35663908'!$F$39</f>
         <v/>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -3394,27 +3428,27 @@
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>Periodeafgrænsningsposter (passiver)</t>
+          <t>Hensatte forpligtelser</t>
         </is>
       </c>
       <c r="B63" s="11">
-        <f>'balance_raw_35663908'!$B$42</f>
+        <f>'balance_raw_35663908'!$B$40</f>
         <v/>
       </c>
       <c r="C63" s="11">
-        <f>'balance_raw_35663908'!$C$42</f>
+        <f>'balance_raw_35663908'!$C$40</f>
         <v/>
       </c>
       <c r="D63" s="11">
-        <f>'balance_raw_35663908'!$D$42</f>
+        <f>'balance_raw_35663908'!$D$40</f>
         <v/>
       </c>
       <c r="E63" s="11">
-        <f>'balance_raw_35663908'!$E$42</f>
+        <f>'balance_raw_35663908'!$E$40</f>
         <v/>
       </c>
       <c r="F63" s="11">
-        <f>'balance_raw_35663908'!$F$42</f>
+        <f>'balance_raw_35663908'!$F$40</f>
         <v/>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -3440,49 +3474,49 @@
       </c>
     </row>
     <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="7" t="inlineStr">
-        <is>
-          <t>Kortfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B64" s="8">
-        <f>'balance_raw_35663908'!$B$43</f>
-        <v/>
-      </c>
-      <c r="C64" s="8">
-        <f>'balance_raw_35663908'!$C$43</f>
-        <v/>
-      </c>
-      <c r="D64" s="8">
-        <f>'balance_raw_35663908'!$D$43</f>
-        <v/>
-      </c>
-      <c r="E64" s="8">
-        <f>'balance_raw_35663908'!$E$43</f>
-        <v/>
-      </c>
-      <c r="F64" s="8">
-        <f>'balance_raw_35663908'!$F$43</f>
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>Ansvarlig lånekapital (langfristet)</t>
+        </is>
+      </c>
+      <c r="B64" s="5">
+        <f>'balance_raw_35663908'!$B$41</f>
+        <v/>
+      </c>
+      <c r="C64" s="5">
+        <f>'balance_raw_35663908'!$C$41</f>
+        <v/>
+      </c>
+      <c r="D64" s="5">
+        <f>'balance_raw_35663908'!$D$41</f>
+        <v/>
+      </c>
+      <c r="E64" s="5">
+        <f>'balance_raw_35663908'!$E$41</f>
+        <v/>
+      </c>
+      <c r="F64" s="5">
+        <f>'balance_raw_35663908'!$F$41</f>
         <v/>
       </c>
       <c r="G64" t="inlineStr"/>
-      <c r="H64" s="9">
+      <c r="H64" s="6">
         <f>IFERROR(B64/$B$64*100,"")</f>
         <v/>
       </c>
-      <c r="I64" s="9">
+      <c r="I64" s="6">
         <f>IFERROR(C64/$B$64*100,"")</f>
         <v/>
       </c>
-      <c r="J64" s="9">
+      <c r="J64" s="6">
         <f>IFERROR(D64/$B$64*100,"")</f>
         <v/>
       </c>
-      <c r="K64" s="9">
+      <c r="K64" s="6">
         <f>IFERROR(E64/$B$64*100,"")</f>
         <v/>
       </c>
-      <c r="L64" s="9">
+      <c r="L64" s="6">
         <f>IFERROR(F64/$B$64*100,"")</f>
         <v/>
       </c>
@@ -3490,27 +3524,27 @@
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>Gældsforpligtelser</t>
+          <t>Langfristede lån</t>
         </is>
       </c>
       <c r="B65" s="8">
-        <f>'balance_raw_35663908'!$B$44</f>
+        <f>'balance_raw_35663908'!$B$42</f>
         <v/>
       </c>
       <c r="C65" s="8">
-        <f>'balance_raw_35663908'!$C$44</f>
+        <f>'balance_raw_35663908'!$C$42</f>
         <v/>
       </c>
       <c r="D65" s="8">
-        <f>'balance_raw_35663908'!$D$44</f>
+        <f>'balance_raw_35663908'!$D$42</f>
         <v/>
       </c>
       <c r="E65" s="8">
-        <f>'balance_raw_35663908'!$E$44</f>
+        <f>'balance_raw_35663908'!$E$42</f>
         <v/>
       </c>
       <c r="F65" s="8">
-        <f>'balance_raw_35663908'!$F$44</f>
+        <f>'balance_raw_35663908'!$F$42</f>
         <v/>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -3536,119 +3570,193 @@
       </c>
     </row>
     <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="7" t="inlineStr">
-        <is>
-          <t>Passiver</t>
-        </is>
-      </c>
-      <c r="B66" s="8">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Leasingforpligtelser (langfristet)</t>
+        </is>
+      </c>
+      <c r="B66" s="5">
+        <f>'balance_raw_35663908'!$B$43</f>
+        <v/>
+      </c>
+      <c r="C66" s="5">
+        <f>'balance_raw_35663908'!$C$43</f>
+        <v/>
+      </c>
+      <c r="D66" s="5">
+        <f>'balance_raw_35663908'!$D$43</f>
+        <v/>
+      </c>
+      <c r="E66" s="5">
+        <f>'balance_raw_35663908'!$E$43</f>
+        <v/>
+      </c>
+      <c r="F66" s="5">
+        <f>'balance_raw_35663908'!$F$43</f>
+        <v/>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" s="6">
+        <f>IFERROR(B66/$B$66*100,"")</f>
+        <v/>
+      </c>
+      <c r="I66" s="6">
+        <f>IFERROR(C66/$B$66*100,"")</f>
+        <v/>
+      </c>
+      <c r="J66" s="6">
+        <f>IFERROR(D66/$B$66*100,"")</f>
+        <v/>
+      </c>
+      <c r="K66" s="6">
+        <f>IFERROR(E66/$B$66*100,"")</f>
+        <v/>
+      </c>
+      <c r="L66" s="6">
+        <f>IFERROR(F66/$B$66*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>Anden gæld (langfristet)</t>
+        </is>
+      </c>
+      <c r="B67" s="8">
+        <f>'balance_raw_35663908'!$B$44</f>
+        <v/>
+      </c>
+      <c r="C67" s="8">
+        <f>'balance_raw_35663908'!$C$44</f>
+        <v/>
+      </c>
+      <c r="D67" s="8">
+        <f>'balance_raw_35663908'!$D$44</f>
+        <v/>
+      </c>
+      <c r="E67" s="8">
+        <f>'balance_raw_35663908'!$E$44</f>
+        <v/>
+      </c>
+      <c r="F67" s="8">
+        <f>'balance_raw_35663908'!$F$44</f>
+        <v/>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" s="9">
+        <f>IFERROR(B67/$B$67*100,"")</f>
+        <v/>
+      </c>
+      <c r="I67" s="9">
+        <f>IFERROR(C67/$B$67*100,"")</f>
+        <v/>
+      </c>
+      <c r="J67" s="9">
+        <f>IFERROR(D67/$B$67*100,"")</f>
+        <v/>
+      </c>
+      <c r="K67" s="9">
+        <f>IFERROR(E67/$B$67*100,"")</f>
+        <v/>
+      </c>
+      <c r="L67" s="9">
+        <f>IFERROR(F67/$B$67*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>Langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B68" s="11">
         <f>'balance_raw_35663908'!$B$45</f>
         <v/>
       </c>
-      <c r="C66" s="8">
+      <c r="C68" s="11">
         <f>'balance_raw_35663908'!$C$45</f>
         <v/>
       </c>
-      <c r="D66" s="8">
+      <c r="D68" s="11">
         <f>'balance_raw_35663908'!$D$45</f>
         <v/>
       </c>
-      <c r="E66" s="8">
+      <c r="E68" s="11">
         <f>'balance_raw_35663908'!$E$45</f>
         <v/>
       </c>
-      <c r="F66" s="8">
+      <c r="F68" s="11">
         <f>'balance_raw_35663908'!$F$45</f>
         <v/>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" s="9">
-        <f>IFERROR(B66/$B$66*100,"")</f>
-        <v/>
-      </c>
-      <c r="I66" s="9">
-        <f>IFERROR(C66/$B$66*100,"")</f>
-        <v/>
-      </c>
-      <c r="J66" s="9">
-        <f>IFERROR(D66/$B$66*100,"")</f>
-        <v/>
-      </c>
-      <c r="K66" s="9">
-        <f>IFERROR(E66/$B$66*100,"")</f>
-        <v/>
-      </c>
-      <c r="L66" s="9">
-        <f>IFERROR(F66/$B$66*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68" ht="22" customHeight="1">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>NØGLEOPLYSNINGER</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C68" s="3" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D68" s="3" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F68" s="3" t="n">
-        <v>2024</v>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" s="12">
+        <f>IFERROR(B68/$B$68*100,"")</f>
+        <v/>
+      </c>
+      <c r="I68" s="12">
+        <f>IFERROR(C68/$B$68*100,"")</f>
+        <v/>
+      </c>
+      <c r="J68" s="12">
+        <f>IFERROR(D68/$B$68*100,"")</f>
+        <v/>
+      </c>
+      <c r="K68" s="12">
+        <f>IFERROR(E68/$B$68*100,"")</f>
+        <v/>
+      </c>
+      <c r="L68" s="12">
+        <f>IFERROR(F68/$B$68*100,"")</f>
+        <v/>
       </c>
     </row>
     <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="10" t="inlineStr">
-        <is>
-          <t>Gns. antal medarbejdere</t>
-        </is>
-      </c>
-      <c r="B69" s="11">
-        <f>'res_raw_35663908'!$B$17</f>
-        <v/>
-      </c>
-      <c r="C69" s="11">
-        <f>'res_raw_35663908'!$C$17</f>
-        <v/>
-      </c>
-      <c r="D69" s="11">
-        <f>'res_raw_35663908'!$D$17</f>
-        <v/>
-      </c>
-      <c r="E69" s="11">
-        <f>'res_raw_35663908'!$E$17</f>
-        <v/>
-      </c>
-      <c r="F69" s="11">
-        <f>'res_raw_35663908'!$F$17</f>
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>Ansvarlig lånekapital (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B69" s="8">
+        <f>'balance_raw_35663908'!$B$46</f>
+        <v/>
+      </c>
+      <c r="C69" s="8">
+        <f>'balance_raw_35663908'!$C$46</f>
+        <v/>
+      </c>
+      <c r="D69" s="8">
+        <f>'balance_raw_35663908'!$D$46</f>
+        <v/>
+      </c>
+      <c r="E69" s="8">
+        <f>'balance_raw_35663908'!$E$46</f>
+        <v/>
+      </c>
+      <c r="F69" s="8">
+        <f>'balance_raw_35663908'!$F$46</f>
         <v/>
       </c>
       <c r="G69" t="inlineStr"/>
-      <c r="H69" s="12">
+      <c r="H69" s="9">
         <f>IFERROR(B69/$B$69*100,"")</f>
         <v/>
       </c>
-      <c r="I69" s="12">
+      <c r="I69" s="9">
         <f>IFERROR(C69/$B$69*100,"")</f>
         <v/>
       </c>
-      <c r="J69" s="12">
+      <c r="J69" s="9">
         <f>IFERROR(D69/$B$69*100,"")</f>
         <v/>
       </c>
-      <c r="K69" s="12">
+      <c r="K69" s="9">
         <f>IFERROR(E69/$B$69*100,"")</f>
         <v/>
       </c>
-      <c r="L69" s="12">
+      <c r="L69" s="9">
         <f>IFERROR(F69/$B$69*100,"")</f>
         <v/>
       </c>
@@ -3656,27 +3764,27 @@
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Investering i materielle anlægsaktiver</t>
+          <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
       <c r="B70" s="5">
-        <f>'res_raw_35663908'!$B$18</f>
+        <f>'balance_raw_35663908'!$B$47</f>
         <v/>
       </c>
       <c r="C70" s="5">
-        <f>'res_raw_35663908'!$C$18</f>
+        <f>'balance_raw_35663908'!$C$47</f>
         <v/>
       </c>
       <c r="D70" s="5">
-        <f>'res_raw_35663908'!$D$18</f>
+        <f>'balance_raw_35663908'!$D$47</f>
         <v/>
       </c>
       <c r="E70" s="5">
-        <f>'res_raw_35663908'!$E$18</f>
+        <f>'balance_raw_35663908'!$E$47</f>
         <v/>
       </c>
       <c r="F70" s="5">
-        <f>'res_raw_35663908'!$F$18</f>
+        <f>'balance_raw_35663908'!$F$47</f>
         <v/>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -3701,322 +3809,1158 @@
         <v/>
       </c>
     </row>
-    <row r="72" ht="22" customHeight="1">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>NØGLETAL</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C72" s="3" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D72" s="3" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E72" s="3" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F72" s="3" t="n">
-        <v>2024</v>
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>Kreditinstitutter</t>
+        </is>
+      </c>
+      <c r="B71" s="8">
+        <f>'balance_raw_35663908'!$B$48</f>
+        <v/>
+      </c>
+      <c r="C71" s="8">
+        <f>'balance_raw_35663908'!$C$48</f>
+        <v/>
+      </c>
+      <c r="D71" s="8">
+        <f>'balance_raw_35663908'!$D$48</f>
+        <v/>
+      </c>
+      <c r="E71" s="8">
+        <f>'balance_raw_35663908'!$E$48</f>
+        <v/>
+      </c>
+      <c r="F71" s="8">
+        <f>'balance_raw_35663908'!$F$48</f>
+        <v/>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" s="9">
+        <f>IFERROR(B71/$B$71*100,"")</f>
+        <v/>
+      </c>
+      <c r="I71" s="9">
+        <f>IFERROR(C71/$B$71*100,"")</f>
+        <v/>
+      </c>
+      <c r="J71" s="9">
+        <f>IFERROR(D71/$B$71*100,"")</f>
+        <v/>
+      </c>
+      <c r="K71" s="9">
+        <f>IFERROR(E71/$B$71*100,"")</f>
+        <v/>
+      </c>
+      <c r="L71" s="9">
+        <f>IFERROR(F71/$B$71*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>Leasingforpligtelser (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B72" s="5">
+        <f>'balance_raw_35663908'!$B$49</f>
+        <v/>
+      </c>
+      <c r="C72" s="5">
+        <f>'balance_raw_35663908'!$C$49</f>
+        <v/>
+      </c>
+      <c r="D72" s="5">
+        <f>'balance_raw_35663908'!$D$49</f>
+        <v/>
+      </c>
+      <c r="E72" s="5">
+        <f>'balance_raw_35663908'!$E$49</f>
+        <v/>
+      </c>
+      <c r="F72" s="5">
+        <f>'balance_raw_35663908'!$F$49</f>
+        <v/>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" s="6">
+        <f>IFERROR(B72/$B$72*100,"")</f>
+        <v/>
+      </c>
+      <c r="I72" s="6">
+        <f>IFERROR(C72/$B$72*100,"")</f>
+        <v/>
+      </c>
+      <c r="J72" s="6">
+        <f>IFERROR(D72/$B$72*100,"")</f>
+        <v/>
+      </c>
+      <c r="K72" s="6">
+        <f>IFERROR(E72/$B$72*100,"")</f>
+        <v/>
+      </c>
+      <c r="L72" s="6">
+        <f>IFERROR(F72/$B$72*100,"")</f>
+        <v/>
       </c>
     </row>
     <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="10" t="inlineStr">
-        <is>
-          <t>Afkastningsgrad, %</t>
-        </is>
-      </c>
-      <c r="B73" s="13">
-        <f>IFERROR(($B$11+$B$13+$B$12)/$B$36*100,"")</f>
-        <v/>
-      </c>
-      <c r="C73" s="13">
-        <f>IFERROR(($C$11+$C$13+$C$12)/$C$36*100,"")</f>
-        <v/>
-      </c>
-      <c r="D73" s="13">
-        <f>IFERROR(($D$11+$D$13+$D$12)/$D$36*100,"")</f>
-        <v/>
-      </c>
-      <c r="E73" s="13">
-        <f>IFERROR(($E$11+$E$13+$E$12)/$E$36*100,"")</f>
-        <v/>
-      </c>
-      <c r="F73" s="13">
-        <f>IFERROR(($F$11+$F$13+$F$12)/$F$36*100,"")</f>
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>Leverandører af varer og tjenesteydelser</t>
+        </is>
+      </c>
+      <c r="B73" s="8">
+        <f>'balance_raw_35663908'!$B$50</f>
+        <v/>
+      </c>
+      <c r="C73" s="8">
+        <f>'balance_raw_35663908'!$C$50</f>
+        <v/>
+      </c>
+      <c r="D73" s="8">
+        <f>'balance_raw_35663908'!$D$50</f>
+        <v/>
+      </c>
+      <c r="E73" s="8">
+        <f>'balance_raw_35663908'!$E$50</f>
+        <v/>
+      </c>
+      <c r="F73" s="8">
+        <f>'balance_raw_35663908'!$F$50</f>
+        <v/>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" s="9">
+        <f>IFERROR(B73/$B$73*100,"")</f>
+        <v/>
+      </c>
+      <c r="I73" s="9">
+        <f>IFERROR(C73/$B$73*100,"")</f>
+        <v/>
+      </c>
+      <c r="J73" s="9">
+        <f>IFERROR(D73/$B$73*100,"")</f>
+        <v/>
+      </c>
+      <c r="K73" s="9">
+        <f>IFERROR(E73/$B$73*100,"")</f>
+        <v/>
+      </c>
+      <c r="L73" s="9">
+        <f>IFERROR(F73/$B$73*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="74" ht="16" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Overskudsgrad, %</t>
-        </is>
-      </c>
-      <c r="B74" s="14">
-        <f>IFERROR(($B$11+$B$13+$B$12)/$B$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="C74" s="14">
-        <f>IFERROR(($C$11+$C$13+$C$12)/$C$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="D74" s="14">
-        <f>IFERROR(($D$11+$D$13+$D$12)/$D$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="E74" s="14">
-        <f>IFERROR(($E$11+$E$13+$E$12)/$E$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="F74" s="14">
-        <f>IFERROR(($F$11+$F$13+$F$12)/$F$4*100,"")</f>
+          <t>Gæld til tilknyttede virksomheder</t>
+        </is>
+      </c>
+      <c r="B74" s="5">
+        <f>'balance_raw_35663908'!$B$51</f>
+        <v/>
+      </c>
+      <c r="C74" s="5">
+        <f>'balance_raw_35663908'!$C$51</f>
+        <v/>
+      </c>
+      <c r="D74" s="5">
+        <f>'balance_raw_35663908'!$D$51</f>
+        <v/>
+      </c>
+      <c r="E74" s="5">
+        <f>'balance_raw_35663908'!$E$51</f>
+        <v/>
+      </c>
+      <c r="F74" s="5">
+        <f>'balance_raw_35663908'!$F$51</f>
+        <v/>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" s="6">
+        <f>IFERROR(B74/$B$74*100,"")</f>
+        <v/>
+      </c>
+      <c r="I74" s="6">
+        <f>IFERROR(C74/$B$74*100,"")</f>
+        <v/>
+      </c>
+      <c r="J74" s="6">
+        <f>IFERROR(D74/$B$74*100,"")</f>
+        <v/>
+      </c>
+      <c r="K74" s="6">
+        <f>IFERROR(E74/$B$74*100,"")</f>
+        <v/>
+      </c>
+      <c r="L74" s="6">
+        <f>IFERROR(F74/$B$74*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="10" t="inlineStr">
-        <is>
-          <t>Aktivernes omsætningshastighed, gange</t>
-        </is>
-      </c>
-      <c r="B75" s="13">
-        <f>IFERROR($B$4/$B$36,"")</f>
-        <v/>
-      </c>
-      <c r="C75" s="13">
-        <f>IFERROR($C$4/$C$36,"")</f>
-        <v/>
-      </c>
-      <c r="D75" s="13">
-        <f>IFERROR($D$4/$D$36,"")</f>
-        <v/>
-      </c>
-      <c r="E75" s="13">
-        <f>IFERROR($E$4/$E$36,"")</f>
-        <v/>
-      </c>
-      <c r="F75" s="13">
-        <f>IFERROR($F$4/$F$36,"")</f>
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>Gæld til selskabsdeltagere og ledelse</t>
+        </is>
+      </c>
+      <c r="B75" s="8">
+        <f>'balance_raw_35663908'!$B$52</f>
+        <v/>
+      </c>
+      <c r="C75" s="8">
+        <f>'balance_raw_35663908'!$C$52</f>
+        <v/>
+      </c>
+      <c r="D75" s="8">
+        <f>'balance_raw_35663908'!$D$52</f>
+        <v/>
+      </c>
+      <c r="E75" s="8">
+        <f>'balance_raw_35663908'!$E$52</f>
+        <v/>
+      </c>
+      <c r="F75" s="8">
+        <f>'balance_raw_35663908'!$F$52</f>
+        <v/>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" s="9">
+        <f>IFERROR(B75/$B$75*100,"")</f>
+        <v/>
+      </c>
+      <c r="I75" s="9">
+        <f>IFERROR(C75/$B$75*100,"")</f>
+        <v/>
+      </c>
+      <c r="J75" s="9">
+        <f>IFERROR(D75/$B$75*100,"")</f>
+        <v/>
+      </c>
+      <c r="K75" s="9">
+        <f>IFERROR(E75/$B$75*100,"")</f>
+        <v/>
+      </c>
+      <c r="L75" s="9">
+        <f>IFERROR(F75/$B$75*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="16" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Egenkapitalens forrentning, %</t>
-        </is>
-      </c>
-      <c r="B76" s="14">
-        <f>IFERROR($B$16/$B$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="C76" s="14">
-        <f>IFERROR($C$16/$C$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="D76" s="14">
-        <f>IFERROR($D$16/$D$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="E76" s="14">
-        <f>IFERROR($E$16/$E$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="F76" s="14">
-        <f>IFERROR($F$16/$F$45*100,"")</f>
+          <t>Selskabsskat</t>
+        </is>
+      </c>
+      <c r="B76" s="5">
+        <f>'balance_raw_35663908'!$B$53</f>
+        <v/>
+      </c>
+      <c r="C76" s="5">
+        <f>'balance_raw_35663908'!$C$53</f>
+        <v/>
+      </c>
+      <c r="D76" s="5">
+        <f>'balance_raw_35663908'!$D$53</f>
+        <v/>
+      </c>
+      <c r="E76" s="5">
+        <f>'balance_raw_35663908'!$E$53</f>
+        <v/>
+      </c>
+      <c r="F76" s="5">
+        <f>'balance_raw_35663908'!$F$53</f>
+        <v/>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" s="6">
+        <f>IFERROR(B76/$B$76*100,"")</f>
+        <v/>
+      </c>
+      <c r="I76" s="6">
+        <f>IFERROR(C76/$B$76*100,"")</f>
+        <v/>
+      </c>
+      <c r="J76" s="6">
+        <f>IFERROR(D76/$B$76*100,"")</f>
+        <v/>
+      </c>
+      <c r="K76" s="6">
+        <f>IFERROR(E76/$B$76*100,"")</f>
+        <v/>
+      </c>
+      <c r="L76" s="6">
+        <f>IFERROR(F76/$B$76*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="10" t="inlineStr">
-        <is>
-          <t>Gældsrente, %</t>
-        </is>
-      </c>
-      <c r="B77" s="13">
-        <f>IFERROR($B$14/($B$66-$B$45)*100,"")</f>
-        <v/>
-      </c>
-      <c r="C77" s="13">
-        <f>IFERROR($C$14/($C$66-$C$45)*100,"")</f>
-        <v/>
-      </c>
-      <c r="D77" s="13">
-        <f>IFERROR($D$14/($D$66-$D$45)*100,"")</f>
-        <v/>
-      </c>
-      <c r="E77" s="13">
-        <f>IFERROR($E$14/($E$66-$E$45)*100,"")</f>
-        <v/>
-      </c>
-      <c r="F77" s="13">
-        <f>IFERROR($F$14/($F$66-$F$45)*100,"")</f>
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
+        </is>
+      </c>
+      <c r="B77" s="8">
+        <f>'balance_raw_35663908'!$B$54</f>
+        <v/>
+      </c>
+      <c r="C77" s="8">
+        <f>'balance_raw_35663908'!$C$54</f>
+        <v/>
+      </c>
+      <c r="D77" s="8">
+        <f>'balance_raw_35663908'!$D$54</f>
+        <v/>
+      </c>
+      <c r="E77" s="8">
+        <f>'balance_raw_35663908'!$E$54</f>
+        <v/>
+      </c>
+      <c r="F77" s="8">
+        <f>'balance_raw_35663908'!$F$54</f>
+        <v/>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" s="9">
+        <f>IFERROR(B77/$B$77*100,"")</f>
+        <v/>
+      </c>
+      <c r="I77" s="9">
+        <f>IFERROR(C77/$B$77*100,"")</f>
+        <v/>
+      </c>
+      <c r="J77" s="9">
+        <f>IFERROR(D77/$B$77*100,"")</f>
+        <v/>
+      </c>
+      <c r="K77" s="9">
+        <f>IFERROR(E77/$B$77*100,"")</f>
+        <v/>
+      </c>
+      <c r="L77" s="9">
+        <f>IFERROR(F77/$B$77*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="78" ht="16" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>Soliditetsgrad, %</t>
-        </is>
-      </c>
-      <c r="B78" s="14">
-        <f>IFERROR($B$45/$B$36*100,"")</f>
-        <v/>
-      </c>
-      <c r="C78" s="14">
-        <f>IFERROR($C$45/$C$36*100,"")</f>
-        <v/>
-      </c>
-      <c r="D78" s="14">
-        <f>IFERROR($D$45/$D$36*100,"")</f>
-        <v/>
-      </c>
-      <c r="E78" s="14">
-        <f>IFERROR($E$45/$E$36*100,"")</f>
-        <v/>
-      </c>
-      <c r="F78" s="14">
-        <f>IFERROR($F$45/$F$36*100,"")</f>
+          <t>Anden gæld (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B78" s="5">
+        <f>'balance_raw_35663908'!$B$55</f>
+        <v/>
+      </c>
+      <c r="C78" s="5">
+        <f>'balance_raw_35663908'!$C$55</f>
+        <v/>
+      </c>
+      <c r="D78" s="5">
+        <f>'balance_raw_35663908'!$D$55</f>
+        <v/>
+      </c>
+      <c r="E78" s="5">
+        <f>'balance_raw_35663908'!$E$55</f>
+        <v/>
+      </c>
+      <c r="F78" s="5">
+        <f>'balance_raw_35663908'!$F$55</f>
+        <v/>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" s="6">
+        <f>IFERROR(B78/$B$78*100,"")</f>
+        <v/>
+      </c>
+      <c r="I78" s="6">
+        <f>IFERROR(C78/$B$78*100,"")</f>
+        <v/>
+      </c>
+      <c r="J78" s="6">
+        <f>IFERROR(D78/$B$78*100,"")</f>
+        <v/>
+      </c>
+      <c r="K78" s="6">
+        <f>IFERROR(E78/$B$78*100,"")</f>
+        <v/>
+      </c>
+      <c r="L78" s="6">
+        <f>IFERROR(F78/$B$78*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="10" t="inlineStr">
-        <is>
-          <t>Gearing</t>
-        </is>
-      </c>
-      <c r="B79" s="13">
-        <f>IFERROR(($B$66-$B$45)/$B$45,"")</f>
-        <v/>
-      </c>
-      <c r="C79" s="13">
-        <f>IFERROR(($C$66-$C$45)/$C$45,"")</f>
-        <v/>
-      </c>
-      <c r="D79" s="13">
-        <f>IFERROR(($D$66-$D$45)/$D$45,"")</f>
-        <v/>
-      </c>
-      <c r="E79" s="13">
-        <f>IFERROR(($E$66-$E$45)/$E$45,"")</f>
-        <v/>
-      </c>
-      <c r="F79" s="13">
-        <f>IFERROR(($F$66-$F$45)/$F$45,"")</f>
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>Periodeafgrænsningsposter (passiver)</t>
+        </is>
+      </c>
+      <c r="B79" s="8">
+        <f>'balance_raw_35663908'!$B$56</f>
+        <v/>
+      </c>
+      <c r="C79" s="8">
+        <f>'balance_raw_35663908'!$C$56</f>
+        <v/>
+      </c>
+      <c r="D79" s="8">
+        <f>'balance_raw_35663908'!$D$56</f>
+        <v/>
+      </c>
+      <c r="E79" s="8">
+        <f>'balance_raw_35663908'!$E$56</f>
+        <v/>
+      </c>
+      <c r="F79" s="8">
+        <f>'balance_raw_35663908'!$F$56</f>
+        <v/>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" s="9">
+        <f>IFERROR(B79/$B$79*100,"")</f>
+        <v/>
+      </c>
+      <c r="I79" s="9">
+        <f>IFERROR(C79/$B$79*100,"")</f>
+        <v/>
+      </c>
+      <c r="J79" s="9">
+        <f>IFERROR(D79/$B$79*100,"")</f>
+        <v/>
+      </c>
+      <c r="K79" s="9">
+        <f>IFERROR(E79/$B$79*100,"")</f>
+        <v/>
+      </c>
+      <c r="L79" s="9">
+        <f>IFERROR(F79/$B$79*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>Likviditetsgrad, %</t>
-        </is>
-      </c>
-      <c r="B80" s="14">
-        <f>IFERROR($B$35/$B$64*100,"")</f>
-        <v/>
-      </c>
-      <c r="C80" s="14">
-        <f>IFERROR($C$35/$C$64*100,"")</f>
-        <v/>
-      </c>
-      <c r="D80" s="14">
-        <f>IFERROR($D$35/$D$64*100,"")</f>
-        <v/>
-      </c>
-      <c r="E80" s="14">
-        <f>IFERROR($E$35/$E$64*100,"")</f>
-        <v/>
-      </c>
-      <c r="F80" s="14">
-        <f>IFERROR($F$35/$F$64*100,"")</f>
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>Kortfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B80" s="11">
+        <f>'balance_raw_35663908'!$B$57</f>
+        <v/>
+      </c>
+      <c r="C80" s="11">
+        <f>'balance_raw_35663908'!$C$57</f>
+        <v/>
+      </c>
+      <c r="D80" s="11">
+        <f>'balance_raw_35663908'!$D$57</f>
+        <v/>
+      </c>
+      <c r="E80" s="11">
+        <f>'balance_raw_35663908'!$E$57</f>
+        <v/>
+      </c>
+      <c r="F80" s="11">
+        <f>'balance_raw_35663908'!$F$57</f>
+        <v/>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" s="12">
+        <f>IFERROR(B80/$B$80*100,"")</f>
+        <v/>
+      </c>
+      <c r="I80" s="12">
+        <f>IFERROR(C80/$B$80*100,"")</f>
+        <v/>
+      </c>
+      <c r="J80" s="12">
+        <f>IFERROR(D80/$B$80*100,"")</f>
+        <v/>
+      </c>
+      <c r="K80" s="12">
+        <f>IFERROR(E80/$B$80*100,"")</f>
+        <v/>
+      </c>
+      <c r="L80" s="12">
+        <f>IFERROR(F80/$B$80*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1">
       <c r="A81" s="10" t="inlineStr">
         <is>
+          <t>Gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B81" s="11">
+        <f>'balance_raw_35663908'!$B$58</f>
+        <v/>
+      </c>
+      <c r="C81" s="11">
+        <f>'balance_raw_35663908'!$C$58</f>
+        <v/>
+      </c>
+      <c r="D81" s="11">
+        <f>'balance_raw_35663908'!$D$58</f>
+        <v/>
+      </c>
+      <c r="E81" s="11">
+        <f>'balance_raw_35663908'!$E$58</f>
+        <v/>
+      </c>
+      <c r="F81" s="11">
+        <f>'balance_raw_35663908'!$F$58</f>
+        <v/>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" s="12">
+        <f>IFERROR(B81/$B$81*100,"")</f>
+        <v/>
+      </c>
+      <c r="I81" s="12">
+        <f>IFERROR(C81/$B$81*100,"")</f>
+        <v/>
+      </c>
+      <c r="J81" s="12">
+        <f>IFERROR(D81/$B$81*100,"")</f>
+        <v/>
+      </c>
+      <c r="K81" s="12">
+        <f>IFERROR(E81/$B$81*100,"")</f>
+        <v/>
+      </c>
+      <c r="L81" s="12">
+        <f>IFERROR(F81/$B$81*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" ht="16" customHeight="1">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>Passiver</t>
+        </is>
+      </c>
+      <c r="B82" s="11">
+        <f>'balance_raw_35663908'!$B$59</f>
+        <v/>
+      </c>
+      <c r="C82" s="11">
+        <f>'balance_raw_35663908'!$C$59</f>
+        <v/>
+      </c>
+      <c r="D82" s="11">
+        <f>'balance_raw_35663908'!$D$59</f>
+        <v/>
+      </c>
+      <c r="E82" s="11">
+        <f>'balance_raw_35663908'!$E$59</f>
+        <v/>
+      </c>
+      <c r="F82" s="11">
+        <f>'balance_raw_35663908'!$F$59</f>
+        <v/>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" s="12">
+        <f>IFERROR(B82/$B$82*100,"")</f>
+        <v/>
+      </c>
+      <c r="I82" s="12">
+        <f>IFERROR(C82/$B$82*100,"")</f>
+        <v/>
+      </c>
+      <c r="J82" s="12">
+        <f>IFERROR(D82/$B$82*100,"")</f>
+        <v/>
+      </c>
+      <c r="K82" s="12">
+        <f>IFERROR(E82/$B$82*100,"")</f>
+        <v/>
+      </c>
+      <c r="L82" s="12">
+        <f>IFERROR(F82/$B$82*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>NØGLEOPLYSNINGER</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="85" ht="16" customHeight="1">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>Gns. antal medarbejdere</t>
+        </is>
+      </c>
+      <c r="B85" s="8">
+        <f>'res_raw_35663908'!$B$19</f>
+        <v/>
+      </c>
+      <c r="C85" s="8">
+        <f>'res_raw_35663908'!$C$19</f>
+        <v/>
+      </c>
+      <c r="D85" s="8">
+        <f>'res_raw_35663908'!$D$19</f>
+        <v/>
+      </c>
+      <c r="E85" s="8">
+        <f>'res_raw_35663908'!$E$19</f>
+        <v/>
+      </c>
+      <c r="F85" s="8">
+        <f>'res_raw_35663908'!$F$19</f>
+        <v/>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" s="9">
+        <f>IFERROR(B85/$B$85*100,"")</f>
+        <v/>
+      </c>
+      <c r="I85" s="9">
+        <f>IFERROR(C85/$B$85*100,"")</f>
+        <v/>
+      </c>
+      <c r="J85" s="9">
+        <f>IFERROR(D85/$B$85*100,"")</f>
+        <v/>
+      </c>
+      <c r="K85" s="9">
+        <f>IFERROR(E85/$B$85*100,"")</f>
+        <v/>
+      </c>
+      <c r="L85" s="9">
+        <f>IFERROR(F85/$B$85*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" ht="16" customHeight="1">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>Investering i materielle anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B86" s="5">
+        <f>'res_raw_35663908'!$B$20</f>
+        <v/>
+      </c>
+      <c r="C86" s="5">
+        <f>'res_raw_35663908'!$C$20</f>
+        <v/>
+      </c>
+      <c r="D86" s="5">
+        <f>'res_raw_35663908'!$D$20</f>
+        <v/>
+      </c>
+      <c r="E86" s="5">
+        <f>'res_raw_35663908'!$E$20</f>
+        <v/>
+      </c>
+      <c r="F86" s="5">
+        <f>'res_raw_35663908'!$F$20</f>
+        <v/>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" s="6">
+        <f>IFERROR(B86/$B$86*100,"")</f>
+        <v/>
+      </c>
+      <c r="I86" s="6">
+        <f>IFERROR(C86/$B$86*100,"")</f>
+        <v/>
+      </c>
+      <c r="J86" s="6">
+        <f>IFERROR(D86/$B$86*100,"")</f>
+        <v/>
+      </c>
+      <c r="K86" s="6">
+        <f>IFERROR(E86/$B$86*100,"")</f>
+        <v/>
+      </c>
+      <c r="L86" s="6">
+        <f>IFERROR(F86/$B$86*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" ht="22" customHeight="1">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>NØGLETAL</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="89" ht="16" customHeight="1">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>Afkastningsgrad, %</t>
+        </is>
+      </c>
+      <c r="B89" s="13">
+        <f>IFERROR(($B$13+$B$15+$B$14)/$B$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="C89" s="13">
+        <f>IFERROR(($C$13+$C$15+$C$14)/$C$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="D89" s="13">
+        <f>IFERROR(($D$13+$D$15+$D$14)/$D$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="E89" s="13">
+        <f>IFERROR(($E$13+$E$15+$E$14)/$E$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="F89" s="13">
+        <f>IFERROR(($F$13+$F$15+$F$14)/$F$52*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>Overskudsgrad, %</t>
+        </is>
+      </c>
+      <c r="B90" s="14">
+        <f>IFERROR(($B$13+$B$15+$B$14)/$B$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="C90" s="14">
+        <f>IFERROR(($C$13+$C$15+$C$14)/$C$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="D90" s="14">
+        <f>IFERROR(($D$13+$D$15+$D$14)/$D$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="E90" s="14">
+        <f>IFERROR(($E$13+$E$15+$E$14)/$E$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="F90" s="14">
+        <f>IFERROR(($F$13+$F$15+$F$14)/$F$4*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" ht="16" customHeight="1">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>Aktivernes omsætningshastighed, gange</t>
+        </is>
+      </c>
+      <c r="B91" s="13">
+        <f>IFERROR($B$4/$B$52,"")</f>
+        <v/>
+      </c>
+      <c r="C91" s="13">
+        <f>IFERROR($C$4/$C$52,"")</f>
+        <v/>
+      </c>
+      <c r="D91" s="13">
+        <f>IFERROR($D$4/$D$52,"")</f>
+        <v/>
+      </c>
+      <c r="E91" s="13">
+        <f>IFERROR($E$4/$E$52,"")</f>
+        <v/>
+      </c>
+      <c r="F91" s="13">
+        <f>IFERROR($F$4/$F$52,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" ht="16" customHeight="1">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>Egenkapitalens forrentning, %</t>
+        </is>
+      </c>
+      <c r="B92" s="14">
+        <f>IFERROR($B$18/$B$61*100,"")</f>
+        <v/>
+      </c>
+      <c r="C92" s="14">
+        <f>IFERROR($C$18/$C$61*100,"")</f>
+        <v/>
+      </c>
+      <c r="D92" s="14">
+        <f>IFERROR($D$18/$D$61*100,"")</f>
+        <v/>
+      </c>
+      <c r="E92" s="14">
+        <f>IFERROR($E$18/$E$61*100,"")</f>
+        <v/>
+      </c>
+      <c r="F92" s="14">
+        <f>IFERROR($F$18/$F$61*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" ht="16" customHeight="1">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>Gældsrente, %</t>
+        </is>
+      </c>
+      <c r="B93" s="13">
+        <f>IFERROR($B$16/($B$82-$B$61)*100,"")</f>
+        <v/>
+      </c>
+      <c r="C93" s="13">
+        <f>IFERROR($C$16/($C$82-$C$61)*100,"")</f>
+        <v/>
+      </c>
+      <c r="D93" s="13">
+        <f>IFERROR($D$16/($D$82-$D$61)*100,"")</f>
+        <v/>
+      </c>
+      <c r="E93" s="13">
+        <f>IFERROR($E$16/($E$82-$E$61)*100,"")</f>
+        <v/>
+      </c>
+      <c r="F93" s="13">
+        <f>IFERROR($F$16/($F$82-$F$61)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" ht="16" customHeight="1">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>Soliditetsgrad, %</t>
+        </is>
+      </c>
+      <c r="B94" s="14">
+        <f>IFERROR($B$61/$B$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="C94" s="14">
+        <f>IFERROR($C$61/$C$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="D94" s="14">
+        <f>IFERROR($D$61/$D$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="E94" s="14">
+        <f>IFERROR($E$61/$E$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="F94" s="14">
+        <f>IFERROR($F$61/$F$52*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" ht="16" customHeight="1">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>Gearing</t>
+        </is>
+      </c>
+      <c r="B95" s="13">
+        <f>IFERROR(($B$82-$B$61)/$B$61,"")</f>
+        <v/>
+      </c>
+      <c r="C95" s="13">
+        <f>IFERROR(($C$82-$C$61)/$C$61,"")</f>
+        <v/>
+      </c>
+      <c r="D95" s="13">
+        <f>IFERROR(($D$82-$D$61)/$D$61,"")</f>
+        <v/>
+      </c>
+      <c r="E95" s="13">
+        <f>IFERROR(($E$82-$E$61)/$E$61,"")</f>
+        <v/>
+      </c>
+      <c r="F95" s="13">
+        <f>IFERROR(($F$82-$F$61)/$F$61,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96" ht="16" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>Likviditetsgrad, %</t>
+        </is>
+      </c>
+      <c r="B96" s="14">
+        <f>IFERROR($B$51/$B$80*100,"")</f>
+        <v/>
+      </c>
+      <c r="C96" s="14">
+        <f>IFERROR($C$51/$C$80*100,"")</f>
+        <v/>
+      </c>
+      <c r="D96" s="14">
+        <f>IFERROR($D$51/$D$80*100,"")</f>
+        <v/>
+      </c>
+      <c r="E96" s="14">
+        <f>IFERROR($E$51/$E$80*100,"")</f>
+        <v/>
+      </c>
+      <c r="F96" s="14">
+        <f>IFERROR($F$51/$F$80*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97" ht="16" customHeight="1">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
           <t>Rentemarginal, %</t>
         </is>
       </c>
-      <c r="B81" s="13">
-        <f>IFERROR(B73-B77,"")</f>
-        <v/>
-      </c>
-      <c r="C81" s="13">
-        <f>IFERROR(C73-C77,"")</f>
-        <v/>
-      </c>
-      <c r="D81" s="13">
-        <f>IFERROR(D73-D77,"")</f>
-        <v/>
-      </c>
-      <c r="E81" s="13">
-        <f>IFERROR(E73-E77,"")</f>
-        <v/>
-      </c>
-      <c r="F81" s="13">
-        <f>IFERROR(F73-F77,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82" ht="16" customHeight="1">
-      <c r="A82" s="4" t="inlineStr">
+      <c r="B97" s="13">
+        <f>IFERROR(B89-B93,"")</f>
+        <v/>
+      </c>
+      <c r="C97" s="13">
+        <f>IFERROR(C89-C93,"")</f>
+        <v/>
+      </c>
+      <c r="D97" s="13">
+        <f>IFERROR(D89-D93,"")</f>
+        <v/>
+      </c>
+      <c r="E97" s="13">
+        <f>IFERROR(E89-E93,"")</f>
+        <v/>
+      </c>
+      <c r="F97" s="13">
+        <f>IFERROR(F89-F93,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98" ht="16" customHeight="1">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t>Gældsandel, %</t>
         </is>
       </c>
-      <c r="B82" s="14">
-        <f>IFERROR(($B$66-$B$45)/$B$36*100,"")</f>
-        <v/>
-      </c>
-      <c r="C82" s="14">
-        <f>IFERROR(($C$66-$C$45)/$C$36*100,"")</f>
-        <v/>
-      </c>
-      <c r="D82" s="14">
-        <f>IFERROR(($D$66-$D$45)/$D$36*100,"")</f>
-        <v/>
-      </c>
-      <c r="E82" s="14">
-        <f>IFERROR(($E$66-$E$45)/$E$36*100,"")</f>
-        <v/>
-      </c>
-      <c r="F82" s="14">
-        <f>IFERROR(($F$66-$F$45)/$F$36*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83" ht="16" customHeight="1">
-      <c r="A83" s="10" t="inlineStr">
+      <c r="B98" s="14">
+        <f>IFERROR(($B$82-$B$61)/$B$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="C98" s="14">
+        <f>IFERROR(($C$82-$C$61)/$C$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="D98" s="14">
+        <f>IFERROR(($D$82-$D$61)/$D$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="E98" s="14">
+        <f>IFERROR(($E$82-$E$61)/$E$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="F98" s="14">
+        <f>IFERROR(($F$82-$F$61)/$F$52*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99" ht="16" customHeight="1">
+      <c r="A99" s="7" t="inlineStr">
         <is>
           <t>Kapitalbindingsgrad, %</t>
         </is>
       </c>
-      <c r="B83" s="13">
-        <f>IFERROR($B$23/($B$45+$B$52)*100,"")</f>
-        <v/>
-      </c>
-      <c r="C83" s="13">
-        <f>IFERROR($C$23/($C$45+$C$52)*100,"")</f>
-        <v/>
-      </c>
-      <c r="D83" s="13">
-        <f>IFERROR($D$23/($D$45+$D$52)*100,"")</f>
-        <v/>
-      </c>
-      <c r="E83" s="13">
-        <f>IFERROR($E$23/($E$45+$E$52)*100,"")</f>
-        <v/>
-      </c>
-      <c r="F83" s="13">
-        <f>IFERROR($F$23/($F$45+$F$52)*100,"")</f>
+      <c r="B99" s="13">
+        <f>IFERROR($B$36/($B$61+$B$68)*100,"")</f>
+        <v/>
+      </c>
+      <c r="C99" s="13">
+        <f>IFERROR($C$36/($C$61+$C$68)*100,"")</f>
+        <v/>
+      </c>
+      <c r="D99" s="13">
+        <f>IFERROR($D$36/($D$61+$D$68)*100,"")</f>
+        <v/>
+      </c>
+      <c r="E99" s="13">
+        <f>IFERROR($E$36/($E$61+$E$68)*100,"")</f>
+        <v/>
+      </c>
+      <c r="F99" s="13">
+        <f>IFERROR($F$36/($F$61+$F$68)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE t.kr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B102" s="17">
+        <f>'pengestrom_raw_35663908'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C102" s="17">
+        <f>'pengestrom_raw_35663908'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D102" s="17">
+        <f>'pengestrom_raw_35663908'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E102" s="17">
+        <f>'pengestrom_raw_35663908'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F102" s="17">
+        <f>'pengestrom_raw_35663908'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B103" s="17">
+        <f>'pengestrom_raw_35663908'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C103" s="17">
+        <f>'pengestrom_raw_35663908'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D103" s="17">
+        <f>'pengestrom_raw_35663908'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E103" s="17">
+        <f>'pengestrom_raw_35663908'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F103" s="17">
+        <f>'pengestrom_raw_35663908'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B104" s="17">
+        <f>'pengestrom_raw_35663908'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C104" s="17">
+        <f>'pengestrom_raw_35663908'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D104" s="17">
+        <f>'pengestrom_raw_35663908'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E104" s="17">
+        <f>'pengestrom_raw_35663908'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F104" s="17">
+        <f>'pengestrom_raw_35663908'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B105" s="17">
+        <f>'pengestrom_raw_35663908'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C105" s="17">
+        <f>'pengestrom_raw_35663908'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D105" s="17">
+        <f>'pengestrom_raw_35663908'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E105" s="17">
+        <f>'pengestrom_raw_35663908'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F105" s="17">
+        <f>'pengestrom_raw_35663908'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B106">
+        <f>IF(ABS(('pengestrom_raw_35663908'!$B$2+'pengestrom_raw_35663908'!$B$3+'pengestrom_raw_35663908'!$B$4)-'pengestrom_raw_35663908'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_35663908'!$B$2+'pengestrom_raw_35663908'!$B$3+'pengestrom_raw_35663908'!$B$4)-'pengestrom_raw_35663908'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C106">
+        <f>IF(ABS(('pengestrom_raw_35663908'!$C$2+'pengestrom_raw_35663908'!$C$3+'pengestrom_raw_35663908'!$C$4)-'pengestrom_raw_35663908'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_35663908'!$C$2+'pengestrom_raw_35663908'!$C$3+'pengestrom_raw_35663908'!$C$4)-'pengestrom_raw_35663908'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D106">
+        <f>IF(ABS(('pengestrom_raw_35663908'!$D$2+'pengestrom_raw_35663908'!$D$3+'pengestrom_raw_35663908'!$D$4)-'pengestrom_raw_35663908'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_35663908'!$D$2+'pengestrom_raw_35663908'!$D$3+'pengestrom_raw_35663908'!$D$4)-'pengestrom_raw_35663908'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E106">
+        <f>IF(ABS(('pengestrom_raw_35663908'!$E$2+'pengestrom_raw_35663908'!$E$3+'pengestrom_raw_35663908'!$E$4)-'pengestrom_raw_35663908'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_35663908'!$E$2+'pengestrom_raw_35663908'!$E$3+'pengestrom_raw_35663908'!$E$4)-'pengestrom_raw_35663908'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F106">
+        <f>IF(ABS(('pengestrom_raw_35663908'!$F$2+'pengestrom_raw_35663908'!$F$3+'pengestrom_raw_35663908'!$F$4)-'pengestrom_raw_35663908'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_35663908'!$F$2+'pengestrom_raw_35663908'!$F$3+'pengestrom_raw_35663908'!$F$4)-'pengestrom_raw_35663908'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4031,7 +4975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -4049,334 +4993,355 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
-        <v>1983400</v>
-      </c>
-      <c r="C2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>2381500</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>3128500</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>3377900</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>3455600</v>
       </c>
+      <c r="F2" s="17" t="n">
+        <v>3822200</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>Produktionsomkostninger</t>
-        </is>
-      </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n">
-        <v>1288700</v>
-      </c>
-      <c r="D3" s="16" t="n">
-        <v>1733800</v>
-      </c>
-      <c r="E3" s="16" t="n">
-        <v>1810800</v>
-      </c>
-      <c r="F3" s="16" t="n">
-        <v>1796800</v>
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Andre driftsindtægter</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n">
+        <v>16500</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>23600</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>20600</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>28800</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>Bruttoresultat</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="n">
-        <v>882200</v>
-      </c>
-      <c r="C4" s="16" t="n">
-        <v>1047600</v>
-      </c>
-      <c r="D4" s="16" t="n">
-        <v>1339700</v>
-      </c>
-      <c r="E4" s="16" t="n">
-        <v>1518200</v>
-      </c>
-      <c r="F4" s="16" t="n">
-        <v>1600800</v>
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Vareforbrug</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="17" t="n">
+        <v>1859900</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>2101400</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>Salgs- og distributionsomkostninger</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="n"/>
-      <c r="C5" s="16" t="n"/>
-      <c r="D5" s="16" t="n"/>
-      <c r="E5" s="16" t="n"/>
-      <c r="F5" s="16" t="n"/>
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Andre eksterne omkostninger</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>Administrationsomkostninger</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="16" t="n"/>
-      <c r="F6" s="16" t="n"/>
+          <t>Bruttoresultat</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n">
+        <v>1047600</v>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>1339700</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>1518200</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>1595700</v>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>1720800</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>Andre driftsindtægter</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n">
-        <v>16500</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>23600</v>
-      </c>
-      <c r="F7" s="16" t="n"/>
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Personaleomkostninger</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n">
+        <v>881400</v>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>1025400</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
+          <t>Resultat før afskrivninger</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Af- og nedskrivninger</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="16" t="n"/>
-      <c r="E8" s="16" t="n"/>
-      <c r="F8" s="16" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>Resultat af primær drift</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="n">
-        <v>298300</v>
-      </c>
-      <c r="C9" s="16" t="n">
-        <v>378200</v>
-      </c>
-      <c r="D9" s="16" t="n">
-        <v>498300</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>621400</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>576900</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>Indtægter af kapitalandele, dattervirksomheder</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
+          <t>Resultat af primær drift</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n">
+        <v>378200</v>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>498300</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>621400</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>490800</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>522000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Indtægter af kapitalandele, dattervirksomheder</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>23400</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>29800</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>101800</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>25500</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>20600</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="F13" s="17" t="n">
+        <v>42600</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
-        <v>38000</v>
-      </c>
-      <c r="C12" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>34100</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>37200</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>48800</v>
       </c>
-      <c r="F12" s="16" t="n">
-        <v>62500</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>Finansielle poster, netto</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>Resultat før skat</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n">
-        <v>283700</v>
-      </c>
-      <c r="C14" s="16" t="n">
-        <v>355900</v>
-      </c>
-      <c r="D14" s="16" t="n">
-        <v>562900</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>598100</v>
-      </c>
-      <c r="F14" s="16" t="n">
-        <v>535000</v>
+      <c r="E14" s="17" t="n">
+        <v>55900</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>47300</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
+          <t>Finansielle poster, netto</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Resultat før skat</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="n">
+        <v>355900</v>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>562900</v>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>598100</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>455500</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>517300</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
-        <v>59300</v>
-      </c>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="16" t="n">
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n">
         <v>115400</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>133700</v>
       </c>
-      <c r="F15" s="16" t="n">
-        <v>116000</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>Årets resultat</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="n">
-        <v>224400</v>
-      </c>
-      <c r="C16" s="16" t="n">
-        <v>279200</v>
-      </c>
-      <c r="D16" s="16" t="n">
-        <v>447500</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>464400</v>
-      </c>
-      <c r="F16" s="16" t="n">
-        <v>419000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>Gns. antal medarbejdere</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="n">
-        <v>1419</v>
-      </c>
-      <c r="C17" s="16" t="n">
-        <v>1488</v>
-      </c>
-      <c r="D17" s="16" t="n">
-        <v>1811</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>1886</v>
+      <c r="E17" s="17" t="n">
+        <v>116200</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>130000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
+          <t>Årets resultat</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n">
+        <v>279200</v>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>447500</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>464400</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>339300</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>387300</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>Gns. antal medarbejdere</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n">
+        <v>1488</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>1811</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>1886</v>
+      </c>
+      <c r="F19" s="17" t="n">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
-        <v>14200</v>
-      </c>
-      <c r="C18" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>19900</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="C20" s="17" t="n">
         <v>39900</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="D20" s="17" t="n">
         <v>59600</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="E20" s="17" t="n">
         <v>102600</v>
       </c>
+      <c r="F20" s="17" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4389,7 +5354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -4407,781 +5372,1015 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Udviklingsprojekter</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n">
+        <v>64500</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>54300</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Patenter, varemærker mv.</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n">
+        <v>99800</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>99900</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="17" t="n">
+        <v>1056100</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>965700</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Immaterielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
-        <v>1273100</v>
-      </c>
-      <c r="C2" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>1288800</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>1289800</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>1295100</v>
       </c>
-      <c r="F2" s="16" t="n">
-        <v>1320100</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="17" t="inlineStr">
-        <is>
-          <t>Materielle anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B3" s="16" t="n">
-        <v>127800</v>
-      </c>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n">
-        <v>145300</v>
-      </c>
-      <c r="E3" s="16" t="n">
-        <v>179300</v>
-      </c>
-      <c r="F3" s="16" t="n">
-        <v>243300</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>Anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="n">
-        <v>1630700</v>
-      </c>
-      <c r="C4" s="16" t="n">
-        <v>1642900</v>
-      </c>
-      <c r="D4" s="16" t="n">
-        <v>1714500</v>
-      </c>
-      <c r="E4" s="16" t="n">
-        <v>1708000</v>
-      </c>
-      <c r="F4" s="16" t="n">
-        <v>1774400</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>Varebeholdninger</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="n">
-        <v>124600</v>
-      </c>
-      <c r="C5" s="16" t="n">
-        <v>168200</v>
-      </c>
-      <c r="D5" s="16" t="n">
-        <v>260200</v>
-      </c>
-      <c r="E5" s="16" t="n">
-        <v>219900</v>
-      </c>
-      <c r="F5" s="16" t="n">
-        <v>238400</v>
+      <c r="E5" s="17" t="n">
+        <v>1239900</v>
+      </c>
+      <c r="F5" s="17" t="n">
+        <v>1161000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>Tilgodehavender fra salg og tjenesteydelser</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="16" t="n">
-        <v>462300</v>
-      </c>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="16" t="n"/>
-      <c r="F6" s="16" t="n"/>
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Grunde og bygninger</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n">
+        <v>156900</v>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>153000</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>Tilgodehavender hos tilknyttede virksomheder</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Produktionsanlæg og maskiner</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n">
+        <v>81700</v>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>86300</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>Andre tilgodehavender</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="16" t="n"/>
-      <c r="E8" s="16" t="n"/>
-      <c r="F8" s="16" t="n"/>
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Driftsmateriel og inventar</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>Periodeafgrænsningsposter (aktiver)</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="n">
-        <v>31600</v>
-      </c>
-      <c r="C9" s="16" t="n">
-        <v>42700</v>
-      </c>
-      <c r="D9" s="16" t="n">
-        <v>54000</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>48500</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>64800</v>
-      </c>
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Indretning af lejede lokaler</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>Udskudt skatteaktiv</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="n">
-        <v>3600</v>
-      </c>
-      <c r="C10" s="16" t="n">
-        <v>5400</v>
-      </c>
-      <c r="D10" s="16" t="n">
-        <v>10100</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>10400</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>11400</v>
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Forudbetaling og anlægsaktiver under opførelse</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n">
+        <v>4700</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>13000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="16" t="n"/>
-      <c r="D11" s="16" t="n"/>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="16" t="n"/>
+          <t>Materielle anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n">
+        <v>145300</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>179300</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>243300</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>252300</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>Kortfristede skattetilgodehavender</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="16" t="n">
-        <v>9000</v>
-      </c>
-      <c r="E12" s="16" t="n">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Kapitalandele, dattervirksomheder</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n">
+        <v>1312400</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>1312400</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>Deposita</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="F13" s="17" t="n">
         <v>0</v>
-      </c>
-      <c r="F12" s="16" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>Tilgodehavender</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n">
-        <v>38800</v>
-      </c>
-      <c r="D13" s="16" t="n">
-        <v>65200</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>41500</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>43200</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>Værdipapirer</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="16" t="n"/>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="16" t="n"/>
+          <t>Finansielle anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="17" t="n">
+        <v>12800</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>24000</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>Likvide beholdninger</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="n">
-        <v>197100</v>
-      </c>
-      <c r="C15" s="16" t="n">
-        <v>116000</v>
-      </c>
-      <c r="D15" s="16" t="n">
-        <v>195100</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>243900</v>
-      </c>
-      <c r="F15" s="16" t="n">
-        <v>243900</v>
+          <t>Anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>1642900</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>1714500</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>1708000</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>1496000</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>1437300</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>Omsætningsaktiver</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="n">
-        <v>729000</v>
-      </c>
-      <c r="C16" s="16" t="n">
-        <v>845900</v>
-      </c>
-      <c r="D16" s="16" t="n">
-        <v>1259600</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>1177800</v>
-      </c>
-      <c r="F16" s="16" t="n">
-        <v>1196400</v>
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>Råvarer og hjælpematerialer</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="17" t="n">
+        <v>74000</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>72800</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>Aktiver</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="n">
-        <v>2359700</v>
-      </c>
-      <c r="C17" s="16" t="n">
-        <v>2488800</v>
-      </c>
-      <c r="D17" s="16" t="n">
-        <v>2974100</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>2885800</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>2970800</v>
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>Varer under fremstilling</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n">
+        <v>59100</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>74600</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>Selskabskapital</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="n">
-        <v>51800</v>
-      </c>
-      <c r="C18" s="16" t="n">
-        <v>51900</v>
-      </c>
-      <c r="D18" s="16" t="n">
-        <v>51900</v>
-      </c>
-      <c r="E18" s="16" t="n">
-        <v>51900</v>
-      </c>
-      <c r="F18" s="16" t="n">
-        <v>51900</v>
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>Færdigvarer og handelsvarer</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n">
+        <v>105300</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>123800</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="16" t="n"/>
-      <c r="F19" s="16" t="n"/>
+          <t>Varebeholdninger</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n">
+        <v>168200</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>260200</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>219900</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>238400</v>
+      </c>
+      <c r="F19" s="17" t="n">
+        <v>271200</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>Reserve for udviklingsomkostninger</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>Tilgodehavender fra salg og tjenesteydelser</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n">
+        <v>462300</v>
+      </c>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n">
+        <v>554100</v>
+      </c>
+      <c r="F20" s="17" t="n">
+        <v>617900</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>Reserve for sikringstransaktioner</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="16" t="n"/>
-      <c r="D21" s="16" t="n"/>
-      <c r="E21" s="16" t="n"/>
-      <c r="F21" s="16" t="n"/>
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>Tilgodehavender hos tilknyttede virksomheder</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>Andre reserver</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="16" t="n"/>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="16" t="n"/>
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>Andre tilgodehavender</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="17" t="n">
+        <v>43200</v>
+      </c>
+      <c r="F22" s="17" t="n">
+        <v>22700</v>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>Overført resultat</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="n"/>
-      <c r="C23" s="16" t="n">
-        <v>756600</v>
-      </c>
-      <c r="D23" s="16" t="n">
-        <v>955900</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>982100</v>
-      </c>
-      <c r="F23" s="16" t="n">
-        <v>892200</v>
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>Periodeafgrænsningsposter (aktiver)</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="n">
+        <v>42700</v>
+      </c>
+      <c r="C23" s="17" t="n">
+        <v>54000</v>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>48500</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>67400</v>
+      </c>
+      <c r="F23" s="17" t="n">
+        <v>79400</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
-        <is>
-          <t>Egenkapital i alt</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="n">
-        <v>1027600</v>
-      </c>
-      <c r="C24" s="16" t="n">
-        <v>1032100</v>
-      </c>
-      <c r="D24" s="16" t="n">
-        <v>1220400</v>
-      </c>
-      <c r="E24" s="16" t="n">
-        <v>1446800</v>
-      </c>
-      <c r="F24" s="16" t="n">
-        <v>1448400</v>
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>Udskudt skatteaktiv</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n">
+        <v>5400</v>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>10100</v>
+      </c>
+      <c r="D24" s="17" t="n">
+        <v>10400</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>11400</v>
+      </c>
+      <c r="F24" s="17" t="n">
+        <v>10900</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>Hensættelse til udskudt skat</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="n">
-        <v>51200</v>
-      </c>
-      <c r="C25" s="16" t="n">
-        <v>42800</v>
-      </c>
-      <c r="D25" s="16" t="n">
-        <v>43300</v>
-      </c>
-      <c r="E25" s="16" t="n">
-        <v>45300</v>
-      </c>
-      <c r="F25" s="16" t="n">
-        <v>48300</v>
-      </c>
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="inlineStr">
-        <is>
-          <t>Hensatte forpligtelser</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="n">
-        <v>12800</v>
-      </c>
-      <c r="C26" s="16" t="n">
-        <v>14000</v>
-      </c>
-      <c r="D26" s="16" t="n">
-        <v>43300</v>
-      </c>
-      <c r="E26" s="16" t="n">
-        <v>45300</v>
-      </c>
-      <c r="F26" s="16" t="n">
-        <v>48300</v>
-      </c>
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>Kortfristede skattetilgodehavender</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n">
+        <v>9000</v>
+      </c>
+      <c r="D26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="17" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>Ansvarlig lånekapital (langfristet)</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="16" t="n"/>
-      <c r="E27" s="16" t="n"/>
-      <c r="F27" s="16" t="n"/>
+          <t>Tilgodehavender</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="n">
+        <v>38800</v>
+      </c>
+      <c r="C27" s="17" t="n">
+        <v>65200</v>
+      </c>
+      <c r="D27" s="17" t="n">
+        <v>41500</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>732600</v>
+      </c>
+      <c r="F27" s="17" t="n">
+        <v>775800</v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>Langfristede lån</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="16" t="n"/>
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>Værdipapirer</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>Leasingforpligtelser (langfristet)</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="n">
-        <v>186200</v>
-      </c>
-      <c r="C29" s="16" t="n">
-        <v>182200</v>
-      </c>
-      <c r="D29" s="16" t="n">
-        <v>185900</v>
-      </c>
-      <c r="E29" s="16" t="n">
-        <v>153800</v>
-      </c>
-      <c r="F29" s="16" t="n">
-        <v>142900</v>
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>Likvide beholdninger</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="n">
+        <v>116000</v>
+      </c>
+      <c r="C29" s="17" t="n">
+        <v>195100</v>
+      </c>
+      <c r="D29" s="17" t="n">
+        <v>243900</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>228000</v>
+      </c>
+      <c r="F29" s="17" t="n">
+        <v>173800</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>Anden gæld (langfristet)</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="n">
-        <v>68900</v>
-      </c>
-      <c r="C30" s="16" t="n">
-        <v>52100</v>
-      </c>
-      <c r="D30" s="16" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="16" t="n">
-        <v>29500</v>
+          <t>Omsætningsaktiver</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="n">
+        <v>845900</v>
+      </c>
+      <c r="C30" s="17" t="n">
+        <v>1259600</v>
+      </c>
+      <c r="D30" s="17" t="n">
+        <v>1177800</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>1199000</v>
+      </c>
+      <c r="F30" s="17" t="n">
+        <v>1220700</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>Langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="n">
-        <v>774900</v>
-      </c>
-      <c r="C31" s="16" t="n">
-        <v>858700</v>
-      </c>
-      <c r="D31" s="16" t="n">
-        <v>1007900</v>
-      </c>
-      <c r="E31" s="16" t="n">
-        <v>812400</v>
-      </c>
-      <c r="F31" s="16" t="n">
-        <v>808200</v>
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>Aktiver</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="n">
+        <v>2488800</v>
+      </c>
+      <c r="C31" s="17" t="n">
+        <v>2974100</v>
+      </c>
+      <c r="D31" s="17" t="n">
+        <v>2885800</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>2695000</v>
+      </c>
+      <c r="F31" s="17" t="n">
+        <v>2658000</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
-        <is>
-          <t>Ansvarlig lånekapital (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="n"/>
-      <c r="C32" s="16" t="n"/>
-      <c r="D32" s="16" t="n"/>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="16" t="n"/>
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>Selskabskapital</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="n">
+        <v>51900</v>
+      </c>
+      <c r="C32" s="17" t="n">
+        <v>51900</v>
+      </c>
+      <c r="D32" s="17" t="n">
+        <v>51900</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>51900</v>
+      </c>
+      <c r="F32" s="17" t="n">
+        <v>51900</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>Kortfristet del af langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="n"/>
-      <c r="C33" s="16" t="n"/>
-      <c r="D33" s="16" t="n"/>
-      <c r="E33" s="16" t="n"/>
-      <c r="F33" s="16" t="n"/>
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="17" t="n"/>
+      <c r="D33" s="17" t="n"/>
+      <c r="E33" s="17" t="n"/>
+      <c r="F33" s="17" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
-        <is>
-          <t>Kreditinstitutter</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="n"/>
-      <c r="C34" s="16" t="n">
-        <v>97100</v>
-      </c>
-      <c r="D34" s="16" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="16" t="n"/>
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>Reserve for udviklingsomkostninger</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="17" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
-        <is>
-          <t>Leasingforpligtelser (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="n">
-        <v>45900</v>
-      </c>
-      <c r="C35" s="16" t="n">
-        <v>45600</v>
-      </c>
-      <c r="D35" s="16" t="n">
-        <v>55800</v>
-      </c>
-      <c r="E35" s="16" t="n">
-        <v>54600</v>
-      </c>
-      <c r="F35" s="16" t="n">
-        <v>67300</v>
-      </c>
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>Reserve for sikringstransaktioner</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="17" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
-        <is>
-          <t>Leverandører af varer og tjenesteydelser</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="n">
-        <v>193600</v>
-      </c>
-      <c r="C36" s="16" t="n">
-        <v>241800</v>
-      </c>
-      <c r="D36" s="16" t="n">
-        <v>249200</v>
-      </c>
-      <c r="E36" s="16" t="n">
-        <v>260400</v>
-      </c>
-      <c r="F36" s="16" t="n">
-        <v>302300</v>
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>Andre reserver</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="17" t="n"/>
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="17" t="n">
+        <v>-14400</v>
+      </c>
+      <c r="F36" s="17" t="n">
+        <v>-47700</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
-        <is>
-          <t>Gæld til tilknyttede virksomheder</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="n"/>
-      <c r="C37" s="16" t="n"/>
-      <c r="D37" s="16" t="n"/>
-      <c r="E37" s="16" t="n"/>
-      <c r="F37" s="16" t="n"/>
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>Overført resultat</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="n">
+        <v>756600</v>
+      </c>
+      <c r="C37" s="17" t="n">
+        <v>955900</v>
+      </c>
+      <c r="D37" s="17" t="n">
+        <v>982100</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>821700</v>
+      </c>
+      <c r="F37" s="17" t="n">
+        <v>701200</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="15" t="inlineStr">
         <is>
-          <t>Gæld til selskabsdeltagere og ledelse</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="n"/>
-      <c r="C38" s="16" t="n"/>
-      <c r="D38" s="16" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="16" t="n"/>
+          <t>Egenkapital i alt</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="n">
+        <v>1032100</v>
+      </c>
+      <c r="C38" s="17" t="n">
+        <v>1220400</v>
+      </c>
+      <c r="D38" s="17" t="n">
+        <v>1446800</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>1377900</v>
+      </c>
+      <c r="F38" s="17" t="n">
+        <v>1226500</v>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
-        <is>
-          <t>Selskabsskat</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="n"/>
-      <c r="C39" s="16" t="n"/>
-      <c r="D39" s="16" t="n"/>
-      <c r="E39" s="16" t="n"/>
-      <c r="F39" s="16" t="n"/>
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>Hensættelse til udskudt skat</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="n">
+        <v>42800</v>
+      </c>
+      <c r="C39" s="17" t="n">
+        <v>43300</v>
+      </c>
+      <c r="D39" s="17" t="n">
+        <v>45300</v>
+      </c>
+      <c r="E39" s="17" t="n"/>
+      <c r="F39" s="17" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
+          <t>Hensatte forpligtelser</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="n">
+        <v>14000</v>
+      </c>
+      <c r="C40" s="17" t="n">
+        <v>43300</v>
+      </c>
+      <c r="D40" s="17" t="n">
+        <v>45300</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>13300</v>
+      </c>
+      <c r="F40" s="17" t="n">
+        <v>19900</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>Ansvarlig lånekapital (langfristet)</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="F41" s="17" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>Langfristede lån</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="n"/>
+      <c r="C42" s="17" t="n"/>
+      <c r="D42" s="17" t="n"/>
+      <c r="E42" s="17" t="n">
+        <v>559500</v>
+      </c>
+      <c r="F42" s="17" t="n">
+        <v>56100</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>Leasingforpligtelser (langfristet)</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="n">
+        <v>182200</v>
+      </c>
+      <c r="C43" s="17" t="n">
+        <v>185900</v>
+      </c>
+      <c r="D43" s="17" t="n">
+        <v>153800</v>
+      </c>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="17" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>Anden gæld (langfristet)</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="n">
+        <v>52100</v>
+      </c>
+      <c r="C44" s="17" t="n"/>
+      <c r="D44" s="17" t="n"/>
+      <c r="E44" s="17" t="n"/>
+      <c r="F44" s="17" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>Langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="n">
+        <v>858700</v>
+      </c>
+      <c r="C45" s="17" t="n">
+        <v>1007900</v>
+      </c>
+      <c r="D45" s="17" t="n">
+        <v>812400</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>670200</v>
+      </c>
+      <c r="F45" s="17" t="n">
+        <v>186100</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>Ansvarlig lånekapital (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="17" t="n"/>
+      <c r="D46" s="17" t="n"/>
+      <c r="E46" s="17" t="n"/>
+      <c r="F46" s="17" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>Kortfristet del af langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="n"/>
+      <c r="C47" s="17" t="n"/>
+      <c r="D47" s="17" t="n"/>
+      <c r="E47" s="17" t="n"/>
+      <c r="F47" s="17" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>Kreditinstitutter</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="n">
+        <v>97100</v>
+      </c>
+      <c r="C48" s="17" t="n"/>
+      <c r="D48" s="17" t="n"/>
+      <c r="E48" s="17" t="n">
+        <v>23900</v>
+      </c>
+      <c r="F48" s="17" t="n">
+        <v>568500</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>Leasingforpligtelser (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="n">
+        <v>45600</v>
+      </c>
+      <c r="C49" s="17" t="n">
+        <v>55800</v>
+      </c>
+      <c r="D49" s="17" t="n">
+        <v>54600</v>
+      </c>
+      <c r="E49" s="17" t="n"/>
+      <c r="F49" s="17" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>Leverandører af varer og tjenesteydelser</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="n">
+        <v>241800</v>
+      </c>
+      <c r="C50" s="17" t="n">
+        <v>249200</v>
+      </c>
+      <c r="D50" s="17" t="n">
+        <v>260400</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>302300</v>
+      </c>
+      <c r="F50" s="17" t="n">
+        <v>296100</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>Gæld til tilknyttede virksomheder</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="n"/>
+      <c r="C51" s="17" t="n"/>
+      <c r="D51" s="17" t="n"/>
+      <c r="E51" s="17" t="n">
+        <v>7200</v>
+      </c>
+      <c r="F51" s="17" t="n">
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>Gæld til selskabsdeltagere og ledelse</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="n"/>
+      <c r="C52" s="17" t="n"/>
+      <c r="D52" s="17" t="n"/>
+      <c r="E52" s="17" t="n"/>
+      <c r="F52" s="17" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>Selskabsskat</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="n"/>
+      <c r="C53" s="17" t="n"/>
+      <c r="D53" s="17" t="n"/>
+      <c r="E53" s="17" t="n">
+        <v>14100</v>
+      </c>
+      <c r="F53" s="17" t="n">
+        <v>25500</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="16" t="inlineStr">
+        <is>
           <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n"/>
-      <c r="C40" s="16" t="n"/>
-      <c r="D40" s="16" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="16" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="B54" s="17" t="n"/>
+      <c r="C54" s="17" t="n"/>
+      <c r="D54" s="17" t="n"/>
+      <c r="E54" s="17" t="n"/>
+      <c r="F54" s="17" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n">
-        <v>122500</v>
-      </c>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="16" t="n">
+      <c r="B55" s="17" t="n"/>
+      <c r="C55" s="17" t="n">
         <v>185600</v>
       </c>
-      <c r="E41" s="16" t="n">
+      <c r="D55" s="17" t="n">
         <v>183200</v>
       </c>
-      <c r="F41" s="16" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="E55" s="17" t="n">
+        <v>189200</v>
+      </c>
+      <c r="F55" s="17" t="n">
+        <v>222500</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n"/>
-      <c r="C42" s="16" t="n"/>
-      <c r="D42" s="16" t="n"/>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="17" t="inlineStr">
+      <c r="B56" s="17" t="n"/>
+      <c r="C56" s="17" t="n"/>
+      <c r="D56" s="17" t="n"/>
+      <c r="E56" s="17" t="n"/>
+      <c r="F56" s="17" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="15" t="inlineStr">
         <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B43" s="16" t="n">
-        <v>557200</v>
-      </c>
-      <c r="C43" s="16" t="n">
+      <c r="B57" s="17" t="n">
         <v>598000</v>
       </c>
-      <c r="D43" s="16" t="n">
+      <c r="C57" s="17" t="n">
         <v>745800</v>
       </c>
-      <c r="E43" s="16" t="n">
+      <c r="D57" s="17" t="n">
         <v>626600</v>
       </c>
-      <c r="F43" s="16" t="n">
-        <v>714200</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="17" t="inlineStr">
+      <c r="E57" s="17" t="n">
+        <v>646900</v>
+      </c>
+      <c r="F57" s="17" t="n">
+        <v>1246600</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="15" t="inlineStr">
         <is>
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n">
-        <v>1332100</v>
-      </c>
-      <c r="C44" s="16" t="n">
+      <c r="B58" s="17" t="n">
         <v>1456700</v>
       </c>
-      <c r="D44" s="16" t="n">
+      <c r="C58" s="17" t="n">
         <v>1753700</v>
       </c>
-      <c r="E44" s="16" t="n">
+      <c r="D58" s="17" t="n">
         <v>1439000</v>
       </c>
-      <c r="F44" s="16" t="n">
-        <v>1522400</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="17" t="inlineStr">
+      <c r="E58" s="17" t="n">
+        <v>1317100</v>
+      </c>
+      <c r="F58" s="17" t="n">
+        <v>1432700</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="15" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n">
-        <v>2359700</v>
-      </c>
-      <c r="C45" s="16" t="n">
+      <c r="B59" s="17" t="n">
         <v>2488800</v>
       </c>
-      <c r="D45" s="16" t="n">
+      <c r="C59" s="17" t="n">
         <v>2974100</v>
       </c>
-      <c r="E45" s="16" t="n">
+      <c r="D59" s="17" t="n">
         <v>2885800</v>
       </c>
-      <c r="F45" s="16" t="n">
-        <v>2970800</v>
+      <c r="E59" s="17" t="n">
+        <v>2695000</v>
+      </c>
+      <c r="F59" s="17" t="n">
+        <v>2658000</v>
       </c>
     </row>
   </sheetData>
@@ -5195,7 +6394,129 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (t.kr.)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>259600</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>324600</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>711100</v>
+      </c>
+      <c r="E2" s="17" t="n"/>
+      <c r="F2" s="17" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>-54800</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>-97900</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>-126700</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>-138800</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>-97700</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>-288800</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>-148900</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>-535500</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>-422400</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>-469800</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n">
+        <v>77800</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>48900</v>
+      </c>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -5209,7 +6530,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>Regnskabs- og nøgletal (CVR: 35663908) — funktionsopdelt</t>
+          <t>Regnskabs- og nøgletal (CVR: 35663908) — artsopdelt</t>
         </is>
       </c>
     </row>
@@ -5220,13 +6541,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -5272,55 +6593,55 @@
     <row r="6">
       <c r="A6" s="23" t="inlineStr">
         <is>
-          <t>Produktionsomkostninger</t>
+          <t>Andre driftsindtægter</t>
         </is>
       </c>
       <c r="B6" s="24">
-        <f>-'res_raw_35663908'!$F$3</f>
+        <f>'res_raw_35663908'!$F$3</f>
         <v/>
       </c>
       <c r="C6" s="24">
-        <f>-'res_raw_35663908'!$E$3</f>
+        <f>'res_raw_35663908'!$E$3</f>
         <v/>
       </c>
       <c r="D6" s="24">
-        <f>-'res_raw_35663908'!$D$3</f>
+        <f>'res_raw_35663908'!$D$3</f>
         <v/>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>fsa:CostOfProduction (vises negativt). Materialer, lønninger, produktionsoverhead.</t>
+          <t>fsa:OtherOperatingIncome. Indtægter fra sekundære aktiviteter (huslejeindtægter, avance ved salg af anlæg mv.).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="inlineStr">
-        <is>
-          <t>Bruttoresultat</t>
-        </is>
-      </c>
-      <c r="B7" s="27">
-        <f>SUM(B5:B6)</f>
-        <v/>
-      </c>
-      <c r="C7" s="27">
-        <f>SUM(C5:C6)</f>
-        <v/>
-      </c>
-      <c r="D7" s="27">
-        <f>SUM(D5:D6)</f>
-        <v/>
-      </c>
-      <c r="F7" s="28" t="inlineStr">
-        <is>
-          <t>Beregnet: Nettoomsætning − Produktionsomkostninger. Matcher fsa:GrossResult.</t>
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>Vareforbrug</t>
+        </is>
+      </c>
+      <c r="B7" s="24">
+        <f>-'res_raw_35663908'!$F$4</f>
+        <v/>
+      </c>
+      <c r="C7" s="24">
+        <f>-'res_raw_35663908'!$E$4</f>
+        <v/>
+      </c>
+      <c r="D7" s="24">
+        <f>-'res_raw_35663908'!$D$4</f>
+        <v/>
+      </c>
+      <c r="F7" s="25" t="inlineStr">
+        <is>
+          <t>fsa:CostOfSales (vises negativt for korrekt SUM-formel).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="23" t="inlineStr">
         <is>
-          <t>Salgs- og distributionsomk.</t>
+          <t>Andre eksterne omk. mv.</t>
         </is>
       </c>
       <c r="B8" s="24">
@@ -5337,491 +6658,495 @@
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>fsa:DistributionCosts (vises negativt). Marketing, salg, distribution.</t>
+          <t>fsa:OtherExternalExpenses (vises negativt). Husleje, energi, kontorhold mv.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="inlineStr">
-        <is>
-          <t>Administrationsomkostninger mv.</t>
-        </is>
-      </c>
-      <c r="B9" s="24">
-        <f>-'res_raw_35663908'!$F$6</f>
-        <v/>
-      </c>
-      <c r="C9" s="24">
-        <f>-'res_raw_35663908'!$E$6</f>
-        <v/>
-      </c>
-      <c r="D9" s="24">
-        <f>-'res_raw_35663908'!$D$6</f>
-        <v/>
-      </c>
-      <c r="F9" s="25" t="inlineStr">
-        <is>
-          <t>fsa:AdministrativeExpenses (vises negativt). Generel administration.</t>
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>Bruttofortjeneste</t>
+        </is>
+      </c>
+      <c r="B9" s="27">
+        <f>SUM(B5:B8)</f>
+        <v/>
+      </c>
+      <c r="C9" s="27">
+        <f>SUM(C5:C8)</f>
+        <v/>
+      </c>
+      <c r="D9" s="27">
+        <f>SUM(D5:D8)</f>
+        <v/>
+      </c>
+      <c r="F9" s="28" t="inlineStr">
+        <is>
+          <t>Beregnet: Nettoomsætning + Andre driftsindt. − Vareforbrug − Andre ext. omk.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="23" t="inlineStr">
         <is>
-          <t>Andre driftsindtægter</t>
+          <t>Personaleomkostninger</t>
         </is>
       </c>
       <c r="B10" s="24">
-        <f>'res_raw_35663908'!$F$7</f>
+        <f>-'res_raw_35663908'!$F$7</f>
         <v/>
       </c>
       <c r="C10" s="24">
-        <f>'res_raw_35663908'!$E$7</f>
+        <f>-'res_raw_35663908'!$E$7</f>
         <v/>
       </c>
       <c r="D10" s="24">
-        <f>'res_raw_35663908'!$D$7</f>
+        <f>-'res_raw_35663908'!$D$7</f>
         <v/>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>fsa:OtherOperatingIncome. Sekundære driftsindtægter (huslejeindtægter, off. tilskud, avancer mv.).</t>
+          <t>fsa:EmployeeBenefitsExpense (vises negativt). Lønninger, pension, sociale ydelser.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="23" t="inlineStr">
         <is>
+          <t>Af- og nedskrivninger</t>
+        </is>
+      </c>
+      <c r="B11" s="24">
+        <f>-'res_raw_35663908'!$F$9</f>
+        <v/>
+      </c>
+      <c r="C11" s="24">
+        <f>-'res_raw_35663908'!$E$9</f>
+        <v/>
+      </c>
+      <c r="D11" s="24">
+        <f>-'res_raw_35663908'!$D$9</f>
+        <v/>
+      </c>
+      <c r="F11" s="25" t="inlineStr">
+        <is>
+          <t>fsa:Depreciation (vises negativt). Af- og nedskrivninger på materielle og immaterielle anlægsaktiver.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B11" s="24">
-        <f>-'res_raw_35663908'!$F$8</f>
-        <v/>
-      </c>
-      <c r="C11" s="24">
-        <f>-'res_raw_35663908'!$E$8</f>
-        <v/>
-      </c>
-      <c r="D11" s="24">
-        <f>-'res_raw_35663908'!$D$8</f>
-        <v/>
-      </c>
-      <c r="F11" s="25" t="inlineStr">
-        <is>
-          <t>fsa:OtherOperatingExpenses (vises negativt). Sekundære driftsomkostninger.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="B12" s="24">
+        <f>-'res_raw_35663908'!$F$10</f>
+        <v/>
+      </c>
+      <c r="C12" s="24">
+        <f>-'res_raw_35663908'!$E$10</f>
+        <v/>
+      </c>
+      <c r="D12" s="24">
+        <f>-'res_raw_35663908'!$D$10</f>
+        <v/>
+      </c>
+      <c r="F12" s="25" t="inlineStr">
+        <is>
+          <t>fsa:OtherOperatingExpenses (vises negativt). Typisk 0 eller meget lille post.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B12" s="27">
-        <f>SUM(B7:B11)</f>
-        <v/>
-      </c>
-      <c r="C12" s="27">
-        <f>SUM(C7:C11)</f>
-        <v/>
-      </c>
-      <c r="D12" s="27">
-        <f>SUM(D7:D11)</f>
-        <v/>
-      </c>
-      <c r="F12" s="28" t="inlineStr">
-        <is>
-          <t>Beregnet: Bruttoresultat − Salgs/dist. − Administration + Andre driftsindt. − Andre driftsomk. EBIT.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="23" t="inlineStr">
-        <is>
-          <t>Finansielle indtægter mv.</t>
-        </is>
-      </c>
-      <c r="B13" s="24">
-        <f>N('res_raw_35663908'!$F$10)+N('res_raw_35663908'!$F$11)</f>
-        <v/>
-      </c>
-      <c r="C13" s="24">
-        <f>N('res_raw_35663908'!$E$10)+N('res_raw_35663908'!$E$11)</f>
-        <v/>
-      </c>
-      <c r="D13" s="24">
-        <f>N('res_raw_35663908'!$D$10)+N('res_raw_35663908'!$D$11)</f>
-        <v/>
-      </c>
-      <c r="F13" s="25" t="inlineStr">
-        <is>
-          <t>fsa:IncomeFromSubsidiaries + fsa:OtherFinanceIncome.</t>
+      <c r="B13" s="27">
+        <f>SUM(B9:B12)</f>
+        <v/>
+      </c>
+      <c r="C13" s="27">
+        <f>SUM(C9:C12)</f>
+        <v/>
+      </c>
+      <c r="D13" s="27">
+        <f>SUM(D9:D12)</f>
+        <v/>
+      </c>
+      <c r="F13" s="28" t="inlineStr">
+        <is>
+          <t>Beregnet: Bruttofortjeneste − Personaleomk. − Af- og nedskrivninger − Andre driftsomk. EBIT.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="23" t="inlineStr">
         <is>
+          <t>Finansielle indtægter mv.</t>
+        </is>
+      </c>
+      <c r="B14" s="24">
+        <f>N('res_raw_35663908'!$F$12)+N('res_raw_35663908'!$F$13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="24">
+        <f>N('res_raw_35663908'!$E$12)+N('res_raw_35663908'!$E$13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="24">
+        <f>N('res_raw_35663908'!$D$12)+N('res_raw_35663908'!$D$13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="25" t="inlineStr">
+        <is>
+          <t>fsa:IncomeFromSubsidiaries + fsa:OtherFinanceIncome.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
           <t>Finansielle omkostninger mv.</t>
         </is>
       </c>
-      <c r="B14" s="24">
-        <f>-'res_raw_35663908'!$F$12</f>
-        <v/>
-      </c>
-      <c r="C14" s="24">
-        <f>-'res_raw_35663908'!$E$12</f>
-        <v/>
-      </c>
-      <c r="D14" s="24">
-        <f>-'res_raw_35663908'!$D$12</f>
-        <v/>
-      </c>
-      <c r="F14" s="25" t="inlineStr">
-        <is>
-          <t>fsa:OtherFinanceExpenses (vises negativt). Renteomkostninger, kurstab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="26" t="inlineStr">
+      <c r="B15" s="24">
+        <f>-'res_raw_35663908'!$F$14</f>
+        <v/>
+      </c>
+      <c r="C15" s="24">
+        <f>-'res_raw_35663908'!$E$14</f>
+        <v/>
+      </c>
+      <c r="D15" s="24">
+        <f>-'res_raw_35663908'!$D$14</f>
+        <v/>
+      </c>
+      <c r="F15" s="25" t="inlineStr">
+        <is>
+          <t>fsa:OtherFinanceExpenses (vises negativt). Renteomkostninger, kurstab mv.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="26" t="inlineStr">
         <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B15" s="27">
-        <f>SUM(B12:B14)</f>
-        <v/>
-      </c>
-      <c r="C15" s="27">
-        <f>SUM(C12:C14)</f>
-        <v/>
-      </c>
-      <c r="D15" s="27">
-        <f>SUM(D12:D14)</f>
-        <v/>
-      </c>
-      <c r="F15" s="28" t="inlineStr">
+      <c r="B16" s="27">
+        <f>SUM(B13:B15)</f>
+        <v/>
+      </c>
+      <c r="C16" s="27">
+        <f>SUM(C13:C15)</f>
+        <v/>
+      </c>
+      <c r="D16" s="27">
+        <f>SUM(D13:D15)</f>
+        <v/>
+      </c>
+      <c r="F16" s="28" t="inlineStr">
         <is>
           <t>Beregnet: EBIT + Fin. indtægter + Fin. omk. EBT.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="29" t="n"/>
-      <c r="B16" s="29" t="n"/>
-      <c r="C16" s="29" t="n"/>
-      <c r="D16" s="29" t="n"/>
-      <c r="F16" s="29" t="n"/>
-    </row>
     <row r="17">
-      <c r="A17" s="22" t="inlineStr">
+      <c r="A17" s="29" t="n"/>
+      <c r="B17" s="29" t="n"/>
+      <c r="C17" s="29" t="n"/>
+      <c r="D17" s="29" t="n"/>
+      <c r="F17" s="29" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>Uddrag af balance</t>
         </is>
       </c>
-      <c r="B17" s="22" t="n"/>
-      <c r="C17" s="22" t="n"/>
-      <c r="D17" s="22" t="n"/>
-      <c r="F17" s="22" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="23" t="inlineStr">
-        <is>
-          <t>Anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B18" s="24">
-        <f>'balance_raw_35663908'!$F$4</f>
-        <v/>
-      </c>
-      <c r="C18" s="24">
-        <f>'balance_raw_35663908'!$E$4</f>
-        <v/>
-      </c>
-      <c r="D18" s="24">
-        <f>'balance_raw_35663908'!$D$4</f>
-        <v/>
-      </c>
-      <c r="F18" s="25" t="inlineStr">
-        <is>
-          <t>fsa:NoncurrentAssets. Materielle, immaterielle og finansielle anlægsaktiver.</t>
-        </is>
-      </c>
+      <c r="B18" s="22" t="n"/>
+      <c r="C18" s="22" t="n"/>
+      <c r="D18" s="22" t="n"/>
+      <c r="F18" s="22" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="23" t="inlineStr">
         <is>
+          <t>Anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B19" s="24">
+        <f>'balance_raw_35663908'!$F$15</f>
+        <v/>
+      </c>
+      <c r="C19" s="24">
+        <f>'balance_raw_35663908'!$E$15</f>
+        <v/>
+      </c>
+      <c r="D19" s="24">
+        <f>'balance_raw_35663908'!$D$15</f>
+        <v/>
+      </c>
+      <c r="F19" s="25" t="inlineStr">
+        <is>
+          <t>fsa:NoncurrentAssets. Materielle, immaterielle og finansielle anlægsaktiver.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
           <t>Omsætningsaktiver</t>
         </is>
       </c>
-      <c r="B19" s="24">
-        <f>'balance_raw_35663908'!$F$16</f>
-        <v/>
-      </c>
-      <c r="C19" s="24">
-        <f>'balance_raw_35663908'!$E$16</f>
-        <v/>
-      </c>
-      <c r="D19" s="24">
-        <f>'balance_raw_35663908'!$D$16</f>
-        <v/>
-      </c>
-      <c r="F19" s="25" t="inlineStr">
+      <c r="B20" s="24">
+        <f>'balance_raw_35663908'!$F$30</f>
+        <v/>
+      </c>
+      <c r="C20" s="24">
+        <f>'balance_raw_35663908'!$E$30</f>
+        <v/>
+      </c>
+      <c r="D20" s="24">
+        <f>'balance_raw_35663908'!$D$30</f>
+        <v/>
+      </c>
+      <c r="F20" s="25" t="inlineStr">
         <is>
           <t>fsa:CurrentAssets. Varebeholdninger, tilgodehavender, likvider.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="26" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t>Aktiver i alt</t>
         </is>
       </c>
-      <c r="B20" s="27">
-        <f>SUM(B18:B19)</f>
-        <v/>
-      </c>
-      <c r="C20" s="27">
-        <f>SUM(C18:C19)</f>
-        <v/>
-      </c>
-      <c r="D20" s="27">
-        <f>SUM(D18:D19)</f>
-        <v/>
-      </c>
-      <c r="F20" s="28" t="inlineStr">
+      <c r="B21" s="27">
+        <f>SUM(B19:B20)</f>
+        <v/>
+      </c>
+      <c r="C21" s="27">
+        <f>SUM(C19:C20)</f>
+        <v/>
+      </c>
+      <c r="D21" s="27">
+        <f>SUM(D19:D20)</f>
+        <v/>
+      </c>
+      <c r="F21" s="28" t="inlineStr">
         <is>
           <t>Beregnet: Anlægsaktiver + Omsætningsaktiver. Bør matche fsa:Assets.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="29" t="n"/>
-      <c r="B21" s="29" t="n"/>
-      <c r="C21" s="29" t="n"/>
-      <c r="D21" s="29" t="n"/>
-      <c r="F21" s="29" t="n"/>
-    </row>
     <row r="22">
-      <c r="A22" s="23" t="inlineStr">
-        <is>
-          <t>Egenkapital</t>
-        </is>
-      </c>
-      <c r="B22" s="24">
-        <f>'balance_raw_35663908'!$F$24</f>
-        <v/>
-      </c>
-      <c r="C22" s="24">
-        <f>'balance_raw_35663908'!$E$24</f>
-        <v/>
-      </c>
-      <c r="D22" s="24">
-        <f>'balance_raw_35663908'!$D$24</f>
-        <v/>
-      </c>
-      <c r="F22" s="25" t="inlineStr">
-        <is>
-          <t>fsa:Equity. Selskabskapital, overført resultat, reserver.</t>
-        </is>
-      </c>
+      <c r="A22" s="29" t="n"/>
+      <c r="B22" s="29" t="n"/>
+      <c r="C22" s="29" t="n"/>
+      <c r="D22" s="29" t="n"/>
+      <c r="F22" s="29" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="23" t="inlineStr">
         <is>
+          <t>Egenkapital</t>
+        </is>
+      </c>
+      <c r="B23" s="24">
+        <f>'balance_raw_35663908'!$F$38</f>
+        <v/>
+      </c>
+      <c r="C23" s="24">
+        <f>'balance_raw_35663908'!$E$38</f>
+        <v/>
+      </c>
+      <c r="D23" s="24">
+        <f>'balance_raw_35663908'!$D$38</f>
+        <v/>
+      </c>
+      <c r="F23" s="25" t="inlineStr">
+        <is>
+          <t>fsa:Equity. Selskabskapital, overført resultat, reserver.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
           <t>Forpligtelser</t>
         </is>
       </c>
-      <c r="B23" s="24">
-        <f>'balance_raw_35663908'!$F$45-'balance_raw_35663908'!$F$24</f>
-        <v/>
-      </c>
-      <c r="C23" s="24">
-        <f>'balance_raw_35663908'!$E$45-'balance_raw_35663908'!$E$24</f>
-        <v/>
-      </c>
-      <c r="D23" s="24">
-        <f>'balance_raw_35663908'!$D$45-'balance_raw_35663908'!$D$24</f>
-        <v/>
-      </c>
-      <c r="F23" s="25" t="inlineStr">
+      <c r="B24" s="24">
+        <f>'balance_raw_35663908'!$F$59-'balance_raw_35663908'!$F$38</f>
+        <v/>
+      </c>
+      <c r="C24" s="24">
+        <f>'balance_raw_35663908'!$E$59-'balance_raw_35663908'!$E$38</f>
+        <v/>
+      </c>
+      <c r="D24" s="24">
+        <f>'balance_raw_35663908'!$D$59-'balance_raw_35663908'!$D$38</f>
+        <v/>
+      </c>
+      <c r="F24" s="25" t="inlineStr">
         <is>
           <t>Beregnet: Passiver (fsa:LiabilitiesAndEquity) − Egenkapital. Hensættelser + kort- og langfristet gæld.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="26" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="26" t="inlineStr">
         <is>
           <t>Passiver i alt</t>
         </is>
       </c>
-      <c r="B24" s="27">
-        <f>SUM(B22:B23)</f>
-        <v/>
-      </c>
-      <c r="C24" s="27">
-        <f>SUM(C22:C23)</f>
-        <v/>
-      </c>
-      <c r="D24" s="27">
-        <f>SUM(D22:D23)</f>
-        <v/>
-      </c>
-      <c r="F24" s="28" t="inlineStr">
+      <c r="B25" s="27">
+        <f>SUM(B23:B24)</f>
+        <v/>
+      </c>
+      <c r="C25" s="27">
+        <f>SUM(C23:C24)</f>
+        <v/>
+      </c>
+      <c r="D25" s="27">
+        <f>SUM(D23:D24)</f>
+        <v/>
+      </c>
+      <c r="F25" s="28" t="inlineStr">
         <is>
           <t>Beregnet: Egenkapital + Forpligtelser. Bør matche Aktiver i alt.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="29" t="n"/>
-      <c r="B25" s="29" t="n"/>
-      <c r="C25" s="29" t="n"/>
-      <c r="D25" s="29" t="n"/>
-      <c r="F25" s="29" t="n"/>
-    </row>
     <row r="26">
-      <c r="A26" s="22" t="inlineStr">
+      <c r="A26" s="29" t="n"/>
+      <c r="B26" s="29" t="n"/>
+      <c r="C26" s="29" t="n"/>
+      <c r="D26" s="29" t="n"/>
+      <c r="F26" s="29" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
         <is>
           <t>Udvalgte balanceposter</t>
         </is>
       </c>
-      <c r="B26" s="22" t="n"/>
-      <c r="C26" s="22" t="n"/>
-      <c r="D26" s="22" t="n"/>
-      <c r="F26" s="22" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="23" t="inlineStr">
-        <is>
-          <t>Varebeholdninger</t>
-        </is>
-      </c>
-      <c r="B27" s="24">
-        <f>'balance_raw_35663908'!$F$5</f>
-        <v/>
-      </c>
-      <c r="C27" s="24">
-        <f>'balance_raw_35663908'!$E$5</f>
-        <v/>
-      </c>
-      <c r="D27" s="24">
-        <f>'balance_raw_35663908'!$D$5</f>
-        <v/>
-      </c>
-      <c r="F27" s="25" t="inlineStr">
-        <is>
-          <t>fsa:Inventories (eller fsa:ManufacturedGoodsAndGoodsForResale hvis total mangler).</t>
-        </is>
-      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+      <c r="F27" s="22" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="23" t="inlineStr">
         <is>
-          <t>Tilgodehavender fra salg</t>
+          <t>Varebeholdninger</t>
         </is>
       </c>
       <c r="B28" s="24">
-        <f>'balance_raw_35663908'!$F$6</f>
+        <f>'balance_raw_35663908'!$F$19</f>
         <v/>
       </c>
       <c r="C28" s="24">
-        <f>'balance_raw_35663908'!$E$6</f>
+        <f>'balance_raw_35663908'!$E$19</f>
         <v/>
       </c>
       <c r="D28" s="24">
-        <f>'balance_raw_35663908'!$D$6</f>
+        <f>'balance_raw_35663908'!$D$19</f>
         <v/>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>fsa:ShorttermTradeReceivables. Kortfristede tilgodehavender fra kunder.</t>
+          <t>fsa:Inventories (eller fsa:ManufacturedGoodsAndGoodsForResale hvis total mangler).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="23" t="inlineStr">
         <is>
+          <t>Tilgodehavender fra salg</t>
+        </is>
+      </c>
+      <c r="B29" s="24">
+        <f>'balance_raw_35663908'!$F$20</f>
+        <v/>
+      </c>
+      <c r="C29" s="24">
+        <f>'balance_raw_35663908'!$E$20</f>
+        <v/>
+      </c>
+      <c r="D29" s="24">
+        <f>'balance_raw_35663908'!$D$20</f>
+        <v/>
+      </c>
+      <c r="F29" s="25" t="inlineStr">
+        <is>
+          <t>fsa:ShorttermTradeReceivables. Kortfristede tilgodehavender fra kunder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B29" s="24">
-        <f>'balance_raw_35663908'!$F$43</f>
-        <v/>
-      </c>
-      <c r="C29" s="24">
-        <f>'balance_raw_35663908'!$E$43</f>
-        <v/>
-      </c>
-      <c r="D29" s="24">
-        <f>'balance_raw_35663908'!$D$43</f>
-        <v/>
-      </c>
-      <c r="F29" s="25" t="inlineStr">
+      <c r="B30" s="24">
+        <f>'balance_raw_35663908'!$F$57</f>
+        <v/>
+      </c>
+      <c r="C30" s="24">
+        <f>'balance_raw_35663908'!$E$57</f>
+        <v/>
+      </c>
+      <c r="D30" s="24">
+        <f>'balance_raw_35663908'!$D$57</f>
+        <v/>
+      </c>
+      <c r="F30" s="25" t="inlineStr">
         <is>
           <t>fsa:ShorttermLiabilitiesOtherThanProvisions. Gæld der forfalder inden for 1 år.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="29" t="n"/>
-      <c r="B30" s="29" t="n"/>
-      <c r="C30" s="29" t="n"/>
-      <c r="D30" s="29" t="n"/>
-      <c r="F30" s="29" t="n"/>
-    </row>
     <row r="31">
-      <c r="A31" s="22" t="inlineStr">
+      <c r="A31" s="29" t="n"/>
+      <c r="B31" s="29" t="n"/>
+      <c r="C31" s="29" t="n"/>
+      <c r="D31" s="29" t="n"/>
+      <c r="F31" s="29" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="inlineStr">
         <is>
           <t>Rentabilitet</t>
         </is>
       </c>
-      <c r="B31" s="22" t="n"/>
-      <c r="C31" s="22" t="n"/>
-      <c r="D31" s="22" t="n"/>
-      <c r="F31" s="22" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="23" t="inlineStr">
-        <is>
-          <t>Afkastningsgrad, %</t>
-        </is>
-      </c>
-      <c r="B32" s="30">
-        <f>IFERROR((B12+B13)/B20*100,"")</f>
-        <v/>
-      </c>
-      <c r="C32" s="30">
-        <f>IFERROR((C12+C13)/C20*100,"")</f>
-        <v/>
-      </c>
-      <c r="D32" s="30">
-        <f>IFERROR((D12+D13)/D20*100,"")</f>
-        <v/>
-      </c>
-      <c r="F32" s="29" t="n"/>
+      <c r="B32" s="22" t="n"/>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+      <c r="F32" s="22" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="23" t="inlineStr">
         <is>
-          <t>Overskudsgrad, %</t>
+          <t>Afkastningsgrad, %</t>
         </is>
       </c>
       <c r="B33" s="30">
-        <f>IFERROR((B12+B13)/B5*100,"")</f>
+        <f>IFERROR((B13+B14)/B21*100,"")</f>
         <v/>
       </c>
       <c r="C33" s="30">
-        <f>IFERROR((C12+C13)/C5*100,"")</f>
+        <f>IFERROR((C13+C14)/C21*100,"")</f>
         <v/>
       </c>
       <c r="D33" s="30">
-        <f>IFERROR((D12+D13)/D5*100,"")</f>
+        <f>IFERROR((D13+D14)/D21*100,"")</f>
         <v/>
       </c>
       <c r="F33" s="29" t="n"/>
@@ -5829,19 +7154,19 @@
     <row r="34">
       <c r="A34" s="23" t="inlineStr">
         <is>
-          <t>Aktivernes omsætningshastighed, gange</t>
+          <t>Overskudsgrad, %</t>
         </is>
       </c>
       <c r="B34" s="30">
-        <f>IFERROR(B5/B20,"")</f>
+        <f>IFERROR((B13+B14)/B5*100,"")</f>
         <v/>
       </c>
       <c r="C34" s="30">
-        <f>IFERROR(C5/C20,"")</f>
+        <f>IFERROR((C13+C14)/C5*100,"")</f>
         <v/>
       </c>
       <c r="D34" s="30">
-        <f>IFERROR(D5/D20,"")</f>
+        <f>IFERROR((D13+D14)/D5*100,"")</f>
         <v/>
       </c>
       <c r="F34" s="29" t="n"/>
@@ -5849,19 +7174,19 @@
     <row r="35">
       <c r="A35" s="23" t="inlineStr">
         <is>
-          <t>Gældsrente, %</t>
+          <t>Aktivernes omsætningshastighed, gange</t>
         </is>
       </c>
       <c r="B35" s="30">
-        <f>IFERROR(-B14*100/B23,"")</f>
+        <f>IFERROR(B5/B21,"")</f>
         <v/>
       </c>
       <c r="C35" s="30">
-        <f>IFERROR(-C14*100/C23,"")</f>
+        <f>IFERROR(C5/C21,"")</f>
         <v/>
       </c>
       <c r="D35" s="30">
-        <f>IFERROR(-D14*100/D23,"")</f>
+        <f>IFERROR(D5/D21,"")</f>
         <v/>
       </c>
       <c r="F35" s="29" t="n"/>
@@ -5869,19 +7194,19 @@
     <row r="36">
       <c r="A36" s="23" t="inlineStr">
         <is>
-          <t>Egenkapitalens forrentning, %</t>
+          <t>Gældsrente, %</t>
         </is>
       </c>
       <c r="B36" s="30">
-        <f>IFERROR(B15/B22*100,"")</f>
+        <f>IFERROR(-B15*100/B24,"")</f>
         <v/>
       </c>
       <c r="C36" s="30">
-        <f>IFERROR(C15/C22*100,"")</f>
+        <f>IFERROR(-C15*100/C24,"")</f>
         <v/>
       </c>
       <c r="D36" s="30">
-        <f>IFERROR(D15/D22*100,"")</f>
+        <f>IFERROR(-D15*100/D24,"")</f>
         <v/>
       </c>
       <c r="F36" s="29" t="n"/>
@@ -5889,77 +7214,77 @@
     <row r="37">
       <c r="A37" s="23" t="inlineStr">
         <is>
+          <t>Egenkapitalens forrentning, %</t>
+        </is>
+      </c>
+      <c r="B37" s="30">
+        <f>IFERROR(B16/B23*100,"")</f>
+        <v/>
+      </c>
+      <c r="C37" s="30">
+        <f>IFERROR(C16/C23*100,"")</f>
+        <v/>
+      </c>
+      <c r="D37" s="30">
+        <f>IFERROR(D16/D23*100,"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="29" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="23" t="inlineStr">
+        <is>
           <t>Gearing, gange</t>
         </is>
       </c>
-      <c r="B37" s="30">
-        <f>IFERROR(B23/B22,"")</f>
-        <v/>
-      </c>
-      <c r="C37" s="30">
-        <f>IFERROR(C23/C22,"")</f>
-        <v/>
-      </c>
-      <c r="D37" s="30">
-        <f>IFERROR(D23/D22,"")</f>
-        <v/>
-      </c>
-      <c r="F37" s="29" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="29" t="n"/>
-      <c r="B38" s="29" t="n"/>
-      <c r="C38" s="29" t="n"/>
-      <c r="D38" s="29" t="n"/>
+      <c r="B38" s="30">
+        <f>IFERROR(B24/B23,"")</f>
+        <v/>
+      </c>
+      <c r="C38" s="30">
+        <f>IFERROR(C24/C23,"")</f>
+        <v/>
+      </c>
+      <c r="D38" s="30">
+        <f>IFERROR(D24/D23,"")</f>
+        <v/>
+      </c>
       <c r="F38" s="29" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="22" t="inlineStr">
-        <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
-        </is>
-      </c>
-      <c r="B39" s="22" t="n"/>
-      <c r="C39" s="22" t="n"/>
-      <c r="D39" s="22" t="n"/>
-      <c r="F39" s="22" t="n"/>
+      <c r="A39" s="29" t="n"/>
+      <c r="B39" s="29" t="n"/>
+      <c r="C39" s="29" t="n"/>
+      <c r="D39" s="29" t="n"/>
+      <c r="F39" s="29" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="23" t="inlineStr">
-        <is>
-          <t>Nettoomsætning</t>
-        </is>
-      </c>
-      <c r="B40" s="31">
-        <f>IFERROR(B5/$D5*100,"")</f>
-        <v/>
-      </c>
-      <c r="C40" s="31">
-        <f>IFERROR(C5/$D5*100,"")</f>
-        <v/>
-      </c>
-      <c r="D40" s="31">
-        <f>IFERROR(D5/$D5*100,"")</f>
-        <v/>
-      </c>
-      <c r="F40" s="29" t="n"/>
+      <c r="A40" s="22" t="inlineStr">
+        <is>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="n"/>
+      <c r="C40" s="22" t="n"/>
+      <c r="D40" s="22" t="n"/>
+      <c r="F40" s="22" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="23" t="inlineStr">
         <is>
-          <t>Produktionsomkostninger</t>
+          <t>Nettoomsætning</t>
         </is>
       </c>
       <c r="B41" s="31">
-        <f>IFERROR(B6/$D6*100,"")</f>
+        <f>IFERROR(B5/$D5*100,"")</f>
         <v/>
       </c>
       <c r="C41" s="31">
-        <f>IFERROR(C6/$D6*100,"")</f>
+        <f>IFERROR(C5/$D5*100,"")</f>
         <v/>
       </c>
       <c r="D41" s="31">
-        <f>IFERROR(D6/$D6*100,"")</f>
+        <f>IFERROR(D5/$D5*100,"")</f>
         <v/>
       </c>
       <c r="F41" s="29" t="n"/>
@@ -5967,19 +7292,19 @@
     <row r="42">
       <c r="A42" s="23" t="inlineStr">
         <is>
-          <t>Salgs- og distributionsomk.</t>
+          <t>Vareforbrug</t>
         </is>
       </c>
       <c r="B42" s="31">
-        <f>IFERROR(B8/$D8*100,"")</f>
+        <f>IFERROR(B7/$D7*100,"")</f>
         <v/>
       </c>
       <c r="C42" s="31">
-        <f>IFERROR(C8/$D8*100,"")</f>
+        <f>IFERROR(C7/$D7*100,"")</f>
         <v/>
       </c>
       <c r="D42" s="31">
-        <f>IFERROR(D8/$D8*100,"")</f>
+        <f>IFERROR(D7/$D7*100,"")</f>
         <v/>
       </c>
       <c r="F42" s="29" t="n"/>
@@ -5987,19 +7312,19 @@
     <row r="43">
       <c r="A43" s="23" t="inlineStr">
         <is>
-          <t>Administrationsomk.</t>
+          <t>Andre eksterne omk.</t>
         </is>
       </c>
       <c r="B43" s="31">
-        <f>IFERROR(B9/$D9*100,"")</f>
+        <f>IFERROR(B8/$D8*100,"")</f>
         <v/>
       </c>
       <c r="C43" s="31">
-        <f>IFERROR(C9/$D9*100,"")</f>
+        <f>IFERROR(C8/$D8*100,"")</f>
         <v/>
       </c>
       <c r="D43" s="31">
-        <f>IFERROR(D9/$D9*100,"")</f>
+        <f>IFERROR(D8/$D8*100,"")</f>
         <v/>
       </c>
       <c r="F43" s="29" t="n"/>
@@ -6007,77 +7332,77 @@
     <row r="44">
       <c r="A44" s="23" t="inlineStr">
         <is>
-          <t>Andre driftsomkostninger</t>
+          <t>Personaleomkostninger</t>
         </is>
       </c>
       <c r="B44" s="31">
+        <f>IFERROR(B10/$D10*100,"")</f>
+        <v/>
+      </c>
+      <c r="C44" s="31">
+        <f>IFERROR(C10/$D10*100,"")</f>
+        <v/>
+      </c>
+      <c r="D44" s="31">
+        <f>IFERROR(D10/$D10*100,"")</f>
+        <v/>
+      </c>
+      <c r="F44" s="29" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="23" t="inlineStr">
+        <is>
+          <t>Af- og nedskrivninger</t>
+        </is>
+      </c>
+      <c r="B45" s="31">
         <f>IFERROR(B11/$D11*100,"")</f>
         <v/>
       </c>
-      <c r="C44" s="31">
+      <c r="C45" s="31">
         <f>IFERROR(C11/$D11*100,"")</f>
         <v/>
       </c>
-      <c r="D44" s="31">
+      <c r="D45" s="31">
         <f>IFERROR(D11/$D11*100,"")</f>
         <v/>
       </c>
-      <c r="F44" s="29" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="29" t="n"/>
-      <c r="B45" s="29" t="n"/>
-      <c r="C45" s="29" t="n"/>
-      <c r="D45" s="29" t="n"/>
       <c r="F45" s="29" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="22" t="inlineStr">
-        <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
-        </is>
-      </c>
-      <c r="B46" s="22" t="n"/>
-      <c r="C46" s="22" t="n"/>
-      <c r="D46" s="22" t="n"/>
-      <c r="F46" s="22" t="n"/>
+      <c r="A46" s="29" t="n"/>
+      <c r="B46" s="29" t="n"/>
+      <c r="C46" s="29" t="n"/>
+      <c r="D46" s="29" t="n"/>
+      <c r="F46" s="29" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="23" t="inlineStr">
-        <is>
-          <t>Nettoomsætning</t>
-        </is>
-      </c>
-      <c r="B47" s="31">
-        <f>IFERROR(B5*100/$D5,"")</f>
-        <v/>
-      </c>
-      <c r="C47" s="31">
-        <f>IFERROR(C5*100/$D5,"")</f>
-        <v/>
-      </c>
-      <c r="D47" s="31">
-        <f>IFERROR(D5*100/$D5,"")</f>
-        <v/>
-      </c>
-      <c r="F47" s="29" t="n"/>
+      <c r="A47" s="22" t="inlineStr">
+        <is>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
+        </is>
+      </c>
+      <c r="B47" s="22" t="n"/>
+      <c r="C47" s="22" t="n"/>
+      <c r="D47" s="22" t="n"/>
+      <c r="F47" s="22" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="23" t="inlineStr">
         <is>
-          <t>Anlægsaktiver</t>
+          <t>Nettoomsætning</t>
         </is>
       </c>
       <c r="B48" s="31">
-        <f>IFERROR(B18*100/$D18,"")</f>
+        <f>IFERROR(B5*100/$D5,"")</f>
         <v/>
       </c>
       <c r="C48" s="31">
-        <f>IFERROR(C18*100/$D18,"")</f>
+        <f>IFERROR(C5*100/$D5,"")</f>
         <v/>
       </c>
       <c r="D48" s="31">
-        <f>IFERROR(D18*100/$D18,"")</f>
+        <f>IFERROR(D5*100/$D5,"")</f>
         <v/>
       </c>
       <c r="F48" s="29" t="n"/>
@@ -6085,19 +7410,19 @@
     <row r="49">
       <c r="A49" s="23" t="inlineStr">
         <is>
-          <t>Varebeholdninger</t>
+          <t>Anlægsaktiver</t>
         </is>
       </c>
       <c r="B49" s="31">
-        <f>IFERROR(B27*100/$D27,"")</f>
+        <f>IFERROR(B19*100/$D19,"")</f>
         <v/>
       </c>
       <c r="C49" s="31">
-        <f>IFERROR(C27*100/$D27,"")</f>
+        <f>IFERROR(C19*100/$D19,"")</f>
         <v/>
       </c>
       <c r="D49" s="31">
-        <f>IFERROR(D27*100/$D27,"")</f>
+        <f>IFERROR(D19*100/$D19,"")</f>
         <v/>
       </c>
       <c r="F49" s="29" t="n"/>
@@ -6105,7 +7430,7 @@
     <row r="50">
       <c r="A50" s="23" t="inlineStr">
         <is>
-          <t>Tilgodehavender fra salg</t>
+          <t>Varebeholdninger</t>
         </is>
       </c>
       <c r="B50" s="31">
@@ -6123,59 +7448,59 @@
       <c r="F50" s="29" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="29" t="n"/>
-      <c r="B51" s="29" t="n"/>
-      <c r="C51" s="29" t="n"/>
-      <c r="D51" s="29" t="n"/>
+      <c r="A51" s="23" t="inlineStr">
+        <is>
+          <t>Tilgodehavender fra salg</t>
+        </is>
+      </c>
+      <c r="B51" s="31">
+        <f>IFERROR(B29*100/$D29,"")</f>
+        <v/>
+      </c>
+      <c r="C51" s="31">
+        <f>IFERROR(C29*100/$D29,"")</f>
+        <v/>
+      </c>
+      <c r="D51" s="31">
+        <f>IFERROR(D29*100/$D29,"")</f>
+        <v/>
+      </c>
       <c r="F51" s="29" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="22" t="inlineStr">
+      <c r="A52" s="29" t="n"/>
+      <c r="B52" s="29" t="n"/>
+      <c r="C52" s="29" t="n"/>
+      <c r="D52" s="29" t="n"/>
+      <c r="F52" s="29" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="22" t="inlineStr">
         <is>
           <t>Soliditet og likviditet</t>
         </is>
       </c>
-      <c r="B52" s="22" t="n"/>
-      <c r="C52" s="22" t="n"/>
-      <c r="D52" s="22" t="n"/>
-      <c r="F52" s="22" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="23" t="inlineStr">
-        <is>
-          <t>Soliditetsgrad, %</t>
-        </is>
-      </c>
-      <c r="B53" s="30">
-        <f>IFERROR(B22*100/B20,"")</f>
-        <v/>
-      </c>
-      <c r="C53" s="30">
-        <f>IFERROR(C22*100/C20,"")</f>
-        <v/>
-      </c>
-      <c r="D53" s="30">
-        <f>IFERROR(D22*100/D20,"")</f>
-        <v/>
-      </c>
-      <c r="F53" s="29" t="n"/>
+      <c r="B53" s="22" t="n"/>
+      <c r="C53" s="22" t="n"/>
+      <c r="D53" s="22" t="n"/>
+      <c r="F53" s="22" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="23" t="inlineStr">
         <is>
-          <t>Gældsandel, %</t>
+          <t>Soliditetsgrad, %</t>
         </is>
       </c>
       <c r="B54" s="30">
-        <f>IFERROR(B23*100/B20,"")</f>
+        <f>IFERROR(B23*100/B21,"")</f>
         <v/>
       </c>
       <c r="C54" s="30">
-        <f>IFERROR(C23*100/C20,"")</f>
+        <f>IFERROR(C23*100/C21,"")</f>
         <v/>
       </c>
       <c r="D54" s="30">
-        <f>IFERROR(D23*100/D20,"")</f>
+        <f>IFERROR(D23*100/D21,"")</f>
         <v/>
       </c>
       <c r="F54" s="29" t="n"/>
@@ -6183,198 +7508,218 @@
     <row r="55">
       <c r="A55" s="23" t="inlineStr">
         <is>
+          <t>Gældsandel, %</t>
+        </is>
+      </c>
+      <c r="B55" s="30">
+        <f>IFERROR(B24*100/B21,"")</f>
+        <v/>
+      </c>
+      <c r="C55" s="30">
+        <f>IFERROR(C24*100/C21,"")</f>
+        <v/>
+      </c>
+      <c r="D55" s="30">
+        <f>IFERROR(D24*100/D21,"")</f>
+        <v/>
+      </c>
+      <c r="F55" s="29" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="23" t="inlineStr">
+        <is>
           <t>Likviditetsgrad, %</t>
         </is>
       </c>
-      <c r="B55" s="30">
-        <f>IFERROR(B19*100/B29,"")</f>
-        <v/>
-      </c>
-      <c r="C55" s="30">
-        <f>IFERROR(C19*100/C29,"")</f>
-        <v/>
-      </c>
-      <c r="D55" s="30">
-        <f>IFERROR(D19*100/D29,"")</f>
-        <v/>
-      </c>
-      <c r="F55" s="29" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="29" t="n"/>
-      <c r="B56" s="29" t="n"/>
-      <c r="C56" s="29" t="n"/>
-      <c r="D56" s="29" t="n"/>
+      <c r="B56" s="30">
+        <f>IFERROR(B20*100/B30,"")</f>
+        <v/>
+      </c>
+      <c r="C56" s="30">
+        <f>IFERROR(C20*100/C30,"")</f>
+        <v/>
+      </c>
+      <c r="D56" s="30">
+        <f>IFERROR(D20*100/D30,"")</f>
+        <v/>
+      </c>
       <c r="F56" s="29" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="32" t="inlineStr">
-        <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
-        </is>
-      </c>
+      <c r="A57" s="29" t="n"/>
       <c r="B57" s="29" t="n"/>
       <c r="C57" s="29" t="n"/>
       <c r="D57" s="29" t="n"/>
       <c r="F57" s="29" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="29" t="n"/>
+      <c r="A58" s="32" t="inlineStr">
+        <is>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+        </is>
+      </c>
       <c r="B58" s="29" t="n"/>
       <c r="C58" s="29" t="n"/>
       <c r="D58" s="29" t="n"/>
       <c r="F58" s="29" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="22" t="inlineStr">
+      <c r="A59" s="29" t="n"/>
+      <c r="B59" s="29" t="n"/>
+      <c r="C59" s="29" t="n"/>
+      <c r="D59" s="29" t="n"/>
+      <c r="F59" s="29" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="22" t="inlineStr">
         <is>
           <t>Krydstjek mod rådata (tolerance: 1 t.kr.)</t>
         </is>
       </c>
-      <c r="B59" s="22" t="n"/>
-      <c r="C59" s="22" t="n"/>
-      <c r="D59" s="22" t="n"/>
-      <c r="F59" s="22" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="23" t="inlineStr">
-        <is>
-          <t>Aktiver i alt = fsa:Assets</t>
-        </is>
-      </c>
-      <c r="B60" s="29">
-        <f>IF('balance_raw_35663908'!$F$17="","—",IF(ABS(B20-'balance_raw_35663908'!$F$17)&lt;=1,"✓ OK","❌ "&amp;TEXT(B20-'balance_raw_35663908'!$F$17,"+#,##0;-#,##0")&amp;" t.kr."))</f>
-        <v/>
-      </c>
-      <c r="C60" s="29">
-        <f>IF('balance_raw_35663908'!$E$17="","—",IF(ABS(C20-'balance_raw_35663908'!$E$17)&lt;=1,"✓ OK","❌ "&amp;TEXT(C20-'balance_raw_35663908'!$E$17,"+#,##0;-#,##0")&amp;" t.kr."))</f>
-        <v/>
-      </c>
-      <c r="D60" s="29">
-        <f>IF('balance_raw_35663908'!$D$17="","—",IF(ABS(D20-'balance_raw_35663908'!$D$17)&lt;=1,"✓ OK","❌ "&amp;TEXT(D20-'balance_raw_35663908'!$D$17,"+#,##0;-#,##0")&amp;" t.kr."))</f>
-        <v/>
-      </c>
-      <c r="F60" s="25" t="inlineStr">
-        <is>
-          <t>Verificerer at sum(Anlæg+Omsætning) matcher Assets-totalen.</t>
-        </is>
-      </c>
+      <c r="B60" s="22" t="n"/>
+      <c r="C60" s="22" t="n"/>
+      <c r="D60" s="22" t="n"/>
+      <c r="F60" s="22" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="23" t="inlineStr">
         <is>
-          <t>Passiver i alt = fsa:LiabilitiesAndEquity</t>
+          <t>Aktiver i alt = fsa:Assets</t>
         </is>
       </c>
       <c r="B61" s="29">
-        <f>IF('balance_raw_35663908'!$F$45="","—",IF(ABS(B24-'balance_raw_35663908'!$F$45)&lt;=1,"✓ OK","❌ "&amp;TEXT(B24-'balance_raw_35663908'!$F$45,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_35663908'!$F$31="","—",IF(ABS(B21-'balance_raw_35663908'!$F$31)&lt;=1,"✓ OK","❌ "&amp;TEXT(B21-'balance_raw_35663908'!$F$31,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="C61" s="29">
-        <f>IF('balance_raw_35663908'!$E$45="","—",IF(ABS(C24-'balance_raw_35663908'!$E$45)&lt;=1,"✓ OK","❌ "&amp;TEXT(C24-'balance_raw_35663908'!$E$45,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_35663908'!$E$31="","—",IF(ABS(C21-'balance_raw_35663908'!$E$31)&lt;=1,"✓ OK","❌ "&amp;TEXT(C21-'balance_raw_35663908'!$E$31,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="D61" s="29">
-        <f>IF('balance_raw_35663908'!$D$45="","—",IF(ABS(D24-'balance_raw_35663908'!$D$45)&lt;=1,"✓ OK","❌ "&amp;TEXT(D24-'balance_raw_35663908'!$D$45,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_35663908'!$D$31="","—",IF(ABS(D21-'balance_raw_35663908'!$D$31)&lt;=1,"✓ OK","❌ "&amp;TEXT(D21-'balance_raw_35663908'!$D$31,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="F61" s="25" t="inlineStr">
         <is>
-          <t>Verificerer at sum(EK+Forpligtelser) matcher Passiver-totalen.</t>
+          <t>Verificerer at sum(Anlæg+Omsætning) matcher Assets-totalen.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="23" t="inlineStr">
         <is>
-          <t>Aktiver i alt = Passiver i alt</t>
+          <t>Passiver i alt = fsa:LiabilitiesAndEquity</t>
         </is>
       </c>
       <c r="B62" s="29">
-        <f>IF(ABS(B20-B24)&lt;=1,"✓ OK","❌ "&amp;TEXT(B20-B24,"+#,##0;-#,##0")&amp;" t.kr.")</f>
+        <f>IF('balance_raw_35663908'!$F$59="","—",IF(ABS(B25-'balance_raw_35663908'!$F$59)&lt;=1,"✓ OK","❌ "&amp;TEXT(B25-'balance_raw_35663908'!$F$59,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="C62" s="29">
-        <f>IF(ABS(C20-C24)&lt;=1,"✓ OK","❌ "&amp;TEXT(C20-C24,"+#,##0;-#,##0")&amp;" t.kr.")</f>
+        <f>IF('balance_raw_35663908'!$E$59="","—",IF(ABS(C25-'balance_raw_35663908'!$E$59)&lt;=1,"✓ OK","❌ "&amp;TEXT(C25-'balance_raw_35663908'!$E$59,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="D62" s="29">
-        <f>IF(ABS(D20-D24)&lt;=1,"✓ OK","❌ "&amp;TEXT(D20-D24,"+#,##0;-#,##0")&amp;" t.kr.")</f>
+        <f>IF('balance_raw_35663908'!$D$59="","—",IF(ABS(D25-'balance_raw_35663908'!$D$59)&lt;=1,"✓ OK","❌ "&amp;TEXT(D25-'balance_raw_35663908'!$D$59,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="F62" s="25" t="inlineStr">
         <is>
-          <t>Balance-identitet på arket selv. Skal altid være 0 differance.</t>
+          <t>Verificerer at sum(EK+Forpligtelser) matcher Passiver-totalen.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="23" t="inlineStr">
         <is>
-          <t>Bruttoresultat (beregnet) = fsa:GrossResult</t>
+          <t>Aktiver i alt = Passiver i alt</t>
         </is>
       </c>
       <c r="B63" s="29">
-        <f>IF('res_raw_35663908'!$F$4="","—",IF(ABS(B7-'res_raw_35663908'!$F$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(B7-'res_raw_35663908'!$F$4,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF(ABS(B21-B25)&lt;=1,"✓ OK","❌ "&amp;TEXT(B21-B25,"+#,##0;-#,##0")&amp;" t.kr.")</f>
         <v/>
       </c>
       <c r="C63" s="29">
-        <f>IF('res_raw_35663908'!$E$4="","—",IF(ABS(C7-'res_raw_35663908'!$E$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(C7-'res_raw_35663908'!$E$4,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF(ABS(C21-C25)&lt;=1,"✓ OK","❌ "&amp;TEXT(C21-C25,"+#,##0;-#,##0")&amp;" t.kr.")</f>
         <v/>
       </c>
       <c r="D63" s="29">
-        <f>IF('res_raw_35663908'!$D$4="","—",IF(ABS(D7-'res_raw_35663908'!$D$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(D7-'res_raw_35663908'!$D$4,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF(ABS(D21-D25)&lt;=1,"✓ OK","❌ "&amp;TEXT(D21-D25,"+#,##0;-#,##0")&amp;" t.kr.")</f>
         <v/>
       </c>
       <c r="F63" s="25" t="inlineStr">
         <is>
-          <t>Hvis Nettoomsætning eller omkostninger mangler, vil sumberegnet bruttoresultat afvige.</t>
+          <t>Balance-identitet på arket selv. Skal altid være 0 differance.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="23" t="inlineStr">
         <is>
-          <t>EBIT (beregnet) = fsa:ProfitLossFromOrdinaryOperatingActivities</t>
+          <t>Bruttoresultat (beregnet) = fsa:GrossResult</t>
         </is>
       </c>
       <c r="B64" s="29">
-        <f>IF('res_raw_35663908'!$F$9="","—",IF(ABS(B12-'res_raw_35663908'!$F$9)&lt;=1,"✓ OK","❌ "&amp;TEXT(B12-'res_raw_35663908'!$F$9,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_35663908'!$F$6="","—",IF(ABS(B9-'res_raw_35663908'!$F$6)&lt;=1,"✓ OK","❌ "&amp;TEXT(B9-'res_raw_35663908'!$F$6,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="C64" s="29">
-        <f>IF('res_raw_35663908'!$E$9="","—",IF(ABS(C12-'res_raw_35663908'!$E$9)&lt;=1,"✓ OK","❌ "&amp;TEXT(C12-'res_raw_35663908'!$E$9,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_35663908'!$E$6="","—",IF(ABS(C9-'res_raw_35663908'!$E$6)&lt;=1,"✓ OK","❌ "&amp;TEXT(C9-'res_raw_35663908'!$E$6,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="D64" s="29">
-        <f>IF('res_raw_35663908'!$D$9="","—",IF(ABS(D12-'res_raw_35663908'!$D$9)&lt;=1,"✓ OK","❌ "&amp;TEXT(D12-'res_raw_35663908'!$D$9,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_35663908'!$D$6="","—",IF(ABS(D9-'res_raw_35663908'!$D$6)&lt;=1,"✓ OK","❌ "&amp;TEXT(D9-'res_raw_35663908'!$D$6,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="F64" s="25" t="inlineStr">
         <is>
-          <t>Verificerer at sumberegnet EBIT matcher det rapporterede.</t>
+          <t>Hvis Nettoomsætning eller omkostninger mangler, vil sumberegnet bruttoresultat afvige.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="23" t="inlineStr">
         <is>
+          <t>EBIT (beregnet) = fsa:ProfitLossFromOrdinaryOperatingActivities</t>
+        </is>
+      </c>
+      <c r="B65" s="29">
+        <f>IF('res_raw_35663908'!$F$11="","—",IF(ABS(B13-'res_raw_35663908'!$F$11)&lt;=1,"✓ OK","❌ "&amp;TEXT(B13-'res_raw_35663908'!$F$11,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <v/>
+      </c>
+      <c r="C65" s="29">
+        <f>IF('res_raw_35663908'!$E$11="","—",IF(ABS(C13-'res_raw_35663908'!$E$11)&lt;=1,"✓ OK","❌ "&amp;TEXT(C13-'res_raw_35663908'!$E$11,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <v/>
+      </c>
+      <c r="D65" s="29">
+        <f>IF('res_raw_35663908'!$D$11="","—",IF(ABS(D13-'res_raw_35663908'!$D$11)&lt;=1,"✓ OK","❌ "&amp;TEXT(D13-'res_raw_35663908'!$D$11,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <v/>
+      </c>
+      <c r="F65" s="25" t="inlineStr">
+        <is>
+          <t>Verificerer at sumberegnet EBIT matcher det rapporterede.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="23" t="inlineStr">
+        <is>
           <t>EBT (beregnet) = fsa:ProfitLossFromOrdinaryActivitiesBeforeTax</t>
         </is>
       </c>
-      <c r="B65" s="29">
-        <f>IF('res_raw_35663908'!$F$14="","—",IF(ABS(B15-'res_raw_35663908'!$F$14)&lt;=1,"✓ OK","❌ "&amp;TEXT(B15-'res_raw_35663908'!$F$14,"+#,##0;-#,##0")&amp;" t.kr."))</f>
-        <v/>
-      </c>
-      <c r="C65" s="29">
-        <f>IF('res_raw_35663908'!$E$14="","—",IF(ABS(C15-'res_raw_35663908'!$E$14)&lt;=1,"✓ OK","❌ "&amp;TEXT(C15-'res_raw_35663908'!$E$14,"+#,##0;-#,##0")&amp;" t.kr."))</f>
-        <v/>
-      </c>
-      <c r="D65" s="29">
-        <f>IF('res_raw_35663908'!$D$14="","—",IF(ABS(D15-'res_raw_35663908'!$D$14)&lt;=1,"✓ OK","❌ "&amp;TEXT(D15-'res_raw_35663908'!$D$14,"+#,##0;-#,##0")&amp;" t.kr."))</f>
-        <v/>
-      </c>
-      <c r="F65" s="25" t="inlineStr">
+      <c r="B66" s="29">
+        <f>IF('res_raw_35663908'!$F$16="","—",IF(ABS(B16-'res_raw_35663908'!$F$16)&lt;=1,"✓ OK","❌ "&amp;TEXT(B16-'res_raw_35663908'!$F$16,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <v/>
+      </c>
+      <c r="C66" s="29">
+        <f>IF('res_raw_35663908'!$E$16="","—",IF(ABS(C16-'res_raw_35663908'!$E$16)&lt;=1,"✓ OK","❌ "&amp;TEXT(C16-'res_raw_35663908'!$E$16,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <v/>
+      </c>
+      <c r="D66" s="29">
+        <f>IF('res_raw_35663908'!$D$16="","—",IF(ABS(D16-'res_raw_35663908'!$D$16)&lt;=1,"✓ OK","❌ "&amp;TEXT(D16-'res_raw_35663908'!$D$16,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <v/>
+      </c>
+      <c r="F66" s="25" t="inlineStr">
         <is>
           <t>Verificerer at sumberegnet resultat før skat matcher det rapporterede.</t>
         </is>
@@ -6386,4 +7731,635 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="62" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="33" t="inlineStr">
+        <is>
+          <t>Ukendte XBRL-felter — disse er noter og ikke en del af hoved-regnskabet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Dansk navn</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>XBRL feltnavn</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2021 t.kr.</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2022 t.kr.</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023 t.kr.</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2024 t.kr.</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2025 t.kr.</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Forklaring</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="34" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B3" s="34" t="inlineStr">
+        <is>
+          <t>fsa:AcquisitionOfCompaniesAndActivitiesSpecification</t>
+        </is>
+      </c>
+      <c r="C3" s="34" t="inlineStr">
+        <is>
+          <t>fsa:AcquisitionOfCompaniesAndActivitiesSpecification</t>
+        </is>
+      </c>
+      <c r="D3" s="35" t="n"/>
+      <c r="E3" s="35" t="n"/>
+      <c r="F3" s="35" t="n"/>
+      <c r="G3" s="35" t="n">
+        <v>3600</v>
+      </c>
+      <c r="H3" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="36" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="37" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B4" s="37" t="inlineStr">
+        <is>
+          <t>fsa:CurrentContractAssets</t>
+        </is>
+      </c>
+      <c r="C4" s="37" t="inlineStr">
+        <is>
+          <t>fsa:CurrentContractAssets</t>
+        </is>
+      </c>
+      <c r="D4" s="38" t="n"/>
+      <c r="E4" s="38" t="n"/>
+      <c r="F4" s="38" t="n"/>
+      <c r="G4" s="38" t="n">
+        <v>67900</v>
+      </c>
+      <c r="H4" s="38" t="n">
+        <v>55700</v>
+      </c>
+      <c r="I4" s="39" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B5" s="34" t="inlineStr">
+        <is>
+          <t>fsa:CurrentContractLiabilities</t>
+        </is>
+      </c>
+      <c r="C5" s="34" t="inlineStr">
+        <is>
+          <t>fsa:CurrentContractLiabilities</t>
+        </is>
+      </c>
+      <c r="D5" s="35" t="n"/>
+      <c r="E5" s="35" t="n"/>
+      <c r="F5" s="35" t="n"/>
+      <c r="G5" s="35" t="n">
+        <v>101400</v>
+      </c>
+      <c r="H5" s="35" t="n">
+        <v>118500</v>
+      </c>
+      <c r="I5" s="36" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="37" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B6" s="37" t="inlineStr">
+        <is>
+          <t>fsa:DecreaseOfCapital</t>
+        </is>
+      </c>
+      <c r="C6" s="37" t="inlineStr">
+        <is>
+          <t>fsa:DecreaseOfCapital</t>
+        </is>
+      </c>
+      <c r="D6" s="38" t="n"/>
+      <c r="E6" s="38" t="n"/>
+      <c r="F6" s="38" t="n"/>
+      <c r="G6" s="38" t="n"/>
+      <c r="H6" s="38" t="n">
+        <v>33300</v>
+      </c>
+      <c r="I6" s="39" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="34" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B7" s="34" t="inlineStr">
+        <is>
+          <t>fsa:EmployeeExpensesTransferredToAssets</t>
+        </is>
+      </c>
+      <c r="C7" s="34" t="inlineStr">
+        <is>
+          <t>fsa:EmployeeExpensesTransferredToAssets</t>
+        </is>
+      </c>
+      <c r="D7" s="35" t="n"/>
+      <c r="E7" s="35" t="n"/>
+      <c r="F7" s="35" t="n"/>
+      <c r="G7" s="35" t="n">
+        <v>-15200</v>
+      </c>
+      <c r="H7" s="35" t="n">
+        <v>-21300</v>
+      </c>
+      <c r="I7" s="36" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="37" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B8" s="37" t="inlineStr">
+        <is>
+          <t>fsa:FeesForAuditorsPerformingOtherAssuranceReports</t>
+        </is>
+      </c>
+      <c r="C8" s="37" t="inlineStr">
+        <is>
+          <t>fsa:FeesForAuditorsPerformingOtherAssuranceReports</t>
+        </is>
+      </c>
+      <c r="D8" s="38" t="n"/>
+      <c r="E8" s="38" t="n"/>
+      <c r="F8" s="38" t="n"/>
+      <c r="G8" s="38" t="n">
+        <v>100</v>
+      </c>
+      <c r="H8" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="39" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="34" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B9" s="34" t="inlineStr">
+        <is>
+          <t>fsa:InterestExpenseAssignedToAssociates</t>
+        </is>
+      </c>
+      <c r="C9" s="34" t="inlineStr">
+        <is>
+          <t>fsa:InterestExpenseAssignedToAssociates</t>
+        </is>
+      </c>
+      <c r="D9" s="35" t="n"/>
+      <c r="E9" s="35" t="n"/>
+      <c r="F9" s="35" t="n"/>
+      <c r="G9" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="35" t="n">
+        <v>700</v>
+      </c>
+      <c r="I9" s="36" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="37" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B10" s="37" t="inlineStr">
+        <is>
+          <t>fsa:InterestExpenseToParticipatingInterests</t>
+        </is>
+      </c>
+      <c r="C10" s="37" t="inlineStr">
+        <is>
+          <t>fsa:InterestExpenseToParticipatingInterests</t>
+        </is>
+      </c>
+      <c r="D10" s="38" t="n"/>
+      <c r="E10" s="38" t="n"/>
+      <c r="F10" s="38" t="n"/>
+      <c r="G10" s="38" t="n">
+        <v>25700</v>
+      </c>
+      <c r="H10" s="38" t="n">
+        <v>17900</v>
+      </c>
+      <c r="I10" s="39" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="34" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B11" s="34" t="inlineStr">
+        <is>
+          <t>fsa:InterestReceived</t>
+        </is>
+      </c>
+      <c r="C11" s="34" t="inlineStr">
+        <is>
+          <t>fsa:InterestReceived</t>
+        </is>
+      </c>
+      <c r="D11" s="35" t="n"/>
+      <c r="E11" s="35" t="n"/>
+      <c r="F11" s="35" t="n"/>
+      <c r="G11" s="35" t="n">
+        <v>-11800</v>
+      </c>
+      <c r="H11" s="35" t="n">
+        <v>-7700</v>
+      </c>
+      <c r="I11" s="36" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="37" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B12" s="37" t="inlineStr">
+        <is>
+          <t>fsa:LongtermTaxPayables</t>
+        </is>
+      </c>
+      <c r="C12" s="37" t="inlineStr">
+        <is>
+          <t>fsa:LongtermTaxPayables</t>
+        </is>
+      </c>
+      <c r="D12" s="38" t="n"/>
+      <c r="E12" s="38" t="n"/>
+      <c r="F12" s="38" t="n"/>
+      <c r="G12" s="38" t="n">
+        <v>53300</v>
+      </c>
+      <c r="H12" s="38" t="n">
+        <v>54100</v>
+      </c>
+      <c r="I12" s="39" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="34" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B13" s="34" t="inlineStr">
+        <is>
+          <t>fsa:NoncurrentContractLiabilities</t>
+        </is>
+      </c>
+      <c r="C13" s="34" t="inlineStr">
+        <is>
+          <t>fsa:NoncurrentContractLiabilities</t>
+        </is>
+      </c>
+      <c r="D13" s="35" t="n"/>
+      <c r="E13" s="35" t="n"/>
+      <c r="F13" s="35" t="n"/>
+      <c r="G13" s="35" t="n">
+        <v>11100</v>
+      </c>
+      <c r="H13" s="35" t="n">
+        <v>31100</v>
+      </c>
+      <c r="I13" s="36" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="37" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B14" s="37" t="inlineStr">
+        <is>
+          <t>fsa:OtherProvisionsLiabilitiesShortterm</t>
+        </is>
+      </c>
+      <c r="C14" s="37" t="inlineStr">
+        <is>
+          <t>fsa:OtherProvisionsLiabilitiesShortterm</t>
+        </is>
+      </c>
+      <c r="D14" s="38" t="n"/>
+      <c r="E14" s="38" t="n"/>
+      <c r="F14" s="38" t="n"/>
+      <c r="G14" s="38" t="n">
+        <v>8800</v>
+      </c>
+      <c r="H14" s="38" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I14" s="39" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="34" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B15" s="34" t="inlineStr">
+        <is>
+          <t>fsa:PensionLiabilitiesRelatedToManagementCategory</t>
+        </is>
+      </c>
+      <c r="C15" s="34" t="inlineStr">
+        <is>
+          <t>fsa:PensionLiabilitiesRelatedToManagementCategory</t>
+        </is>
+      </c>
+      <c r="D15" s="35" t="n"/>
+      <c r="E15" s="35" t="n"/>
+      <c r="F15" s="35" t="n"/>
+      <c r="G15" s="35" t="n">
+        <v>400</v>
+      </c>
+      <c r="H15" s="35" t="n">
+        <v>300</v>
+      </c>
+      <c r="I15" s="36" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="37" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B16" s="37" t="inlineStr">
+        <is>
+          <t>fsa:PensionsAndSimilarLiabilitiesLiabilitiesLongterm</t>
+        </is>
+      </c>
+      <c r="C16" s="37" t="inlineStr">
+        <is>
+          <t>fsa:PensionsAndSimilarLiabilitiesLiabilitiesLongterm</t>
+        </is>
+      </c>
+      <c r="D16" s="38" t="n"/>
+      <c r="E16" s="38" t="n"/>
+      <c r="F16" s="38" t="n"/>
+      <c r="G16" s="38" t="n">
+        <v>3500</v>
+      </c>
+      <c r="H16" s="38" t="n">
+        <v>3900</v>
+      </c>
+      <c r="I16" s="39" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="34" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B17" s="34" t="inlineStr">
+        <is>
+          <t>fsa:SaleOfMinorityShares</t>
+        </is>
+      </c>
+      <c r="C17" s="34" t="inlineStr">
+        <is>
+          <t>fsa:SaleOfMinorityShares</t>
+        </is>
+      </c>
+      <c r="D17" s="35" t="n"/>
+      <c r="E17" s="35" t="n"/>
+      <c r="F17" s="35" t="n"/>
+      <c r="G17" s="35" t="n"/>
+      <c r="H17" s="35" t="n">
+        <v>500</v>
+      </c>
+      <c r="I17" s="36" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="37" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B18" s="37" t="inlineStr">
+        <is>
+          <t>fsa:SaleOfTreasuryShares</t>
+        </is>
+      </c>
+      <c r="C18" s="37" t="inlineStr">
+        <is>
+          <t>fsa:SaleOfTreasuryShares</t>
+        </is>
+      </c>
+      <c r="D18" s="38" t="n"/>
+      <c r="E18" s="38" t="n"/>
+      <c r="F18" s="38" t="n"/>
+      <c r="G18" s="38" t="n">
+        <v>8600</v>
+      </c>
+      <c r="H18" s="38" t="n">
+        <v>10100</v>
+      </c>
+      <c r="I18" s="39" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="34" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B19" s="34" t="inlineStr">
+        <is>
+          <t>fsa:SalesOfTreasuryShares</t>
+        </is>
+      </c>
+      <c r="C19" s="34" t="inlineStr">
+        <is>
+          <t>fsa:SalesOfTreasuryShares</t>
+        </is>
+      </c>
+      <c r="D19" s="35" t="n"/>
+      <c r="E19" s="35" t="n"/>
+      <c r="F19" s="35" t="n"/>
+      <c r="G19" s="35" t="n"/>
+      <c r="H19" s="35" t="n">
+        <v>9600</v>
+      </c>
+      <c r="I19" s="36" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="37" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B20" s="37" t="inlineStr">
+        <is>
+          <t>fsa:ShorttermReceivablesDividendsFromGroupEnterprises</t>
+        </is>
+      </c>
+      <c r="C20" s="37" t="inlineStr">
+        <is>
+          <t>fsa:ShorttermReceivablesDividendsFromGroupEnterprises</t>
+        </is>
+      </c>
+      <c r="D20" s="38" t="n"/>
+      <c r="E20" s="38" t="n"/>
+      <c r="F20" s="38" t="n"/>
+      <c r="G20" s="38" t="n">
+        <v>7700</v>
+      </c>
+      <c r="H20" s="38" t="n">
+        <v>5200</v>
+      </c>
+      <c r="I20" s="39" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>